--- a/2026/ITALIA/Julio/Julio ITALIA.xlsx
+++ b/2026/ITALIA/Julio/Julio ITALIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68489463-9752-48BC-B48C-F958859E482F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE229E11-CF48-4432-B110-1F4AB0B46D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$127</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$145</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$141</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="262">
   <si>
     <t>TOTAL</t>
   </si>
@@ -475,12 +480,6 @@
   </si>
   <si>
     <t>CUIT ADMINISTRACION:  27-23125687-9</t>
-  </si>
-  <si>
-    <t>Mantenimiento de cuenta - Banco Credicop</t>
-  </si>
-  <si>
-    <t>ARCA VEP</t>
   </si>
   <si>
     <t>Municipalidad de avellaneda</t>
@@ -605,9 +604,6 @@
     <t>4 E COCHERA MARIA AMELIA XHARDEZ</t>
   </si>
   <si>
-    <t>ARCA - Plan de pago - Cuota 45/60</t>
-  </si>
-  <si>
     <t>Ramon Troncoso</t>
   </si>
   <si>
@@ -677,99 +673,21 @@
     <t>InOut Control - Comando control y camaras - JUNIO</t>
   </si>
   <si>
-    <t>Galvan Zaffalon - Compra de bombachupadora de calle de 1hp monofasica</t>
-  </si>
-  <si>
-    <t>Transf 26/06</t>
-  </si>
-  <si>
-    <t>Incluye SAC</t>
-  </si>
-  <si>
-    <t>Transf 25/06</t>
-  </si>
-  <si>
     <t>Quotteri Mateo - Certificacion de deuda de expensas UF 68</t>
   </si>
   <si>
-    <t>Fire - Compra de pantalon, remera, buzo para Sr. Encargado</t>
-  </si>
-  <si>
     <t>Cuello Natalia - Desobstruccion lavadero 9C</t>
   </si>
   <si>
-    <t>Transf 19/06</t>
-  </si>
-  <si>
     <t>Cuello Natalia - Desobstruccion lavadero 9D</t>
   </si>
   <si>
     <t>Cuello Natalia - Desobstruccion lavadero 6D</t>
   </si>
   <si>
-    <t>Doartero Julio - Visita electrica</t>
-  </si>
-  <si>
-    <t>Transf 04/06</t>
-  </si>
-  <si>
-    <t>Debito 12/06</t>
-  </si>
-  <si>
-    <t>Transf 05/06</t>
-  </si>
-  <si>
-    <t>Ferreteria La 95 - Copia de llave</t>
-  </si>
-  <si>
-    <t>Sra. Arias mirta - Confieccion de formulario 931 - periodo 04/2025</t>
-  </si>
-  <si>
-    <t>Transf 11/06</t>
-  </si>
-  <si>
-    <t>Transf 17/06</t>
-  </si>
-  <si>
-    <t>Transf 18/06</t>
-  </si>
-  <si>
-    <t>Suplente Sr. Cristian Del Pezzo</t>
-  </si>
-  <si>
-    <t>Ascensores Lema - Arreglo finalizacion pago cambio cables de acero</t>
-  </si>
-  <si>
-    <t>Suplente Sr Lucas Ezequiel Dominguez</t>
-  </si>
-  <si>
-    <t>Seguro Sr. Lucas</t>
-  </si>
-  <si>
-    <t>Seguro Sr. Cristan</t>
-  </si>
-  <si>
     <t>Efectivo</t>
   </si>
   <si>
-    <t>Oscar Colmeiro / Cordoba Matias - A cuenta de trabajo de plomeria, albañileria y pintura</t>
-  </si>
-  <si>
-    <t>Transf 08/06 - 11/06</t>
-  </si>
-  <si>
-    <t>Transf 08/06 - 16/06</t>
-  </si>
-  <si>
-    <t>Debito 30/06</t>
-  </si>
-  <si>
-    <t>Falta de fondos</t>
-  </si>
-  <si>
-    <t>Efectivo por falta de fondos en banco</t>
-  </si>
-  <si>
     <t>Total 1er</t>
   </si>
   <si>
@@ -803,9 +721,6 @@
     <t>QUIENES SE ENCUENTRAN MARCADOS EN COLOR AMARILLO CONTINÚAN ABONANDO SUS EXPENSAS EN LA CUENTA BANCARIA ANTERIOR. LES RECORDAMOS QUE, A PARTIR DEL CAMBIO APROBADO, TODAS LAS EXPENSAS DEBEN DEPOSITARSE EXCLUSIVAMENTE EN LA CUENTA DEL BANCO SANTANDER. POR FAVOR, VERIFIQUEN LOS DATOS BANCARIOS ANTES DE REALIZAR EL PAGO.</t>
   </si>
   <si>
-    <t>Gastos bancarios - Credicop - No se puede cerrar la cuenta aun por el plan de ARCA hasta no tener inscripto el reglamento que ya Sali - Dependemos de la voluntad de la antigua administradora</t>
-  </si>
-  <si>
     <t>EN PROCESO DE EJECUCION</t>
   </si>
   <si>
@@ -836,25 +751,105 @@
     <t xml:space="preserve">Suarez Agustin Ignacio - MAYO </t>
   </si>
   <si>
-    <t>Suarez Agustin Ignacio - JUNIO - Fumigacion se adeuda JULIO</t>
-  </si>
-  <si>
     <t>Transf 10/07</t>
   </si>
   <si>
     <t>Cuello Natalia - Desobstruccion lavadero 11A</t>
   </si>
   <si>
-    <t>Cuello Natalia - Desobstruccion de columna en baño en 2D</t>
-  </si>
-  <si>
     <t>Transf 21/07</t>
   </si>
   <si>
     <t>Transf 23/07</t>
   </si>
   <si>
-    <t>Romnatti carlos - Certificacion copias digitales</t>
+    <t>Transf 06/07</t>
+  </si>
+  <si>
+    <t>Debito 13/07</t>
+  </si>
+  <si>
+    <t>Correo Argentino - Envio 2 cartas documentos - Edificio lindero : situacion raices de arbol</t>
+  </si>
+  <si>
+    <t>Suarez Agustin Ignacio - JUNIO - Se adeuda JULIO</t>
+  </si>
+  <si>
+    <r>
+      <t>Oscar Colmeiro / Cordoba Matias -</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A cuenta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de trabajo de plomeria, albañileria y pintura - 8vo B cambio de desague cocina y lavadero - 8vo f cambio de desague de cocina, lavadero y albañileria - 8vo E cambio de desague de cocina, lavadero y albañileria - 6to c cambio de desague de cocina, lavadero y albañileria + llave de paso - 7mo C cambio de desague de cocina, lavadero y albañileria - 3ro D cambio de desague de cocina, lavadero y albañileria + cambio de cañeria agua fria cocina y lavadero + llaves de paso - 3ro C cambio de desague de cocina, lavadero + Cambio de cañeria agua fria y caliente cocina y lavadero + llaves de paso - 4to D cambio de llaves de paso agua fria y caliente - 1ro C reparacion de llave de paso</t>
+    </r>
+  </si>
+  <si>
+    <t>En Juli0 2026 suben a $781.000</t>
+  </si>
+  <si>
+    <t>Grafica Tauge - Fotocopias BYN</t>
+  </si>
+  <si>
+    <t>Galvan Zaffalon - Compra de materiales para modificacion de cañeria entrada de agua con By pass</t>
+  </si>
+  <si>
+    <t>Transf 14/7</t>
+  </si>
+  <si>
+    <t>Suplencia Sra. Silvana</t>
+  </si>
+  <si>
+    <t>Feriado</t>
+  </si>
+  <si>
+    <t>Transf 15/07</t>
+  </si>
+  <si>
+    <t>Seguro Sra. Silvana</t>
+  </si>
+  <si>
+    <t>Transf 16/07</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Desobstruccion emergencia de columna en baño en 2D</t>
+  </si>
+  <si>
+    <t>Romnatti carlos - Digitalizacion de reglamento entregado por el gestor</t>
+  </si>
+  <si>
+    <t>Transf 30/07</t>
+  </si>
+  <si>
+    <t>Ascensores Lema - Pago material placa ascensores</t>
+  </si>
+  <si>
+    <t>Gastos bancarios - Santander</t>
+  </si>
+  <si>
+    <t>Mantenimiento de cuenta - Banco Credicop + Gastos bancarios</t>
+  </si>
+  <si>
+    <t>ARCA - Plan de pago - Cuota 46/60</t>
+  </si>
+  <si>
+    <t>ARCA VEP - No se abona (explicacion en el cuerpo de expensas)</t>
   </si>
 </sst>
 </file>
@@ -1629,7 +1624,7 @@
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="289">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1981,202 +1976,205 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="8" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="8" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -2261,9 +2259,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2301,9 +2299,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2336,9 +2334,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2371,9 +2386,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2547,23 +2579,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M146"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M142"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="228" t="s">
         <v>146</v>
@@ -2572,7 +2604,7 @@
       <c r="D1" s="228"/>
       <c r="E1" s="229"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="9" t="s">
         <v>148</v>
@@ -2581,16 +2613,16 @@
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="232" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C3" s="232"/>
       <c r="D3" s="232"/>
       <c r="E3" s="233"/>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>100</v>
       </c>
@@ -2601,12 +2633,12 @@
       <c r="D4" s="7"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
@@ -2614,55 +2646,55 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="90" t="s">
         <v>137</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="48"/>
       <c r="B8" s="234" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="C8" s="234"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="48"/>
       <c r="B9" s="234"/>
       <c r="C9" s="234"/>
       <c r="D9" s="48"/>
       <c r="E9" s="48"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="48"/>
       <c r="B10" s="234"/>
       <c r="C10" s="234"/>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="48"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
       <c r="E11" s="48"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="48"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
       <c r="D12" s="48"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="235" t="s">
         <v>103</v>
       </c>
@@ -2671,49 +2703,49 @@
       <c r="D13" s="235"/>
       <c r="E13" s="235"/>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="235"/>
       <c r="B14" s="235"/>
       <c r="C14" s="235"/>
       <c r="D14" s="235"/>
       <c r="E14" s="235"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="235"/>
       <c r="B15" s="235"/>
       <c r="C15" s="235"/>
       <c r="D15" s="235"/>
       <c r="E15" s="235"/>
     </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="235"/>
       <c r="B16" s="235"/>
       <c r="C16" s="235"/>
       <c r="D16" s="235"/>
       <c r="E16" s="235"/>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
       <c r="E17" s="48"/>
     </row>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="178"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="179" t="s">
         <v>104</v>
       </c>
@@ -2722,7 +2754,7 @@
       <c r="D20" s="58"/>
       <c r="E20" s="59"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
         <v>138</v>
       </c>
@@ -2731,45 +2763,43 @@
       <c r="D21" s="117"/>
       <c r="E21" s="152"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="230" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B22" s="231"/>
       <c r="C22" s="182"/>
       <c r="D22" s="183">
-        <v>3382992.69</v>
-      </c>
-      <c r="E22" s="153" t="s">
-        <v>215</v>
-      </c>
+        <v>2337709.7000000002</v>
+      </c>
+      <c r="E22" s="153"/>
       <c r="H22" s="19"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="230" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B23" s="231"/>
       <c r="C23" s="182"/>
       <c r="D23" s="183">
-        <v>-735800.92</v>
+        <v>-508451.7</v>
       </c>
       <c r="E23" s="20"/>
       <c r="H23" s="19"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="230" t="s">
         <v>1</v>
       </c>
       <c r="B24" s="231"/>
       <c r="C24" s="182"/>
       <c r="D24" s="184">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="E24" s="20"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="185" t="s">
         <v>105</v>
       </c>
@@ -2778,82 +2808,75 @@
       <c r="D25" s="22"/>
       <c r="E25" s="154">
         <f>SUM(D22:D24)</f>
-        <v>2647192</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>1829258.0000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="185" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B26" s="185"/>
       <c r="C26" s="185"/>
       <c r="D26" s="22"/>
       <c r="E26" s="155"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="182"/>
       <c r="B27" s="182"/>
       <c r="C27" s="182"/>
       <c r="D27" s="35"/>
       <c r="E27" s="168"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="182"/>
       <c r="B28" s="182"/>
       <c r="C28" s="182"/>
       <c r="D28" s="35"/>
       <c r="E28" s="168"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="182" t="s">
-        <v>232</v>
-      </c>
+    <row r="29" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="182"/>
       <c r="B29" s="182"/>
       <c r="C29" s="182"/>
-      <c r="D29" s="35">
-        <v>37000</v>
-      </c>
+      <c r="D29" s="35"/>
       <c r="E29" s="168"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="182" t="s">
-        <v>234</v>
-      </c>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="182"/>
       <c r="B30" s="182"/>
       <c r="C30" s="182"/>
-      <c r="D30" s="35">
-        <f>53000+480000</f>
-        <v>533000</v>
-      </c>
+      <c r="D30" s="35"/>
       <c r="E30" s="156"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="182" t="s">
-        <v>235</v>
-      </c>
-      <c r="B31" s="182"/>
+        <v>249</v>
+      </c>
+      <c r="B31" s="182" t="s">
+        <v>250</v>
+      </c>
       <c r="C31" s="182"/>
-      <c r="D31" s="35">
-        <v>5837</v>
+      <c r="D31" s="223">
+        <v>125000</v>
       </c>
       <c r="E31" s="156" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="182" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B32" s="182"/>
       <c r="C32" s="182"/>
-      <c r="D32" s="35">
-        <v>5837</v>
+      <c r="D32" s="223">
+        <v>5087</v>
       </c>
       <c r="E32" s="156" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="185" t="s">
         <v>105</v>
       </c>
@@ -2862,10 +2885,10 @@
       <c r="D33" s="107"/>
       <c r="E33" s="157">
         <f>SUM(D29:D32)</f>
-        <v>581674</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>130087</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
         <v>139</v>
       </c>
@@ -2874,88 +2897,86 @@
       <c r="D34" s="22"/>
       <c r="E34" s="155"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="182" t="s">
-        <v>189</v>
+        <v>260</v>
       </c>
       <c r="B35" s="187"/>
       <c r="C35" s="187"/>
-      <c r="D35" s="35">
-        <v>12320.76</v>
+      <c r="D35" s="223">
+        <v>12214.52</v>
       </c>
       <c r="E35" s="156" t="str">
         <f>E37</f>
-        <v>Debito 12/06</v>
+        <v>Debito 13/07</v>
       </c>
       <c r="G35" s="66"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="182" t="s">
-        <v>150</v>
+        <v>261</v>
       </c>
       <c r="B36" s="187"/>
       <c r="C36" s="187"/>
       <c r="D36" s="35">
-        <v>923050.1</v>
-      </c>
-      <c r="E36" s="156" t="s">
-        <v>241</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E36" s="156"/>
       <c r="G36" s="66"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="182" t="s">
         <v>141</v>
       </c>
       <c r="B37" s="187"/>
       <c r="C37" s="187"/>
-      <c r="D37" s="288">
+      <c r="D37" s="223">
         <v>292530.53999999998</v>
       </c>
       <c r="E37" s="156" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="G37" s="66"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="182" t="s">
         <v>143</v>
       </c>
       <c r="B38" s="187"/>
       <c r="C38" s="187"/>
-      <c r="D38" s="288">
+      <c r="D38" s="223">
         <v>152234.67000000001</v>
       </c>
       <c r="E38" s="156" t="str">
         <f>E37</f>
-        <v>Debito 12/06</v>
+        <v>Debito 13/07</v>
       </c>
       <c r="G38" s="50"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="182" t="s">
         <v>142</v>
       </c>
       <c r="B39" s="187"/>
       <c r="C39" s="187"/>
-      <c r="D39" s="288">
+      <c r="D39" s="223">
         <v>16914.96</v>
       </c>
       <c r="E39" s="156" t="str">
         <f>E37</f>
-        <v>Debito 12/06</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>Debito 13/07</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="182" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B40" s="187"/>
       <c r="C40" s="187"/>
       <c r="D40" s="35"/>
       <c r="E40" s="156"/>
     </row>
-    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="185" t="s">
         <v>140</v>
       </c>
@@ -2964,10 +2985,10 @@
       <c r="D41" s="22"/>
       <c r="E41" s="41">
         <f>SUM(D35:D40)</f>
-        <v>1397051.0299999998</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>473894.69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>106</v>
       </c>
@@ -2976,33 +2997,33 @@
       <c r="D42" s="23"/>
       <c r="E42" s="157"/>
     </row>
-    <row r="43" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="226" t="s">
-        <v>185</v>
-      </c>
-      <c r="B43" s="227"/>
+    <row r="43" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="236" t="s">
+        <v>183</v>
+      </c>
+      <c r="B43" s="237"/>
       <c r="C43" s="26"/>
       <c r="D43" s="287">
         <v>7805</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="226" t="s">
-        <v>187</v>
-      </c>
-      <c r="B44" s="227"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="236" t="s">
+        <v>185</v>
+      </c>
+      <c r="B44" s="237"/>
       <c r="C44" s="26"/>
       <c r="D44" s="287">
-        <v>214164</v>
+        <v>213891</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
         <v>107</v>
       </c>
@@ -3011,10 +3032,10 @@
       <c r="D45" s="22"/>
       <c r="E45" s="41">
         <f>SUM(D43:D44)</f>
-        <v>221969</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>221696</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>108</v>
       </c>
@@ -3023,40 +3044,42 @@
       <c r="D46" s="28"/>
       <c r="E46" s="158"/>
     </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
         <v>109</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C47" s="29"/>
-      <c r="D47" s="282">
+      <c r="D47" s="221">
         <v>1390852.75</v>
       </c>
-      <c r="E47" s="192"/>
-    </row>
-    <row r="48" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E47" s="118" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
         <v>109</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C48" s="29"/>
-      <c r="D48" s="282">
+      <c r="D48" s="221">
         <v>36242.83</v>
       </c>
       <c r="E48" s="192" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="29" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C49" s="29"/>
       <c r="D49" s="30">
@@ -3064,9 +3087,9 @@
       </c>
       <c r="E49" s="20"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B50" s="31"/>
       <c r="C50" s="29"/>
@@ -3075,20 +3098,20 @@
       </c>
       <c r="E50" s="20"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="226" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="236" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="227"/>
+      <c r="B51" s="237"/>
       <c r="C51" s="29"/>
-      <c r="D51" s="30">
-        <v>0</v>
+      <c r="D51" s="221">
+        <v>5946930.7699999996</v>
       </c>
       <c r="E51" s="118" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="32" t="s">
         <v>111</v>
       </c>
@@ -3097,7 +3120,7 @@
       <c r="D52" s="30"/>
       <c r="E52" s="20"/>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="21" t="s">
         <v>112</v>
       </c>
@@ -3106,899 +3129,843 @@
       <c r="D53" s="33"/>
       <c r="E53" s="159">
         <f>SUM(D47:D52)</f>
-        <v>1427095.58</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7374026.3499999996</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="22"/>
       <c r="E54" s="160"/>
     </row>
-    <row r="55" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="219" t="s">
-        <v>166</v>
-      </c>
-      <c r="B55" s="220"/>
+    <row r="55" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="224" t="s">
+        <v>164</v>
+      </c>
+      <c r="B55" s="225"/>
       <c r="C55" s="29"/>
-      <c r="D55" s="282">
+      <c r="D55" s="221">
         <v>285000</v>
       </c>
       <c r="E55" s="167" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="219" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="224" t="s">
+        <v>257</v>
+      </c>
+      <c r="B56" s="225"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="221">
+        <v>280000</v>
+      </c>
+      <c r="E56" s="167" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="224" t="s">
+        <v>244</v>
+      </c>
+      <c r="B57" s="225"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="221">
+        <v>1400000</v>
+      </c>
+      <c r="E57" s="167"/>
+      <c r="F57" s="50"/>
+    </row>
+    <row r="58" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="92" t="s">
         <v>233</v>
-      </c>
-      <c r="B56" s="220"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="30">
-        <f>660000+1400000</f>
-        <v>2060000</v>
-      </c>
-      <c r="E56" s="167" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="219" t="s">
-        <v>238</v>
-      </c>
-      <c r="B57" s="220"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="282">
-        <v>1400000</v>
-      </c>
-      <c r="E57" s="167" t="s">
-        <v>240</v>
-      </c>
-      <c r="F57" s="50"/>
-    </row>
-    <row r="58" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="92" t="s">
-        <v>263</v>
       </c>
       <c r="B58" s="17"/>
       <c r="C58" s="29"/>
-      <c r="D58" s="282">
+      <c r="D58" s="221">
         <v>841000</v>
       </c>
       <c r="E58" s="167" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="F58" s="50"/>
     </row>
-    <row r="59" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="B59" s="17"/>
+    <row r="59" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="224" t="s">
+        <v>247</v>
+      </c>
+      <c r="B59" s="225"/>
       <c r="C59" s="29"/>
-      <c r="D59" s="30">
-        <v>3000</v>
+      <c r="D59" s="221">
+        <v>687000</v>
       </c>
       <c r="E59" s="34" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F59" s="50"/>
     </row>
-    <row r="60" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="B60" s="17"/>
+    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="219" t="s">
+        <v>224</v>
+      </c>
+      <c r="B60" s="220"/>
       <c r="C60" s="29"/>
-      <c r="D60" s="30">
+      <c r="D60" s="221">
         <v>6990</v>
       </c>
       <c r="E60" s="34"/>
       <c r="F60" s="50"/>
     </row>
-    <row r="61" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="219" t="s">
-        <v>213</v>
-      </c>
-      <c r="B61" s="220"/>
+    <row r="61" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="92" t="s">
+        <v>212</v>
+      </c>
+      <c r="B61" s="17"/>
       <c r="C61" s="29"/>
-      <c r="D61" s="30">
-        <v>342000</v>
+      <c r="D61" s="221">
+        <v>31400</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="F61" s="50"/>
     </row>
-    <row r="62" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="92" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="B62" s="17"/>
       <c r="C62" s="29"/>
-      <c r="D62" s="30">
-        <v>67900</v>
+      <c r="D62" s="221">
+        <v>31400</v>
       </c>
       <c r="E62" s="34" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="F62" s="50"/>
     </row>
-    <row r="63" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="92" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B63" s="17"/>
       <c r="C63" s="29"/>
-      <c r="D63" s="282">
+      <c r="D63" s="221">
         <v>31400</v>
       </c>
       <c r="E63" s="34" t="s">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="F63" s="50"/>
     </row>
-    <row r="64" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="92" t="s">
-        <v>268</v>
+        <v>213</v>
       </c>
       <c r="B64" s="17"/>
       <c r="C64" s="29"/>
-      <c r="D64" s="282">
+      <c r="D64" s="221">
         <v>31400</v>
       </c>
       <c r="E64" s="34" t="s">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="F64" s="50"/>
     </row>
-    <row r="65" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="92" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B65" s="17"/>
       <c r="C65" s="29"/>
-      <c r="D65" s="282">
+      <c r="D65" s="221">
         <v>31400</v>
       </c>
-      <c r="E65" s="34"/>
+      <c r="E65" s="34" t="s">
+        <v>238</v>
+      </c>
       <c r="F65" s="50"/>
     </row>
-    <row r="66" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="92" t="s">
-        <v>222</v>
-      </c>
-      <c r="B66" s="17"/>
+    <row r="66" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="224" t="s">
+        <v>254</v>
+      </c>
+      <c r="B66" s="225"/>
       <c r="C66" s="29"/>
-      <c r="D66" s="282">
-        <v>31400</v>
+      <c r="D66" s="221">
+        <v>138600</v>
       </c>
       <c r="E66" s="34" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="F66" s="50"/>
     </row>
-    <row r="67" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="92" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="B67" s="17"/>
       <c r="C67" s="29"/>
-      <c r="D67" s="282">
-        <v>31400</v>
-      </c>
-      <c r="E67" s="34" t="s">
-        <v>270</v>
+      <c r="D67" s="221">
+        <v>145600</v>
+      </c>
+      <c r="E67" s="167" t="s">
+        <v>234</v>
       </c>
       <c r="F67" s="50"/>
     </row>
-    <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="92" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="B68" s="17"/>
       <c r="C68" s="29"/>
-      <c r="D68" s="282">
-        <v>138600</v>
-      </c>
-      <c r="E68" s="34" t="s">
-        <v>270</v>
+      <c r="D68" s="221">
+        <v>152250</v>
+      </c>
+      <c r="E68" s="167" t="s">
+        <v>234</v>
       </c>
       <c r="F68" s="50"/>
     </row>
-    <row r="69" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="92" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="B69" s="17"/>
       <c r="C69" s="29"/>
-      <c r="D69" s="282">
-        <v>145600</v>
+      <c r="D69" s="221">
+        <v>7500</v>
       </c>
       <c r="E69" s="167" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="F69" s="50"/>
     </row>
-    <row r="70" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="92" t="s">
-        <v>266</v>
+        <v>200</v>
       </c>
       <c r="B70" s="17"/>
       <c r="C70" s="29"/>
-      <c r="D70" s="282">
-        <v>145600</v>
+      <c r="D70" s="221">
+        <v>405300</v>
       </c>
       <c r="E70" s="167" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="F70" s="50"/>
     </row>
-    <row r="71" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="92" t="s">
-        <v>203</v>
-      </c>
-      <c r="B71" s="17"/>
+    <row r="71" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="224" t="s">
+        <v>209</v>
+      </c>
+      <c r="B71" s="225"/>
       <c r="C71" s="29"/>
-      <c r="D71" s="30">
-        <v>292300</v>
+      <c r="D71" s="221">
+        <v>124611.12</v>
       </c>
       <c r="E71" s="167" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="F71" s="50"/>
     </row>
-    <row r="72" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="92" t="s">
-        <v>203</v>
-      </c>
-      <c r="B72" s="17"/>
+    <row r="72" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="224" t="s">
+        <v>230</v>
+      </c>
+      <c r="B72" s="225"/>
       <c r="C72" s="29"/>
-      <c r="D72" s="30">
-        <v>467850</v>
+      <c r="D72" s="221">
+        <v>124611.12</v>
       </c>
       <c r="E72" s="167" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F72" s="50"/>
     </row>
-    <row r="73" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="92" t="s">
-        <v>203</v>
-      </c>
-      <c r="B73" s="17"/>
-      <c r="C73" s="29"/>
-      <c r="D73" s="30">
-        <v>380000</v>
-      </c>
-      <c r="E73" s="167" t="s">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B73" s="14"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="41">
+        <f>SUM(D55:D72)</f>
+        <v>4755462.24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B74" s="14"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="152"/>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="224" t="s">
         <v>231</v>
       </c>
-      <c r="F73" s="50"/>
-    </row>
-    <row r="74" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="219" t="s">
-        <v>223</v>
-      </c>
-      <c r="B74" s="220"/>
-      <c r="C74" s="29"/>
-      <c r="D74" s="30">
-        <v>25000</v>
-      </c>
-      <c r="E74" s="167" t="s">
-        <v>224</v>
-      </c>
-      <c r="F74" s="50"/>
-    </row>
-    <row r="75" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="219" t="s">
-        <v>212</v>
-      </c>
-      <c r="B75" s="220"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="282">
-        <v>124611.12</v>
+      <c r="B75" s="225"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="288">
+        <v>650000</v>
       </c>
       <c r="E75" s="167" t="s">
-        <v>264</v>
-      </c>
-      <c r="F75" s="50"/>
-    </row>
-    <row r="76" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="219" t="s">
-        <v>260</v>
-      </c>
-      <c r="B76" s="220"/>
-      <c r="C76" s="29"/>
-      <c r="D76" s="282">
-        <v>124611.12</v>
+        <v>234</v>
+      </c>
+      <c r="G75" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="224" t="s">
+        <v>242</v>
+      </c>
+      <c r="B76" s="225"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="222">
+        <v>50000</v>
       </c>
       <c r="E76" s="167" t="s">
-        <v>264</v>
-      </c>
-      <c r="F76" s="50"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="36"/>
-      <c r="E77" s="41">
-        <f>SUM(D55:D76)</f>
-        <v>7007062.2400000002</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="152"/>
-    </row>
-    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="219" t="s">
-        <v>261</v>
-      </c>
-      <c r="B79" s="220"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B77" s="17"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="222">
+        <v>250000</v>
+      </c>
+      <c r="E77" s="167" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="92" t="s">
+        <v>255</v>
+      </c>
+      <c r="B78" s="17"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="222">
+        <v>484217.8</v>
+      </c>
+      <c r="E78" s="167" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="92" t="s">
+        <v>232</v>
+      </c>
+      <c r="B79" s="17"/>
       <c r="C79" s="18"/>
-      <c r="D79" s="284">
-        <v>650000</v>
+      <c r="D79" s="222">
+        <v>50000</v>
       </c>
       <c r="E79" s="167" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B80" s="17"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="283">
-        <v>250000</v>
-      </c>
-      <c r="E80" s="167" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="92" t="s">
-        <v>272</v>
-      </c>
-      <c r="B81" s="17"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="283">
-        <v>484217.8</v>
-      </c>
-      <c r="E81" s="167" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="92" t="s">
-        <v>228</v>
-      </c>
-      <c r="B82" s="17"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="285">
-        <v>100000</v>
-      </c>
-      <c r="E82" s="153" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="92" t="s">
-        <v>262</v>
-      </c>
-      <c r="B83" s="17"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="285">
-        <v>45000</v>
-      </c>
-      <c r="E83" s="167" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="21" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="B84" s="21"/>
-      <c r="C84" s="21"/>
-      <c r="D84" s="22"/>
-      <c r="E84" s="154">
-        <f>SUM(D79:D83)</f>
-        <v>1529217.8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="14" t="s">
+      <c r="B80" s="21"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="154">
+        <f>SUM(D75:D79)</f>
+        <v>1484217.8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B85" s="37"/>
-      <c r="C85" s="21"/>
-      <c r="D85" s="38"/>
-      <c r="E85" s="41"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="B86" s="91"/>
-      <c r="C86" s="91"/>
-      <c r="D86" s="286">
-        <v>59000</v>
-      </c>
-      <c r="E86" s="161"/>
-    </row>
-    <row r="87" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="226" t="s">
-        <v>255</v>
-      </c>
-      <c r="B87" s="227"/>
-      <c r="C87" s="91"/>
-      <c r="D87" s="286">
-        <f>39523+201766.98</f>
-        <v>241289.98</v>
-      </c>
-      <c r="E87" s="161"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="39" t="s">
+      <c r="B81" s="37"/>
+      <c r="C81" s="21"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="41"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="B82" s="91"/>
+      <c r="C82" s="91"/>
+      <c r="D82" s="289">
+        <f>44612.24+65000-12214.52</f>
+        <v>97397.719999999987</v>
+      </c>
+      <c r="E82" s="161"/>
+    </row>
+    <row r="83" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="236" t="s">
+        <v>258</v>
+      </c>
+      <c r="B83" s="237"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="289">
+        <v>225591.15</v>
+      </c>
+      <c r="E83" s="161"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="B88" s="39"/>
-      <c r="C88" s="39"/>
-      <c r="D88" s="40"/>
-      <c r="E88" s="41">
-        <f>SUM(D86:D87)</f>
-        <v>300289.98</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="29"/>
-      <c r="B89" s="29"/>
-      <c r="C89" s="29"/>
-      <c r="D89" s="42"/>
-      <c r="E89" s="43"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="44" t="s">
+      <c r="B84" s="39"/>
+      <c r="C84" s="39"/>
+      <c r="D84" s="40"/>
+      <c r="E84" s="41">
+        <f>SUM(D82:D83)</f>
+        <v>322988.87</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="29"/>
+      <c r="B85" s="29"/>
+      <c r="C85" s="29"/>
+      <c r="D85" s="42"/>
+      <c r="E85" s="43"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="B90" s="44"/>
-      <c r="C90" s="44"/>
-      <c r="D90" s="45"/>
-      <c r="E90" s="46"/>
-    </row>
-    <row r="91" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="47"/>
-      <c r="D91" s="48"/>
-      <c r="E91" s="49"/>
-      <c r="F91" s="50"/>
-    </row>
-    <row r="92" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="51" t="s">
+      <c r="B86" s="44"/>
+      <c r="C86" s="44"/>
+      <c r="D86" s="45"/>
+      <c r="E86" s="46"/>
+    </row>
+    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="47"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="50"/>
+    </row>
+    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="B92" s="52"/>
-      <c r="C92" s="53"/>
-      <c r="D92" s="54"/>
-      <c r="E92" s="55">
-        <f>(SUM(E21:E90))</f>
-        <v>15111551.630000001</v>
-      </c>
-      <c r="F92" s="56"/>
-      <c r="G92" s="50"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D93" s="48"/>
-      <c r="E93" s="48"/>
-    </row>
-    <row r="94" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D94" s="48"/>
-      <c r="E94" s="48"/>
-      <c r="H94" s="57"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="11" t="s">
+      <c r="B88" s="52"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="54"/>
+      <c r="E88" s="55">
+        <f>(SUM(E21:E86))</f>
+        <v>16591630.949999999</v>
+      </c>
+      <c r="F88" s="56"/>
+      <c r="G88" s="50"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D89" s="48"/>
+      <c r="E89" s="48"/>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D90" s="48"/>
+      <c r="E90" s="48"/>
+      <c r="H90" s="57"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B95" s="12"/>
-      <c r="C95" s="13"/>
-      <c r="D95" s="58"/>
-      <c r="E95" s="59"/>
-    </row>
-    <row r="96" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="221"/>
-      <c r="B96" s="221"/>
-      <c r="C96" s="31"/>
-      <c r="D96" s="222"/>
-      <c r="E96" s="224"/>
-    </row>
-    <row r="97" spans="1:5" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="221"/>
-      <c r="B97" s="221"/>
-      <c r="C97" s="31"/>
-      <c r="D97" s="223"/>
-      <c r="E97" s="225"/>
-    </row>
-    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="29"/>
-      <c r="B98" s="29"/>
-      <c r="D98" s="42"/>
-      <c r="E98" s="42"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="24"/>
-      <c r="B99" s="61"/>
-      <c r="C99" s="29"/>
-      <c r="D99" s="35"/>
-      <c r="E99" s="60"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="62" t="s">
+      <c r="B91" s="12"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="58"/>
+      <c r="E91" s="59"/>
+    </row>
+    <row r="92" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="238"/>
+      <c r="B92" s="238"/>
+      <c r="C92" s="31"/>
+      <c r="D92" s="239"/>
+      <c r="E92" s="241"/>
+    </row>
+    <row r="93" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="238"/>
+      <c r="B93" s="238"/>
+      <c r="C93" s="31"/>
+      <c r="D93" s="240"/>
+      <c r="E93" s="242"/>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="29"/>
+      <c r="B94" s="29"/>
+      <c r="D94" s="42"/>
+      <c r="E94" s="42"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="24"/>
+      <c r="B95" s="61"/>
+      <c r="C95" s="29"/>
+      <c r="D95" s="35"/>
+      <c r="E95" s="60"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="B100" s="63"/>
-      <c r="C100" s="63"/>
-      <c r="D100" s="116"/>
-      <c r="E100" s="162">
-        <f>SUM(D96:D99)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D101" s="48"/>
-      <c r="E101" s="48"/>
-    </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B96" s="63"/>
+      <c r="C96" s="63"/>
+      <c r="D96" s="116"/>
+      <c r="E96" s="162">
+        <f>SUM(D92:D95)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D97" s="48"/>
+      <c r="E97" s="48"/>
+    </row>
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D98" s="48"/>
+      <c r="E98" s="48"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B99" s="44"/>
+      <c r="C99" s="44"/>
+      <c r="D99" s="45"/>
+      <c r="E99" s="166">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D100" s="48"/>
+      <c r="E100" s="48"/>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B101" s="52"/>
+      <c r="C101" s="53"/>
+      <c r="D101" s="54"/>
+      <c r="E101" s="55">
+        <f>E96+E99</f>
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D102" s="48"/>
       <c r="E102" s="48"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="B103" s="44"/>
-      <c r="C103" s="44"/>
-      <c r="D103" s="45"/>
-      <c r="E103" s="166">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="B103" s="65">
+        <f>E88</f>
+        <v>16591630.949999999</v>
+      </c>
+      <c r="D103" s="48"/>
+      <c r="E103" s="48"/>
+    </row>
+    <row r="104" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="B104" s="65">
+        <f>E88-E86</f>
+        <v>16591630.949999999</v>
+      </c>
       <c r="D104" s="48"/>
       <c r="E104" s="48"/>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="B105" s="52"/>
-      <c r="C105" s="53"/>
-      <c r="D105" s="54"/>
-      <c r="E105" s="55">
-        <f>E100+E103</f>
+    <row r="105" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="B105" s="65">
+        <f>E101-E99</f>
+        <v>0</v>
+      </c>
+      <c r="D105" s="48"/>
+      <c r="E105" s="48"/>
+    </row>
+    <row r="106" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="B106" s="65">
+        <f>E101</f>
         <v>3000000</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D106" s="48"/>
       <c r="E106" s="48"/>
     </row>
-    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="64" t="s">
-        <v>120</v>
-      </c>
-      <c r="B107" s="65">
-        <f>E92</f>
-        <v>15111551.630000001</v>
-      </c>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
     </row>
-    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="64" t="s">
-        <v>121</v>
-      </c>
-      <c r="B108" s="65">
-        <f>E92-E90</f>
-        <v>15111551.630000001</v>
-      </c>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D108" s="48"/>
       <c r="E108" s="48"/>
     </row>
-    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="B109" s="65">
-        <f>E105-E103</f>
-        <v>0</v>
-      </c>
+    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="227" t="s">
+        <v>172</v>
+      </c>
+      <c r="B109" s="227"/>
       <c r="D109" s="48"/>
       <c r="E109" s="48"/>
     </row>
-    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="B110" s="65">
-        <f>E105</f>
-        <v>3000000</v>
-      </c>
+    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="227"/>
+      <c r="B110" s="227"/>
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="227"/>
+      <c r="B111" s="227"/>
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
     </row>
-    <row r="113" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="237" t="s">
-        <v>174</v>
-      </c>
-      <c r="B113" s="237"/>
+    <row r="113" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="227" t="s">
+        <v>199</v>
+      </c>
+      <c r="B113" s="227"/>
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
     </row>
-    <row r="114" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="237"/>
-      <c r="B114" s="237"/>
+    <row r="114" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="227"/>
+      <c r="B114" s="227"/>
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
-    <row r="115" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="237"/>
-      <c r="B115" s="237"/>
+    <row r="115" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="227"/>
+      <c r="B115" s="227"/>
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
     </row>
-    <row r="117" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="237" t="s">
-        <v>202</v>
-      </c>
-      <c r="B117" s="237"/>
+    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="227" t="s">
+        <v>179</v>
+      </c>
+      <c r="B117" s="227"/>
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
     </row>
-    <row r="118" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="237"/>
-      <c r="B118" s="237"/>
+    <row r="118" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="227"/>
+      <c r="B118" s="227"/>
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
     </row>
-    <row r="119" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="237"/>
-      <c r="B119" s="237"/>
+    <row r="119" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="227"/>
+      <c r="B119" s="227"/>
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
-    <row r="120" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D120" s="48"/>
       <c r="E120" s="48"/>
     </row>
-    <row r="121" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="237" t="s">
-        <v>181</v>
-      </c>
-      <c r="B121" s="237"/>
+    <row r="121" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="227" t="s">
+        <v>182</v>
+      </c>
+      <c r="B121" s="227"/>
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
     </row>
-    <row r="122" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="237"/>
-      <c r="B122" s="237"/>
+    <row r="122" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="227"/>
+      <c r="B122" s="227"/>
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
     </row>
-    <row r="123" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="237"/>
-      <c r="B123" s="237"/>
+    <row r="123" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="227"/>
+      <c r="B123" s="227"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
     </row>
-    <row r="124" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
     </row>
-    <row r="125" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="237" t="s">
-        <v>184</v>
-      </c>
-      <c r="B125" s="237"/>
+    <row r="125" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="227" t="s">
+        <v>181</v>
+      </c>
+      <c r="B125" s="227"/>
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
     </row>
-    <row r="126" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="237"/>
-      <c r="B126" s="237"/>
+    <row r="126" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="227"/>
+      <c r="B126" s="227"/>
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
     </row>
-    <row r="127" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="237"/>
-      <c r="B127" s="237"/>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="227"/>
+      <c r="B127" s="227"/>
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
     </row>
-    <row r="128" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D128" s="48"/>
       <c r="E128" s="48"/>
     </row>
-    <row r="129" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="237" t="s">
-        <v>183</v>
-      </c>
-      <c r="B129" s="237"/>
-      <c r="D129" s="48"/>
-      <c r="E129" s="48"/>
-    </row>
-    <row r="130" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="237"/>
-      <c r="B130" s="237"/>
-      <c r="D130" s="48"/>
-      <c r="E130" s="48"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="237"/>
-      <c r="B131" s="237"/>
+    <row r="129" spans="1:13" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129"/>
+      <c r="B129" s="66"/>
+      <c r="C129" s="67"/>
+      <c r="D129" s="163"/>
+      <c r="E129" s="163"/>
+    </row>
+    <row r="130" spans="1:13" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="169" t="s">
+        <v>189</v>
+      </c>
+      <c r="B130" s="69">
+        <v>-668629.54</v>
+      </c>
+      <c r="C130" s="67"/>
+      <c r="D130" s="164"/>
+      <c r="E130" s="164"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B131" s="70">
+        <f>-B104-B105</f>
+        <v>-16591630.949999999</v>
+      </c>
       <c r="D131" s="48"/>
       <c r="E131" s="48"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B132" s="70">
+        <f>B141</f>
+        <v>432000</v>
+      </c>
       <c r="D132" s="48"/>
       <c r="E132" s="48"/>
-    </row>
-    <row r="133" spans="1:6" s="68" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A133"/>
-      <c r="B133" s="66"/>
-      <c r="C133" s="67"/>
-      <c r="D133" s="163"/>
-      <c r="E133" s="163"/>
-    </row>
-    <row r="134" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="169" t="s">
-        <v>192</v>
-      </c>
-      <c r="B134" s="69">
-        <v>-668629.54</v>
-      </c>
-      <c r="C134" s="67"/>
-      <c r="D134" s="164"/>
-      <c r="E134" s="164"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="B135" s="70">
-        <f>-B108-B109</f>
-        <v>-15111551.630000001</v>
-      </c>
-      <c r="D135" s="48"/>
-      <c r="E135" s="48"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="B136" s="70">
-        <f>B145</f>
-        <v>432000</v>
-      </c>
-      <c r="D136" s="48"/>
-      <c r="E136" s="48"/>
-      <c r="F136" s="66"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="26" t="s">
+      <c r="F132" s="66"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B137" s="71">
+      <c r="B133" s="71">
         <f>PRORRATEO!F119</f>
         <v>16631233.519999996</v>
       </c>
-      <c r="D137" s="48"/>
-      <c r="E137" s="48"/>
-      <c r="F137" s="66"/>
-    </row>
-    <row r="138" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A138" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="B138" s="146">
+      <c r="D133" s="48"/>
+      <c r="E133" s="48"/>
+      <c r="F133" s="66"/>
+    </row>
+    <row r="134" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A134" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="B134" s="146">
         <v>-95000</v>
       </c>
-      <c r="D138" s="48"/>
-      <c r="E138" s="48"/>
-      <c r="F138" s="66"/>
-    </row>
-    <row r="139" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="72" t="s">
-        <v>162</v>
-      </c>
-      <c r="B139" s="73">
-        <f>SUM(B134:C138)</f>
-        <v>1188052.349999994</v>
-      </c>
-      <c r="D139" s="66"/>
-      <c r="E139" s="50"/>
-      <c r="F139" s="50"/>
-    </row>
-    <row r="140" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="236" t="s">
+      <c r="D134" s="48"/>
+      <c r="E134" s="48"/>
+      <c r="F134" s="66"/>
+    </row>
+    <row r="135" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="72" t="s">
+        <v>160</v>
+      </c>
+      <c r="B135" s="73">
+        <f>SUM(B130:C134)</f>
+        <v>-292026.97000000253</v>
+      </c>
+      <c r="D135" s="66"/>
+      <c r="E135" s="50"/>
+      <c r="F135" s="50"/>
+    </row>
+    <row r="136" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" s="226" t="s">
         <v>125</v>
       </c>
-      <c r="B141" s="236"/>
-      <c r="C141" s="236"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="236"/>
-      <c r="B142" s="236"/>
-      <c r="C142" s="236"/>
-    </row>
-    <row r="143" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="74" t="s">
-        <v>245</v>
-      </c>
-      <c r="B143" s="115">
+      <c r="B137" s="226"/>
+      <c r="C137" s="226"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" s="226"/>
+      <c r="B138" s="226"/>
+      <c r="C138" s="226"/>
+    </row>
+    <row r="139" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="74" t="s">
+        <v>216</v>
+      </c>
+      <c r="B139" s="115">
         <v>300000</v>
       </c>
-      <c r="C143" s="75"/>
-      <c r="D143" s="56"/>
-    </row>
-    <row r="144" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="147" t="s">
-        <v>250</v>
-      </c>
-      <c r="B144" s="115">
+      <c r="C139" s="75"/>
+      <c r="D139" s="56"/>
+    </row>
+    <row r="140" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="147" t="s">
+        <v>221</v>
+      </c>
+      <c r="B140" s="115">
         <v>132000</v>
       </c>
-      <c r="C144" s="75"/>
-      <c r="D144" s="56"/>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A145" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B145" s="77">
-        <f>SUM(B143:B144)</f>
+      <c r="C140" s="75"/>
+      <c r="D140" s="56"/>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B141" s="77">
+        <f>SUM(B139:B140)</f>
         <v>432000</v>
       </c>
-      <c r="C145" s="78"/>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M146" s="79"/>
+      <c r="C141" s="78"/>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M142" s="79"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A141:C142"/>
-    <mergeCell ref="A117:B119"/>
-    <mergeCell ref="A129:B131"/>
-    <mergeCell ref="A125:B127"/>
-    <mergeCell ref="A113:B115"/>
-    <mergeCell ref="A121:B123"/>
+  <mergeCells count="29">
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="E92:E93"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A66:B66"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A75:B75"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
@@ -4007,16 +3974,19 @@
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A74:B74"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A59:B59"/>
     <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A96:B97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A137:C138"/>
+    <mergeCell ref="A113:B115"/>
+    <mergeCell ref="A125:B127"/>
+    <mergeCell ref="A121:B123"/>
+    <mergeCell ref="A109:B111"/>
+    <mergeCell ref="A117:B119"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A92:B93"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4027,53 +3997,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:P127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" customWidth="1"/>
-    <col min="11" max="12" width="12.33203125" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
+    <col min="11" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="93"/>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="239"/>
-      <c r="L1" s="239"/>
-      <c r="M1" s="239"/>
+      <c r="D1" s="256"/>
+      <c r="E1" s="256"/>
+      <c r="F1" s="256"/>
+      <c r="G1" s="256"/>
+      <c r="H1" s="256"/>
+      <c r="I1" s="256"/>
+      <c r="J1" s="256"/>
+      <c r="K1" s="256"/>
+      <c r="L1" s="256"/>
+      <c r="M1" s="256"/>
       <c r="N1" s="95"/>
     </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="96"/>
       <c r="B2" s="97"/>
       <c r="C2" s="98"/>
       <c r="D2" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="263">
+      <c r="E2" s="278">
         <v>3000000</v>
       </c>
-      <c r="F2" s="263"/>
+      <c r="F2" s="278"/>
       <c r="G2" s="98"/>
       <c r="H2" s="98"/>
       <c r="I2" s="98" t="s">
@@ -4091,7 +4061,7 @@
         <v>13312274.1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="102"/>
       <c r="B3" s="103"/>
       <c r="C3" s="103"/>
@@ -4108,228 +4078,228 @@
       <c r="N3" s="106"/>
       <c r="O3" s="80"/>
     </row>
-    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="240" t="s">
-        <v>161</v>
-      </c>
-      <c r="B4" s="241"/>
-      <c r="C4" s="241"/>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="M4" s="241"/>
-      <c r="N4" s="242"/>
+    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="257" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="258"/>
+      <c r="C4" s="258"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+      <c r="M4" s="258"/>
+      <c r="N4" s="259"/>
       <c r="O4" s="80"/>
     </row>
-    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="243"/>
-      <c r="B5" s="244"/>
-      <c r="C5" s="244"/>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="M5" s="244"/>
-      <c r="N5" s="245"/>
+    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="260"/>
+      <c r="B5" s="261"/>
+      <c r="C5" s="261"/>
+      <c r="D5" s="261"/>
+      <c r="E5" s="261"/>
+      <c r="F5" s="261"/>
+      <c r="G5" s="261"/>
+      <c r="H5" s="261"/>
+      <c r="I5" s="261"/>
+      <c r="J5" s="261"/>
+      <c r="K5" s="261"/>
+      <c r="L5" s="261"/>
+      <c r="M5" s="261"/>
+      <c r="N5" s="262"/>
       <c r="O5" s="80"/>
     </row>
-    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="243"/>
-      <c r="B6" s="244"/>
-      <c r="C6" s="244"/>
-      <c r="D6" s="244"/>
-      <c r="E6" s="244"/>
-      <c r="F6" s="244"/>
-      <c r="G6" s="244"/>
-      <c r="H6" s="244"/>
-      <c r="I6" s="244"/>
-      <c r="J6" s="244"/>
-      <c r="K6" s="244"/>
-      <c r="L6" s="244"/>
-      <c r="M6" s="244"/>
-      <c r="N6" s="245"/>
+    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="260"/>
+      <c r="B6" s="261"/>
+      <c r="C6" s="261"/>
+      <c r="D6" s="261"/>
+      <c r="E6" s="261"/>
+      <c r="F6" s="261"/>
+      <c r="G6" s="261"/>
+      <c r="H6" s="261"/>
+      <c r="I6" s="261"/>
+      <c r="J6" s="261"/>
+      <c r="K6" s="261"/>
+      <c r="L6" s="261"/>
+      <c r="M6" s="261"/>
+      <c r="N6" s="262"/>
       <c r="O6" s="80"/>
     </row>
-    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="243"/>
-      <c r="B7" s="244"/>
-      <c r="C7" s="244"/>
-      <c r="D7" s="244"/>
-      <c r="E7" s="244"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="244"/>
-      <c r="H7" s="244"/>
-      <c r="I7" s="244"/>
-      <c r="J7" s="244"/>
-      <c r="K7" s="244"/>
-      <c r="L7" s="244"/>
-      <c r="M7" s="244"/>
-      <c r="N7" s="245"/>
+    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="260"/>
+      <c r="B7" s="261"/>
+      <c r="C7" s="261"/>
+      <c r="D7" s="261"/>
+      <c r="E7" s="261"/>
+      <c r="F7" s="261"/>
+      <c r="G7" s="261"/>
+      <c r="H7" s="261"/>
+      <c r="I7" s="261"/>
+      <c r="J7" s="261"/>
+      <c r="K7" s="261"/>
+      <c r="L7" s="261"/>
+      <c r="M7" s="261"/>
+      <c r="N7" s="262"/>
       <c r="O7" s="80"/>
     </row>
-    <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="246"/>
-      <c r="B8" s="247"/>
-      <c r="C8" s="247"/>
-      <c r="D8" s="247"/>
-      <c r="E8" s="247"/>
-      <c r="F8" s="247"/>
-      <c r="G8" s="247"/>
-      <c r="H8" s="247"/>
-      <c r="I8" s="247"/>
-      <c r="J8" s="247"/>
-      <c r="K8" s="247"/>
-      <c r="L8" s="247"/>
-      <c r="M8" s="247"/>
-      <c r="N8" s="248"/>
-    </row>
-    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="257" t="s">
-        <v>159</v>
-      </c>
-      <c r="B9" s="258"/>
-      <c r="C9" s="258"/>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="258"/>
-      <c r="K9" s="258"/>
-      <c r="L9" s="258"/>
-      <c r="M9" s="258"/>
-      <c r="N9" s="259"/>
-    </row>
-    <row r="10" spans="1:16" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="268" t="s">
-        <v>254</v>
-      </c>
-      <c r="B10" s="269"/>
-      <c r="C10" s="269"/>
-      <c r="D10" s="269"/>
-      <c r="E10" s="269"/>
-      <c r="F10" s="269"/>
-      <c r="G10" s="269"/>
-      <c r="H10" s="269"/>
-      <c r="I10" s="269"/>
-      <c r="J10" s="269"/>
-      <c r="K10" s="269"/>
-      <c r="L10" s="269"/>
-      <c r="M10" s="269"/>
-      <c r="N10" s="270"/>
-    </row>
-    <row r="11" spans="1:16" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="271" t="s">
-        <v>256</v>
-      </c>
-      <c r="B11" s="272"/>
-      <c r="C11" s="272"/>
-      <c r="D11" s="272"/>
-      <c r="E11" s="272"/>
-      <c r="F11" s="272"/>
-      <c r="G11" s="272"/>
-      <c r="H11" s="272"/>
-      <c r="I11" s="272"/>
-      <c r="J11" s="272"/>
-      <c r="K11" s="272"/>
-      <c r="L11" s="272"/>
-      <c r="M11" s="272"/>
-      <c r="N11" s="273"/>
-    </row>
-    <row r="12" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="260" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" s="261"/>
-      <c r="C12" s="261"/>
-      <c r="D12" s="261"/>
-      <c r="E12" s="261"/>
-      <c r="F12" s="261"/>
-      <c r="G12" s="261"/>
-      <c r="H12" s="261"/>
-      <c r="I12" s="261"/>
-      <c r="J12" s="261"/>
-      <c r="K12" s="261"/>
-      <c r="L12" s="261"/>
-      <c r="M12" s="261"/>
-      <c r="N12" s="262"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="249" t="s">
+    <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="263"/>
+      <c r="B8" s="264"/>
+      <c r="C8" s="264"/>
+      <c r="D8" s="264"/>
+      <c r="E8" s="264"/>
+      <c r="F8" s="264"/>
+      <c r="G8" s="264"/>
+      <c r="H8" s="264"/>
+      <c r="I8" s="264"/>
+      <c r="J8" s="264"/>
+      <c r="K8" s="264"/>
+      <c r="L8" s="264"/>
+      <c r="M8" s="264"/>
+      <c r="N8" s="265"/>
+    </row>
+    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="272" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="273"/>
+      <c r="C9" s="273"/>
+      <c r="D9" s="273"/>
+      <c r="E9" s="273"/>
+      <c r="F9" s="273"/>
+      <c r="G9" s="273"/>
+      <c r="H9" s="273"/>
+      <c r="I9" s="273"/>
+      <c r="J9" s="273"/>
+      <c r="K9" s="273"/>
+      <c r="L9" s="273"/>
+      <c r="M9" s="273"/>
+      <c r="N9" s="274"/>
+    </row>
+    <row r="10" spans="1:16" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="247" t="s">
+        <v>225</v>
+      </c>
+      <c r="B10" s="248"/>
+      <c r="C10" s="248"/>
+      <c r="D10" s="248"/>
+      <c r="E10" s="248"/>
+      <c r="F10" s="248"/>
+      <c r="G10" s="248"/>
+      <c r="H10" s="248"/>
+      <c r="I10" s="248"/>
+      <c r="J10" s="248"/>
+      <c r="K10" s="248"/>
+      <c r="L10" s="248"/>
+      <c r="M10" s="248"/>
+      <c r="N10" s="249"/>
+    </row>
+    <row r="11" spans="1:16" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="250" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" s="251"/>
+      <c r="C11" s="251"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
+      <c r="M11" s="251"/>
+      <c r="N11" s="252"/>
+    </row>
+    <row r="12" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="275" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="276"/>
+      <c r="C12" s="276"/>
+      <c r="D12" s="276"/>
+      <c r="E12" s="276"/>
+      <c r="F12" s="276"/>
+      <c r="G12" s="276"/>
+      <c r="H12" s="276"/>
+      <c r="I12" s="276"/>
+      <c r="J12" s="276"/>
+      <c r="K12" s="276"/>
+      <c r="L12" s="276"/>
+      <c r="M12" s="276"/>
+      <c r="N12" s="277"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="266" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="251" t="s">
+      <c r="B13" s="268" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="251" t="s">
+      <c r="C13" s="268" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="251" t="s">
+      <c r="D13" s="268" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="253" t="s">
+      <c r="E13" s="245" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="251" t="s">
+      <c r="F13" s="268" t="s">
         <v>133</v>
       </c>
-      <c r="G13" s="255" t="s">
+      <c r="G13" s="270" t="s">
         <v>134</v>
       </c>
-      <c r="H13" s="253" t="s">
+      <c r="H13" s="245" t="s">
         <v>135</v>
       </c>
-      <c r="I13" s="253" t="s">
+      <c r="I13" s="245" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="253" t="s">
+      <c r="J13" s="245" t="s">
         <v>126</v>
       </c>
-      <c r="K13" s="264" t="s">
-        <v>176</v>
-      </c>
-      <c r="L13" s="266" t="s">
-        <v>182</v>
+      <c r="K13" s="279" t="s">
+        <v>174</v>
+      </c>
+      <c r="L13" s="243" t="s">
+        <v>180</v>
       </c>
       <c r="M13" s="143" t="s">
-        <v>244</v>
-      </c>
-      <c r="N13" s="274" t="s">
+        <v>215</v>
+      </c>
+      <c r="N13" s="253" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="250"/>
-      <c r="B14" s="252"/>
-      <c r="C14" s="252"/>
-      <c r="D14" s="252"/>
-      <c r="E14" s="254"/>
-      <c r="F14" s="252"/>
-      <c r="G14" s="256"/>
-      <c r="H14" s="254"/>
-      <c r="I14" s="254"/>
-      <c r="J14" s="254"/>
-      <c r="K14" s="265"/>
-      <c r="L14" s="267"/>
+    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="267"/>
+      <c r="B14" s="269"/>
+      <c r="C14" s="269"/>
+      <c r="D14" s="269"/>
+      <c r="E14" s="246"/>
+      <c r="F14" s="269"/>
+      <c r="G14" s="271"/>
+      <c r="H14" s="246"/>
+      <c r="I14" s="246"/>
+      <c r="J14" s="246"/>
+      <c r="K14" s="280"/>
+      <c r="L14" s="244"/>
       <c r="M14" s="144" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="N14" s="275"/>
-    </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N14" s="254"/>
+    </row>
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="129">
         <v>1</v>
       </c>
@@ -4377,7 +4347,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="188">
         <v>2</v>
       </c>
@@ -4423,10 +4393,10 @@
         <v>0.02</v>
       </c>
       <c r="P16" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="129">
         <v>3</v>
       </c>
@@ -4475,7 +4445,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="130">
         <v>4</v>
       </c>
@@ -4524,7 +4494,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="129">
         <v>5</v>
       </c>
@@ -4572,7 +4542,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="129">
         <v>6</v>
       </c>
@@ -4620,7 +4590,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="129">
         <v>7</v>
       </c>
@@ -4669,7 +4639,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="129">
         <v>8</v>
       </c>
@@ -4718,7 +4688,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="129">
         <v>9</v>
       </c>
@@ -4766,7 +4736,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="129">
         <v>10</v>
       </c>
@@ -4814,7 +4784,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="129">
         <v>11</v>
       </c>
@@ -4863,7 +4833,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="188">
         <v>12</v>
       </c>
@@ -4911,7 +4881,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="129">
         <v>13</v>
       </c>
@@ -4960,7 +4930,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="129">
         <v>14</v>
       </c>
@@ -5006,7 +4976,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="130">
         <v>15</v>
       </c>
@@ -5055,7 +5025,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="129">
         <v>16</v>
       </c>
@@ -5104,7 +5074,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="129">
         <v>17</v>
       </c>
@@ -5152,7 +5122,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="130">
         <v>18</v>
       </c>
@@ -5201,7 +5171,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="130">
         <v>19</v>
       </c>
@@ -5249,10 +5219,10 @@
         <v>0.19000000000000003</v>
       </c>
       <c r="P33" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="131">
         <v>20</v>
       </c>
@@ -5299,10 +5269,10 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="P34" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="130">
         <v>21</v>
       </c>
@@ -5351,13 +5321,13 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="130">
         <f>A35+1</f>
         <v>22</v>
       </c>
       <c r="B36" s="114" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C36" s="87"/>
       <c r="D36" s="82">
@@ -5401,7 +5371,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="129">
         <f t="shared" ref="A37:A100" si="9">A36+1</f>
         <v>23</v>
@@ -5451,7 +5421,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="129">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -5500,7 +5470,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="129">
         <f t="shared" si="9"/>
         <v>25</v>
@@ -5550,7 +5520,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="129">
         <f t="shared" si="9"/>
         <v>26</v>
@@ -5600,7 +5570,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="129">
         <f t="shared" si="9"/>
         <v>27</v>
@@ -5650,7 +5620,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="129">
         <f t="shared" si="9"/>
         <v>28</v>
@@ -5697,7 +5667,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="130">
         <f t="shared" si="9"/>
         <v>29</v>
@@ -5747,10 +5717,10 @@
         <v>0.29000000000000009</v>
       </c>
       <c r="P43" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="130">
         <f t="shared" si="9"/>
         <v>30</v>
@@ -5800,7 +5770,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="129">
         <f t="shared" si="9"/>
         <v>31</v>
@@ -5850,7 +5820,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="129">
         <f t="shared" si="9"/>
         <v>32</v>
@@ -5899,7 +5869,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="131">
         <f t="shared" si="9"/>
         <v>33</v>
@@ -5948,10 +5918,10 @@
         <v>0.33000000000000013</v>
       </c>
       <c r="P47" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="129">
         <f t="shared" si="9"/>
         <v>34</v>
@@ -6001,7 +5971,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="193">
         <f t="shared" si="9"/>
         <v>35</v>
@@ -6051,10 +6021,10 @@
         <v>0.35000000000000014</v>
       </c>
       <c r="P49" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="129">
         <f t="shared" si="9"/>
         <v>36</v>
@@ -6104,10 +6074,10 @@
         <v>0.36000000000000015</v>
       </c>
       <c r="P50" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="129">
         <f t="shared" si="9"/>
         <v>37</v>
@@ -6156,10 +6126,10 @@
         <v>0.37000000000000016</v>
       </c>
       <c r="P51" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="129">
         <f t="shared" si="9"/>
         <v>38</v>
@@ -6206,10 +6176,10 @@
         <v>0.38000000000000017</v>
       </c>
       <c r="P52" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="129">
         <f t="shared" si="9"/>
         <v>39</v>
@@ -6259,7 +6229,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="129">
         <f t="shared" si="9"/>
         <v>40</v>
@@ -6309,7 +6279,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="129">
         <f t="shared" si="9"/>
         <v>41</v>
@@ -6358,7 +6328,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="131">
         <f t="shared" si="9"/>
         <v>42</v>
@@ -6407,10 +6377,10 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="P56" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="131">
         <f t="shared" si="9"/>
         <v>43</v>
@@ -6462,10 +6432,10 @@
         <v>0.43000000000000022</v>
       </c>
       <c r="P57" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="130">
         <f t="shared" si="9"/>
         <v>44</v>
@@ -6515,16 +6485,16 @@
         <v>0.44000000000000022</v>
       </c>
       <c r="P58" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="130">
         <f t="shared" si="9"/>
         <v>45</v>
       </c>
       <c r="B59" s="114" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C59" s="113"/>
       <c r="D59" s="110">
@@ -6568,7 +6538,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="217">
         <f t="shared" si="9"/>
         <v>46</v>
@@ -6617,10 +6587,10 @@
         <v>0.46000000000000024</v>
       </c>
       <c r="P60" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="131">
         <f t="shared" si="9"/>
         <v>47</v>
@@ -6668,10 +6638,10 @@
         <v>0.47000000000000025</v>
       </c>
       <c r="P61" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="130">
         <f t="shared" si="9"/>
         <v>48</v>
@@ -6721,10 +6691,10 @@
         <v>0.48000000000000026</v>
       </c>
       <c r="P62" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="130">
         <f t="shared" si="9"/>
         <v>49</v>
@@ -6774,7 +6744,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="130">
         <f t="shared" si="9"/>
         <v>50</v>
@@ -6824,7 +6794,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="130">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6874,7 +6844,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="130">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -6924,7 +6894,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="130">
         <f t="shared" si="9"/>
         <v>53</v>
@@ -6974,7 +6944,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="130">
         <f t="shared" si="9"/>
         <v>54</v>
@@ -7023,7 +6993,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="130">
         <f t="shared" si="9"/>
         <v>55</v>
@@ -7072,7 +7042,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="130">
         <f t="shared" si="9"/>
         <v>56</v>
@@ -7121,7 +7091,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="130">
         <f t="shared" si="9"/>
         <v>57</v>
@@ -7171,7 +7141,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="130">
         <f t="shared" si="9"/>
         <v>58</v>
@@ -7221,10 +7191,10 @@
         <v>0.58000000000000029</v>
       </c>
       <c r="P72" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="130">
         <f t="shared" si="9"/>
         <v>59</v>
@@ -7273,7 +7243,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="130">
         <f t="shared" si="9"/>
         <v>60</v>
@@ -7322,7 +7292,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="130">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -7372,7 +7342,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="130">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -7421,7 +7391,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="130">
         <f t="shared" si="9"/>
         <v>63</v>
@@ -7471,10 +7441,10 @@
         <v>0.63000000000000034</v>
       </c>
       <c r="P77" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="130">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -7523,7 +7493,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="130">
         <f t="shared" si="9"/>
         <v>65</v>
@@ -7572,10 +7542,10 @@
         <v>0.65000000000000036</v>
       </c>
       <c r="P79" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="190">
         <f t="shared" si="9"/>
         <v>66</v>
@@ -7624,7 +7594,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="130">
         <f t="shared" si="9"/>
         <v>67</v>
@@ -7673,7 +7643,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="188">
         <f t="shared" si="9"/>
         <v>68</v>
@@ -7724,7 +7694,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="130">
         <f t="shared" si="9"/>
         <v>69</v>
@@ -7759,7 +7729,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K83" s="125" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L83" s="148"/>
       <c r="M83" s="86">
@@ -7775,7 +7745,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="130">
         <f t="shared" si="9"/>
         <v>70</v>
@@ -7825,10 +7795,10 @@
         <v>0.7000000000000004</v>
       </c>
       <c r="P84" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="130">
         <f t="shared" si="9"/>
         <v>71</v>
@@ -7878,7 +7848,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="130">
         <f t="shared" si="9"/>
         <v>72</v>
@@ -7928,7 +7898,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="130">
         <f t="shared" si="9"/>
         <v>73</v>
@@ -7978,7 +7948,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="129">
         <f t="shared" si="9"/>
         <v>74</v>
@@ -8027,7 +7997,7 @@
         <v>0.74000000000000044</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="129">
         <f t="shared" si="9"/>
         <v>75</v>
@@ -8077,7 +8047,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="129">
         <f t="shared" si="9"/>
         <v>76</v>
@@ -8127,7 +8097,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="129">
         <f t="shared" si="9"/>
         <v>77</v>
@@ -8177,7 +8147,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="131">
         <f t="shared" si="9"/>
         <v>78</v>
@@ -8226,16 +8196,16 @@
         <v>0.78000000000000047</v>
       </c>
       <c r="P92" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="129">
         <f t="shared" si="9"/>
         <v>79</v>
       </c>
       <c r="B93" s="88" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C93" s="87"/>
       <c r="D93" s="82">
@@ -8279,10 +8249,10 @@
         <v>0.79000000000000048</v>
       </c>
       <c r="P93" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="130">
         <f t="shared" si="9"/>
         <v>80</v>
@@ -8332,7 +8302,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="130">
         <f t="shared" si="9"/>
         <v>81</v>
@@ -8382,10 +8352,10 @@
         <v>0.8100000000000005</v>
       </c>
       <c r="P95" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="130">
         <f t="shared" si="9"/>
         <v>82</v>
@@ -8434,7 +8404,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="130">
         <f t="shared" si="9"/>
         <v>83</v>
@@ -8484,7 +8454,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="130">
         <f t="shared" si="9"/>
         <v>84</v>
@@ -8531,7 +8501,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="129">
         <f t="shared" si="9"/>
         <v>85</v>
@@ -8581,7 +8551,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="190">
         <f t="shared" si="9"/>
         <v>86</v>
@@ -8631,7 +8601,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="129">
         <f t="shared" ref="A101:A117" si="23">A100+1</f>
         <v>87</v>
@@ -8681,7 +8651,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="129">
         <f t="shared" si="23"/>
         <v>88</v>
@@ -8731,7 +8701,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="129">
         <f t="shared" si="23"/>
         <v>89</v>
@@ -8781,7 +8751,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="129">
         <f t="shared" si="23"/>
         <v>90</v>
@@ -8831,7 +8801,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="129">
         <f t="shared" si="23"/>
         <v>91</v>
@@ -8880,7 +8850,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="129">
         <f t="shared" si="23"/>
         <v>92</v>
@@ -8929,7 +8899,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="130">
         <f t="shared" si="23"/>
         <v>93</v>
@@ -8978,7 +8948,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="130">
         <f t="shared" si="23"/>
         <v>94</v>
@@ -9028,13 +8998,13 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="130">
         <f t="shared" si="23"/>
         <v>95</v>
       </c>
       <c r="B109" s="114" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C109" s="113"/>
       <c r="D109" s="110">
@@ -9078,7 +9048,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="130">
         <f t="shared" si="23"/>
         <v>96</v>
@@ -9127,10 +9097,10 @@
         <v>0.96000000000000063</v>
       </c>
       <c r="P110" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="130">
         <f t="shared" si="23"/>
         <v>97</v>
@@ -9180,7 +9150,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="130">
         <f t="shared" si="23"/>
         <v>98</v>
@@ -9230,7 +9200,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="130">
         <f t="shared" si="23"/>
         <v>99</v>
@@ -9280,7 +9250,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="130">
         <f t="shared" si="23"/>
         <v>100</v>
@@ -9327,7 +9297,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="130">
         <f t="shared" si="23"/>
         <v>101</v>
@@ -9376,7 +9346,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="130">
         <f t="shared" si="23"/>
         <v>102</v>
@@ -9426,13 +9396,13 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="130">
         <f t="shared" si="23"/>
         <v>103</v>
       </c>
       <c r="B117" s="114" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C117" s="113"/>
       <c r="D117" s="110">
@@ -9476,7 +9446,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="130"/>
       <c r="B118" s="108"/>
       <c r="C118" s="113"/>
@@ -9493,7 +9463,7 @@
       <c r="N118" s="140"/>
       <c r="O118" s="50"/>
     </row>
-    <row r="119" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="132"/>
       <c r="B119" s="133"/>
       <c r="C119" s="133"/>
@@ -9536,104 +9506,99 @@
         <v>40891254.560000002</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="89"/>
       <c r="C120" s="89"/>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="122" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="238" t="s">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="255" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="238"/>
-      <c r="D122" s="238"/>
-      <c r="E122" s="238"/>
-      <c r="F122" s="238"/>
-      <c r="G122" s="238"/>
-      <c r="H122" s="238"/>
-      <c r="I122" s="238"/>
-      <c r="J122" s="238"/>
-      <c r="K122" s="238"/>
-      <c r="L122" s="238"/>
-      <c r="M122" s="238"/>
-    </row>
-    <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="238"/>
-      <c r="C123" s="238"/>
-      <c r="D123" s="238"/>
-      <c r="E123" s="238"/>
-      <c r="F123" s="238"/>
-      <c r="G123" s="238"/>
-      <c r="H123" s="238"/>
-      <c r="I123" s="238"/>
-      <c r="J123" s="238"/>
-      <c r="K123" s="238"/>
-      <c r="L123" s="238"/>
-      <c r="M123" s="238"/>
-    </row>
-    <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="238"/>
-      <c r="C124" s="238"/>
-      <c r="D124" s="238"/>
-      <c r="E124" s="238"/>
-      <c r="F124" s="238"/>
-      <c r="G124" s="238"/>
-      <c r="H124" s="238"/>
-      <c r="I124" s="238"/>
-      <c r="J124" s="238"/>
-      <c r="K124" s="238"/>
-      <c r="L124" s="238"/>
-      <c r="M124" s="238"/>
-    </row>
-    <row r="125" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="238"/>
-      <c r="C125" s="238"/>
-      <c r="D125" s="238"/>
-      <c r="E125" s="238"/>
-      <c r="F125" s="238"/>
-      <c r="G125" s="238"/>
-      <c r="H125" s="238"/>
-      <c r="I125" s="238"/>
-      <c r="J125" s="238"/>
-      <c r="K125" s="238"/>
-      <c r="L125" s="238"/>
-      <c r="M125" s="238"/>
-    </row>
-    <row r="126" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="238"/>
-      <c r="C126" s="238"/>
-      <c r="D126" s="238"/>
-      <c r="E126" s="238"/>
-      <c r="F126" s="238"/>
-      <c r="G126" s="238"/>
-      <c r="H126" s="238"/>
-      <c r="I126" s="238"/>
-      <c r="J126" s="238"/>
-      <c r="K126" s="238"/>
-      <c r="L126" s="238"/>
-      <c r="M126" s="238"/>
-    </row>
-    <row r="127" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="238"/>
-      <c r="C127" s="238"/>
-      <c r="D127" s="238"/>
-      <c r="E127" s="238"/>
-      <c r="F127" s="238"/>
-      <c r="G127" s="238"/>
-      <c r="H127" s="238"/>
-      <c r="I127" s="238"/>
-      <c r="J127" s="238"/>
-      <c r="K127" s="238"/>
-      <c r="L127" s="238"/>
-      <c r="M127" s="238"/>
+      <c r="C122" s="255"/>
+      <c r="D122" s="255"/>
+      <c r="E122" s="255"/>
+      <c r="F122" s="255"/>
+      <c r="G122" s="255"/>
+      <c r="H122" s="255"/>
+      <c r="I122" s="255"/>
+      <c r="J122" s="255"/>
+      <c r="K122" s="255"/>
+      <c r="L122" s="255"/>
+      <c r="M122" s="255"/>
+    </row>
+    <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="255"/>
+      <c r="C123" s="255"/>
+      <c r="D123" s="255"/>
+      <c r="E123" s="255"/>
+      <c r="F123" s="255"/>
+      <c r="G123" s="255"/>
+      <c r="H123" s="255"/>
+      <c r="I123" s="255"/>
+      <c r="J123" s="255"/>
+      <c r="K123" s="255"/>
+      <c r="L123" s="255"/>
+      <c r="M123" s="255"/>
+    </row>
+    <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="255"/>
+      <c r="C124" s="255"/>
+      <c r="D124" s="255"/>
+      <c r="E124" s="255"/>
+      <c r="F124" s="255"/>
+      <c r="G124" s="255"/>
+      <c r="H124" s="255"/>
+      <c r="I124" s="255"/>
+      <c r="J124" s="255"/>
+      <c r="K124" s="255"/>
+      <c r="L124" s="255"/>
+      <c r="M124" s="255"/>
+    </row>
+    <row r="125" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="255"/>
+      <c r="C125" s="255"/>
+      <c r="D125" s="255"/>
+      <c r="E125" s="255"/>
+      <c r="F125" s="255"/>
+      <c r="G125" s="255"/>
+      <c r="H125" s="255"/>
+      <c r="I125" s="255"/>
+      <c r="J125" s="255"/>
+      <c r="K125" s="255"/>
+      <c r="L125" s="255"/>
+      <c r="M125" s="255"/>
+    </row>
+    <row r="126" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="255"/>
+      <c r="C126" s="255"/>
+      <c r="D126" s="255"/>
+      <c r="E126" s="255"/>
+      <c r="F126" s="255"/>
+      <c r="G126" s="255"/>
+      <c r="H126" s="255"/>
+      <c r="I126" s="255"/>
+      <c r="J126" s="255"/>
+      <c r="K126" s="255"/>
+      <c r="L126" s="255"/>
+      <c r="M126" s="255"/>
+    </row>
+    <row r="127" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="255"/>
+      <c r="C127" s="255"/>
+      <c r="D127" s="255"/>
+      <c r="E127" s="255"/>
+      <c r="F127" s="255"/>
+      <c r="G127" s="255"/>
+      <c r="H127" s="255"/>
+      <c r="I127" s="255"/>
+      <c r="J127" s="255"/>
+      <c r="K127" s="255"/>
+      <c r="L127" s="255"/>
+      <c r="M127" s="255"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="N13:N14"/>
     <mergeCell ref="B122:M127"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="A4:N8"/>
@@ -9650,6 +9615,11 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="N13:N14"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="80" orientation="portrait" r:id="rId1"/>
@@ -9659,18 +9629,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
   <dimension ref="C3:N9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="19"/>
     </row>
-    <row r="4" spans="3:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:14" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="173" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D4" s="174">
         <v>1</v>
@@ -9684,16 +9654,16 @@
       <c r="K4" s="19"/>
       <c r="L4" s="19"/>
     </row>
-    <row r="5" spans="3:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="175" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D5" s="176"/>
       <c r="E5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J5" s="172"/>
       <c r="K5" s="19"/>
@@ -9701,15 +9671,15 @@
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C6" s="175" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D6" s="176" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G6" t="s">
         <v>128</v>
@@ -9723,9 +9693,9 @@
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
     </row>
-    <row r="7" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="47" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J7" s="172"/>
       <c r="K7" s="19"/>
@@ -9733,31 +9703,31 @@
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
     </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C8" s="276" t="s">
-        <v>257</v>
-      </c>
-      <c r="D8" s="277"/>
-      <c r="E8" s="277"/>
-      <c r="F8" s="277"/>
-      <c r="G8" s="277"/>
-      <c r="H8" s="277"/>
-      <c r="I8" s="277"/>
-      <c r="J8" s="278"/>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C8" s="281" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="282"/>
+      <c r="E8" s="282"/>
+      <c r="F8" s="282"/>
+      <c r="G8" s="282"/>
+      <c r="H8" s="282"/>
+      <c r="I8" s="282"/>
+      <c r="J8" s="283"/>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
     </row>
-    <row r="9" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="279"/>
-      <c r="D9" s="280"/>
-      <c r="E9" s="280"/>
-      <c r="F9" s="280"/>
-      <c r="G9" s="280"/>
-      <c r="H9" s="280"/>
-      <c r="I9" s="280"/>
-      <c r="J9" s="281"/>
+    <row r="9" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="284"/>
+      <c r="D9" s="285"/>
+      <c r="E9" s="285"/>
+      <c r="F9" s="285"/>
+      <c r="G9" s="285"/>
+      <c r="H9" s="285"/>
+      <c r="I9" s="285"/>
+      <c r="J9" s="286"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>

--- a/2026/ITALIA/Julio/Julio ITALIA.xlsx
+++ b/2026/ITALIA/Julio/Julio ITALIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6349677D-3890-4B38-BEDC-54603BA5EAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158EB0E9-9084-4777-AD9C-496D2BC4C1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2007,195 +2007,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2223,11 +2034,200 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="10" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2651,12 +2651,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="226" t="s">
+      <c r="B1" s="237" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="226"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="227"/>
+      <c r="C1" s="237"/>
+      <c r="D1" s="237"/>
+      <c r="E1" s="238"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -2669,12 +2669,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="230" t="s">
+      <c r="B3" s="243" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="230"/>
-      <c r="D3" s="230"/>
-      <c r="E3" s="231"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="244"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -2713,24 +2713,24 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="48"/>
-      <c r="B8" s="232" t="s">
+      <c r="B8" s="245" t="s">
         <v>221</v>
       </c>
-      <c r="C8" s="232"/>
+      <c r="C8" s="245"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="48"/>
-      <c r="B9" s="232"/>
-      <c r="C9" s="232"/>
+      <c r="B9" s="245"/>
+      <c r="C9" s="245"/>
       <c r="D9" s="48"/>
       <c r="E9" s="48"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="48"/>
-      <c r="B10" s="232"/>
-      <c r="C10" s="232"/>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
     </row>
@@ -2749,34 +2749,34 @@
       <c r="E12" s="48"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="233" t="s">
+      <c r="A13" s="246" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="233"/>
-      <c r="C13" s="233"/>
-      <c r="D13" s="233"/>
-      <c r="E13" s="233"/>
+      <c r="B13" s="246"/>
+      <c r="C13" s="246"/>
+      <c r="D13" s="246"/>
+      <c r="E13" s="246"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="233"/>
-      <c r="B14" s="233"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="233"/>
-      <c r="E14" s="233"/>
+      <c r="A14" s="246"/>
+      <c r="B14" s="246"/>
+      <c r="C14" s="246"/>
+      <c r="D14" s="246"/>
+      <c r="E14" s="246"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="233"/>
-      <c r="B15" s="233"/>
-      <c r="C15" s="233"/>
-      <c r="D15" s="233"/>
-      <c r="E15" s="233"/>
+      <c r="A15" s="246"/>
+      <c r="B15" s="246"/>
+      <c r="C15" s="246"/>
+      <c r="D15" s="246"/>
+      <c r="E15" s="246"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="233"/>
-      <c r="B16" s="233"/>
-      <c r="C16" s="233"/>
-      <c r="D16" s="233"/>
-      <c r="E16" s="233"/>
+      <c r="A16" s="246"/>
+      <c r="B16" s="246"/>
+      <c r="C16" s="246"/>
+      <c r="D16" s="246"/>
+      <c r="E16" s="246"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48"/>
@@ -2818,10 +2818,10 @@
       <c r="E21" s="151"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="228" t="s">
+      <c r="A22" s="239" t="s">
         <v>161</v>
       </c>
-      <c r="B22" s="229"/>
+      <c r="B22" s="240"/>
       <c r="C22" s="181"/>
       <c r="D22" s="182">
         <v>2337709.7000000002</v>
@@ -2830,10 +2830,10 @@
       <c r="H22" s="19"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="228" t="s">
+      <c r="A23" s="239" t="s">
         <v>162</v>
       </c>
-      <c r="B23" s="229"/>
+      <c r="B23" s="240"/>
       <c r="C23" s="181"/>
       <c r="D23" s="182">
         <v>-508451.7</v>
@@ -2842,10 +2842,10 @@
       <c r="H23" s="19"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="228" t="s">
+      <c r="A24" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="229"/>
+      <c r="B24" s="240"/>
       <c r="C24" s="181"/>
       <c r="D24" s="183">
         <v>0</v>
@@ -2853,7 +2853,7 @@
       <c r="E24" s="20">
         <v>248436.1</v>
       </c>
-      <c r="F24" s="282">
+      <c r="F24" s="219">
         <v>241200.1</v>
       </c>
       <c r="H24" s="19"/>
@@ -3057,12 +3057,12 @@
       <c r="E42" s="156"/>
     </row>
     <row r="43" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="222" t="s">
+      <c r="A43" s="247" t="s">
         <v>183</v>
       </c>
-      <c r="B43" s="223"/>
+      <c r="B43" s="248"/>
       <c r="C43" s="26"/>
-      <c r="D43" s="294">
+      <c r="D43" s="231">
         <v>7805</v>
       </c>
       <c r="E43" s="20" t="s">
@@ -3070,12 +3070,12 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="222" t="s">
+      <c r="A44" s="247" t="s">
         <v>185</v>
       </c>
-      <c r="B44" s="223"/>
+      <c r="B44" s="248"/>
       <c r="C44" s="26"/>
-      <c r="D44" s="294">
+      <c r="D44" s="231">
         <v>213891</v>
       </c>
       <c r="E44" s="20" t="s">
@@ -3158,10 +3158,10 @@
       <c r="E50" s="20"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="222" t="s">
+      <c r="A51" s="247" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="223"/>
+      <c r="B51" s="248"/>
       <c r="C51" s="29"/>
       <c r="D51" s="30">
         <v>5946930.7699999996</v>
@@ -3203,10 +3203,10 @@
       <c r="E54" s="159"/>
     </row>
     <row r="55" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="224" t="s">
+      <c r="A55" s="241" t="s">
         <v>164</v>
       </c>
-      <c r="B55" s="225"/>
+      <c r="B55" s="242"/>
       <c r="C55" s="29"/>
       <c r="D55" s="30">
         <v>285000</v>
@@ -3216,10 +3216,10 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="224" t="s">
+      <c r="A56" s="241" t="s">
         <v>250</v>
       </c>
-      <c r="B56" s="225"/>
+      <c r="B56" s="242"/>
       <c r="C56" s="29"/>
       <c r="D56" s="30">
         <v>280000</v>
@@ -3229,10 +3229,10 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="224" t="s">
+      <c r="A57" s="241" t="s">
         <v>237</v>
       </c>
-      <c r="B57" s="225"/>
+      <c r="B57" s="242"/>
       <c r="C57" s="29"/>
       <c r="D57" s="30">
         <v>1400000</v>
@@ -3258,10 +3258,10 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="224" t="s">
+      <c r="A59" s="241" t="s">
         <v>240</v>
       </c>
-      <c r="B59" s="225"/>
+      <c r="B59" s="242"/>
       <c r="C59" s="29"/>
       <c r="D59" s="30">
         <v>687000</v>
@@ -3281,7 +3281,7 @@
         <v>6990</v>
       </c>
       <c r="E60" s="34"/>
-      <c r="F60" s="283"/>
+      <c r="F60" s="220"/>
     </row>
     <row r="61" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="92" t="s">
@@ -3354,10 +3354,10 @@
       <c r="F65" s="50"/>
     </row>
     <row r="66" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="224" t="s">
+      <c r="A66" s="241" t="s">
         <v>247</v>
       </c>
-      <c r="B66" s="225"/>
+      <c r="B66" s="242"/>
       <c r="C66" s="29"/>
       <c r="D66" s="30">
         <v>138600</v>
@@ -3410,10 +3410,10 @@
       <c r="F69" s="50"/>
     </row>
     <row r="70" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="224" t="s">
+      <c r="A70" s="241" t="s">
         <v>265</v>
       </c>
-      <c r="B70" s="225"/>
+      <c r="B70" s="242"/>
       <c r="C70" s="29"/>
       <c r="D70" s="30">
         <v>85000</v>
@@ -3436,10 +3436,10 @@
       <c r="F71" s="50"/>
     </row>
     <row r="72" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="224" t="s">
+      <c r="A72" s="241" t="s">
         <v>208</v>
       </c>
-      <c r="B72" s="225"/>
+      <c r="B72" s="242"/>
       <c r="C72" s="29"/>
       <c r="D72" s="30">
         <v>124611.12</v>
@@ -3450,10 +3450,10 @@
       <c r="F72" s="50"/>
     </row>
     <row r="73" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="224" t="s">
+      <c r="A73" s="241" t="s">
         <v>223</v>
       </c>
-      <c r="B73" s="225"/>
+      <c r="B73" s="242"/>
       <c r="C73" s="29"/>
       <c r="D73" s="30">
         <v>124611.12</v>
@@ -3485,12 +3485,12 @@
       <c r="E75" s="151"/>
     </row>
     <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="224" t="s">
+      <c r="A76" s="241" t="s">
         <v>224</v>
       </c>
-      <c r="B76" s="225"/>
+      <c r="B76" s="242"/>
       <c r="C76" s="18"/>
-      <c r="D76" s="295">
+      <c r="D76" s="232">
         <v>650000</v>
       </c>
       <c r="E76" s="166" t="s">
@@ -3501,12 +3501,12 @@
       </c>
     </row>
     <row r="77" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="224" t="s">
+      <c r="A77" s="241" t="s">
         <v>235</v>
       </c>
-      <c r="B77" s="225"/>
+      <c r="B77" s="242"/>
       <c r="C77" s="18"/>
-      <c r="D77" s="296">
+      <c r="D77" s="233">
         <v>50000</v>
       </c>
       <c r="E77" s="166" t="s">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="B78" s="17"/>
       <c r="C78" s="18"/>
-      <c r="D78" s="296">
+      <c r="D78" s="233">
         <v>250000</v>
       </c>
       <c r="E78" s="166" t="s">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="B79" s="17"/>
       <c r="C79" s="18"/>
-      <c r="D79" s="296">
+      <c r="D79" s="233">
         <v>484217.8</v>
       </c>
       <c r="E79" s="166" t="s">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="B80" s="17"/>
       <c r="C80" s="18"/>
-      <c r="D80" s="296">
+      <c r="D80" s="233">
         <v>50000</v>
       </c>
       <c r="E80" s="166" t="s">
@@ -3579,19 +3579,19 @@
       </c>
       <c r="B83" s="91"/>
       <c r="C83" s="91"/>
-      <c r="D83" s="297">
+      <c r="D83" s="234">
         <f>44612.24+65000-12214.52</f>
         <v>97397.719999999987</v>
       </c>
       <c r="E83" s="160"/>
     </row>
     <row r="84" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="222" t="s">
+      <c r="A84" s="247" t="s">
         <v>251</v>
       </c>
-      <c r="B84" s="223"/>
+      <c r="B84" s="248"/>
       <c r="C84" s="91"/>
-      <c r="D84" s="297">
+      <c r="D84" s="234">
         <v>225591.15</v>
       </c>
       <c r="E84" s="160"/>
@@ -3665,18 +3665,18 @@
       <c r="E92" s="59"/>
     </row>
     <row r="93" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="236"/>
-      <c r="B93" s="236"/>
+      <c r="A93" s="253"/>
+      <c r="B93" s="253"/>
       <c r="C93" s="31"/>
-      <c r="D93" s="218"/>
-      <c r="E93" s="220"/>
+      <c r="D93" s="249"/>
+      <c r="E93" s="251"/>
     </row>
     <row r="94" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="236"/>
-      <c r="B94" s="236"/>
+      <c r="A94" s="253"/>
+      <c r="B94" s="253"/>
       <c r="C94" s="31"/>
-      <c r="D94" s="219"/>
-      <c r="E94" s="221"/>
+      <c r="D94" s="250"/>
+      <c r="E94" s="252"/>
     </row>
     <row r="95" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="29"/>
@@ -3719,7 +3719,7 @@
       <c r="C100" s="44"/>
       <c r="D100" s="45"/>
       <c r="E100" s="165">
-        <v>3000000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3735,7 +3735,7 @@
       <c r="D102" s="54"/>
       <c r="E102" s="55">
         <f>E97+E100</f>
-        <v>3000000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="B107" s="65">
         <f>E102</f>
-        <v>3000000</v>
+        <v>4500000</v>
       </c>
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
@@ -3795,22 +3795,22 @@
       <c r="E109" s="48"/>
     </row>
     <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="235" t="s">
+      <c r="A110" s="236" t="s">
         <v>172</v>
       </c>
-      <c r="B110" s="235"/>
+      <c r="B110" s="236"/>
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
     </row>
     <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="235"/>
-      <c r="B111" s="235"/>
+      <c r="A111" s="236"/>
+      <c r="B111" s="236"/>
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
     </row>
     <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="235"/>
-      <c r="B112" s="235"/>
+      <c r="A112" s="236"/>
+      <c r="B112" s="236"/>
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
     </row>
@@ -3819,47 +3819,47 @@
       <c r="E113" s="48"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="235" t="s">
+      <c r="A114" s="236" t="s">
         <v>199</v>
       </c>
-      <c r="B114" s="235"/>
+      <c r="B114" s="236"/>
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
     <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="235"/>
-      <c r="B115" s="235"/>
+      <c r="A115" s="236"/>
+      <c r="B115" s="236"/>
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
     <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="235"/>
-      <c r="B116" s="235"/>
+      <c r="A116" s="236"/>
+      <c r="B116" s="236"/>
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
     </row>
     <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
-      <c r="F117" s="282"/>
+      <c r="F117" s="219"/>
     </row>
     <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="235" t="s">
+      <c r="A118" s="236" t="s">
         <v>179</v>
       </c>
-      <c r="B118" s="235"/>
+      <c r="B118" s="236"/>
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
     </row>
     <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="235"/>
-      <c r="B119" s="235"/>
+      <c r="A119" s="236"/>
+      <c r="B119" s="236"/>
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
     <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="235"/>
-      <c r="B120" s="235"/>
+      <c r="A120" s="236"/>
+      <c r="B120" s="236"/>
       <c r="D120" s="48"/>
       <c r="E120" s="48"/>
     </row>
@@ -3868,22 +3868,22 @@
       <c r="E121" s="48"/>
     </row>
     <row r="122" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="235" t="s">
+      <c r="A122" s="236" t="s">
         <v>182</v>
       </c>
-      <c r="B122" s="235"/>
+      <c r="B122" s="236"/>
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
     </row>
     <row r="123" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="235"/>
-      <c r="B123" s="235"/>
+      <c r="A123" s="236"/>
+      <c r="B123" s="236"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
     </row>
     <row r="124" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="235"/>
-      <c r="B124" s="235"/>
+      <c r="A124" s="236"/>
+      <c r="B124" s="236"/>
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
     </row>
@@ -3892,22 +3892,22 @@
       <c r="E125" s="48"/>
     </row>
     <row r="126" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="235" t="s">
+      <c r="A126" s="236" t="s">
         <v>181</v>
       </c>
-      <c r="B126" s="235"/>
+      <c r="B126" s="236"/>
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
     </row>
     <row r="127" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="235"/>
-      <c r="B127" s="235"/>
+      <c r="A127" s="236"/>
+      <c r="B127" s="236"/>
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="235"/>
-      <c r="B128" s="235"/>
+      <c r="A128" s="236"/>
+      <c r="B128" s="236"/>
       <c r="D128" s="48"/>
       <c r="E128" s="48"/>
     </row>
@@ -4004,16 +4004,16 @@
     </row>
     <row r="138" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="234" t="s">
+      <c r="A139" s="235" t="s">
         <v>125</v>
       </c>
-      <c r="B139" s="234"/>
-      <c r="C139" s="234"/>
+      <c r="B139" s="235"/>
+      <c r="C139" s="235"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="234"/>
-      <c r="B140" s="234"/>
-      <c r="C140" s="234"/>
+      <c r="A140" s="235"/>
+      <c r="B140" s="235"/>
+      <c r="C140" s="235"/>
     </row>
     <row r="141" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="74" t="s">
@@ -4060,12 +4060,14 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A139:C140"/>
-    <mergeCell ref="A114:B116"/>
-    <mergeCell ref="A126:B128"/>
-    <mergeCell ref="A122:B124"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="A118:B120"/>
+    <mergeCell ref="D93:D94"/>
+    <mergeCell ref="E93:E94"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A93:B94"/>
+    <mergeCell ref="A70:B70"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A76:B76"/>
@@ -4082,14 +4084,12 @@
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="A72:B72"/>
-    <mergeCell ref="D93:D94"/>
-    <mergeCell ref="E93:E94"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A93:B94"/>
-    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A139:C140"/>
+    <mergeCell ref="A114:B116"/>
+    <mergeCell ref="A126:B128"/>
+    <mergeCell ref="A122:B124"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="A118:B120"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4125,17 +4125,17 @@
       <c r="A1" s="93"/>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
-      <c r="D1" s="238"/>
-      <c r="E1" s="238"/>
-      <c r="F1" s="238"/>
-      <c r="G1" s="238"/>
-      <c r="H1" s="238"/>
-      <c r="I1" s="238"/>
-      <c r="J1" s="238"/>
-      <c r="K1" s="238"/>
-      <c r="L1" s="238"/>
-      <c r="M1" s="238"/>
-      <c r="N1" s="238"/>
+      <c r="D1" s="269"/>
+      <c r="E1" s="269"/>
+      <c r="F1" s="269"/>
+      <c r="G1" s="269"/>
+      <c r="H1" s="269"/>
+      <c r="I1" s="269"/>
+      <c r="J1" s="269"/>
+      <c r="K1" s="269"/>
+      <c r="L1" s="269"/>
+      <c r="M1" s="269"/>
+      <c r="N1" s="269"/>
       <c r="O1" s="95"/>
     </row>
     <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4145,10 +4145,10 @@
       <c r="D2" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="262">
-        <v>3000000</v>
-      </c>
-      <c r="F2" s="262"/>
+      <c r="E2" s="291">
+        <v>4500000</v>
+      </c>
+      <c r="F2" s="291"/>
       <c r="G2" s="98"/>
       <c r="H2" s="98"/>
       <c r="I2" s="98" t="s">
@@ -4191,238 +4191,238 @@
       <c r="P3" s="80"/>
     </row>
     <row r="4" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="239" t="s">
+      <c r="A4" s="270" t="s">
         <v>159</v>
       </c>
-      <c r="B4" s="240"/>
-      <c r="C4" s="240"/>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="M4" s="240"/>
-      <c r="N4" s="240"/>
-      <c r="O4" s="241"/>
+      <c r="B4" s="271"/>
+      <c r="C4" s="271"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
+      <c r="M4" s="271"/>
+      <c r="N4" s="271"/>
+      <c r="O4" s="272"/>
       <c r="P4" s="80"/>
     </row>
     <row r="5" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="242"/>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
-      <c r="D5" s="243"/>
-      <c r="E5" s="243"/>
-      <c r="F5" s="243"/>
-      <c r="G5" s="243"/>
-      <c r="H5" s="243"/>
-      <c r="I5" s="243"/>
-      <c r="J5" s="243"/>
-      <c r="K5" s="243"/>
-      <c r="L5" s="243"/>
-      <c r="M5" s="243"/>
-      <c r="N5" s="243"/>
-      <c r="O5" s="244"/>
+      <c r="A5" s="273"/>
+      <c r="B5" s="274"/>
+      <c r="C5" s="274"/>
+      <c r="D5" s="274"/>
+      <c r="E5" s="274"/>
+      <c r="F5" s="274"/>
+      <c r="G5" s="274"/>
+      <c r="H5" s="274"/>
+      <c r="I5" s="274"/>
+      <c r="J5" s="274"/>
+      <c r="K5" s="274"/>
+      <c r="L5" s="274"/>
+      <c r="M5" s="274"/>
+      <c r="N5" s="274"/>
+      <c r="O5" s="275"/>
       <c r="P5" s="80"/>
     </row>
     <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="242"/>
-      <c r="B6" s="243"/>
-      <c r="C6" s="243"/>
-      <c r="D6" s="243"/>
-      <c r="E6" s="243"/>
-      <c r="F6" s="243"/>
-      <c r="G6" s="243"/>
-      <c r="H6" s="243"/>
-      <c r="I6" s="243"/>
-      <c r="J6" s="243"/>
-      <c r="K6" s="243"/>
-      <c r="L6" s="243"/>
-      <c r="M6" s="243"/>
-      <c r="N6" s="243"/>
-      <c r="O6" s="244"/>
+      <c r="A6" s="273"/>
+      <c r="B6" s="274"/>
+      <c r="C6" s="274"/>
+      <c r="D6" s="274"/>
+      <c r="E6" s="274"/>
+      <c r="F6" s="274"/>
+      <c r="G6" s="274"/>
+      <c r="H6" s="274"/>
+      <c r="I6" s="274"/>
+      <c r="J6" s="274"/>
+      <c r="K6" s="274"/>
+      <c r="L6" s="274"/>
+      <c r="M6" s="274"/>
+      <c r="N6" s="274"/>
+      <c r="O6" s="275"/>
       <c r="P6" s="80"/>
     </row>
     <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="242"/>
-      <c r="B7" s="243"/>
-      <c r="C7" s="243"/>
-      <c r="D7" s="243"/>
-      <c r="E7" s="243"/>
-      <c r="F7" s="243"/>
-      <c r="G7" s="243"/>
-      <c r="H7" s="243"/>
-      <c r="I7" s="243"/>
-      <c r="J7" s="243"/>
-      <c r="K7" s="243"/>
-      <c r="L7" s="243"/>
-      <c r="M7" s="243"/>
-      <c r="N7" s="243"/>
-      <c r="O7" s="244"/>
+      <c r="A7" s="273"/>
+      <c r="B7" s="274"/>
+      <c r="C7" s="274"/>
+      <c r="D7" s="274"/>
+      <c r="E7" s="274"/>
+      <c r="F7" s="274"/>
+      <c r="G7" s="274"/>
+      <c r="H7" s="274"/>
+      <c r="I7" s="274"/>
+      <c r="J7" s="274"/>
+      <c r="K7" s="274"/>
+      <c r="L7" s="274"/>
+      <c r="M7" s="274"/>
+      <c r="N7" s="274"/>
+      <c r="O7" s="275"/>
       <c r="P7" s="80"/>
     </row>
     <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="245"/>
-      <c r="B8" s="246"/>
-      <c r="C8" s="246"/>
-      <c r="D8" s="246"/>
-      <c r="E8" s="246"/>
-      <c r="F8" s="246"/>
-      <c r="G8" s="246"/>
-      <c r="H8" s="246"/>
-      <c r="I8" s="246"/>
-      <c r="J8" s="246"/>
-      <c r="K8" s="246"/>
-      <c r="L8" s="246"/>
-      <c r="M8" s="246"/>
-      <c r="N8" s="246"/>
-      <c r="O8" s="247"/>
+      <c r="A8" s="276"/>
+      <c r="B8" s="277"/>
+      <c r="C8" s="277"/>
+      <c r="D8" s="277"/>
+      <c r="E8" s="277"/>
+      <c r="F8" s="277"/>
+      <c r="G8" s="277"/>
+      <c r="H8" s="277"/>
+      <c r="I8" s="277"/>
+      <c r="J8" s="277"/>
+      <c r="K8" s="277"/>
+      <c r="L8" s="277"/>
+      <c r="M8" s="277"/>
+      <c r="N8" s="277"/>
+      <c r="O8" s="278"/>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="256" t="s">
+      <c r="A9" s="285" t="s">
         <v>157</v>
       </c>
-      <c r="B9" s="257"/>
-      <c r="C9" s="257"/>
-      <c r="D9" s="257"/>
-      <c r="E9" s="257"/>
-      <c r="F9" s="257"/>
-      <c r="G9" s="257"/>
-      <c r="H9" s="257"/>
-      <c r="I9" s="257"/>
-      <c r="J9" s="257"/>
-      <c r="K9" s="257"/>
-      <c r="L9" s="257"/>
-      <c r="M9" s="257"/>
-      <c r="N9" s="257"/>
-      <c r="O9" s="258"/>
+      <c r="B9" s="286"/>
+      <c r="C9" s="286"/>
+      <c r="D9" s="286"/>
+      <c r="E9" s="286"/>
+      <c r="F9" s="286"/>
+      <c r="G9" s="286"/>
+      <c r="H9" s="286"/>
+      <c r="I9" s="286"/>
+      <c r="J9" s="286"/>
+      <c r="K9" s="286"/>
+      <c r="L9" s="286"/>
+      <c r="M9" s="286"/>
+      <c r="N9" s="286"/>
+      <c r="O9" s="287"/>
     </row>
     <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="267" t="s">
+      <c r="A10" s="258" t="s">
         <v>218</v>
       </c>
-      <c r="B10" s="268"/>
-      <c r="C10" s="268"/>
-      <c r="D10" s="268"/>
-      <c r="E10" s="268"/>
-      <c r="F10" s="268"/>
-      <c r="G10" s="268"/>
-      <c r="H10" s="268"/>
-      <c r="I10" s="268"/>
-      <c r="J10" s="268"/>
-      <c r="K10" s="268"/>
-      <c r="L10" s="268"/>
-      <c r="M10" s="268"/>
-      <c r="N10" s="268"/>
-      <c r="O10" s="269"/>
+      <c r="B10" s="259"/>
+      <c r="C10" s="259"/>
+      <c r="D10" s="259"/>
+      <c r="E10" s="259"/>
+      <c r="F10" s="259"/>
+      <c r="G10" s="259"/>
+      <c r="H10" s="259"/>
+      <c r="I10" s="259"/>
+      <c r="J10" s="259"/>
+      <c r="K10" s="259"/>
+      <c r="L10" s="259"/>
+      <c r="M10" s="259"/>
+      <c r="N10" s="259"/>
+      <c r="O10" s="260"/>
     </row>
     <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="270" t="s">
+      <c r="A11" s="261" t="s">
         <v>219</v>
       </c>
-      <c r="B11" s="271"/>
-      <c r="C11" s="271"/>
-      <c r="D11" s="271"/>
-      <c r="E11" s="271"/>
-      <c r="F11" s="271"/>
-      <c r="G11" s="271"/>
-      <c r="H11" s="271"/>
-      <c r="I11" s="271"/>
-      <c r="J11" s="271"/>
-      <c r="K11" s="271"/>
-      <c r="L11" s="271"/>
-      <c r="M11" s="271"/>
-      <c r="N11" s="271"/>
-      <c r="O11" s="272"/>
+      <c r="B11" s="262"/>
+      <c r="C11" s="262"/>
+      <c r="D11" s="262"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="262"/>
+      <c r="G11" s="262"/>
+      <c r="H11" s="262"/>
+      <c r="I11" s="262"/>
+      <c r="J11" s="262"/>
+      <c r="K11" s="262"/>
+      <c r="L11" s="262"/>
+      <c r="M11" s="262"/>
+      <c r="N11" s="262"/>
+      <c r="O11" s="263"/>
     </row>
     <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="259" t="s">
+      <c r="A12" s="288" t="s">
         <v>158</v>
       </c>
-      <c r="B12" s="260"/>
-      <c r="C12" s="260"/>
-      <c r="D12" s="260"/>
-      <c r="E12" s="260"/>
-      <c r="F12" s="260"/>
-      <c r="G12" s="260"/>
-      <c r="H12" s="260"/>
-      <c r="I12" s="260"/>
-      <c r="J12" s="260"/>
-      <c r="K12" s="260"/>
-      <c r="L12" s="260"/>
-      <c r="M12" s="260"/>
-      <c r="N12" s="260"/>
-      <c r="O12" s="261"/>
+      <c r="B12" s="289"/>
+      <c r="C12" s="289"/>
+      <c r="D12" s="289"/>
+      <c r="E12" s="289"/>
+      <c r="F12" s="289"/>
+      <c r="G12" s="289"/>
+      <c r="H12" s="289"/>
+      <c r="I12" s="289"/>
+      <c r="J12" s="289"/>
+      <c r="K12" s="289"/>
+      <c r="L12" s="289"/>
+      <c r="M12" s="289"/>
+      <c r="N12" s="289"/>
+      <c r="O12" s="290"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="248" t="s">
+      <c r="A13" s="279" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="250" t="s">
+      <c r="B13" s="281" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="250" t="s">
+      <c r="C13" s="281" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="250" t="s">
+      <c r="D13" s="281" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="252" t="s">
+      <c r="E13" s="256" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="250" t="s">
+      <c r="F13" s="281" t="s">
         <v>133</v>
       </c>
-      <c r="G13" s="254" t="s">
+      <c r="G13" s="283" t="s">
         <v>134</v>
       </c>
-      <c r="H13" s="252" t="s">
+      <c r="H13" s="256" t="s">
         <v>135</v>
       </c>
-      <c r="I13" s="252" t="s">
+      <c r="I13" s="256" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="252" t="s">
+      <c r="J13" s="256" t="s">
         <v>126</v>
       </c>
-      <c r="K13" s="298" t="s">
+      <c r="K13" s="266" t="s">
         <v>266</v>
       </c>
-      <c r="L13" s="263" t="s">
+      <c r="L13" s="292" t="s">
         <v>174</v>
       </c>
-      <c r="M13" s="265" t="s">
+      <c r="M13" s="254" t="s">
         <v>180</v>
       </c>
       <c r="N13" s="143" t="s">
         <v>213</v>
       </c>
-      <c r="O13" s="273" t="s">
+      <c r="O13" s="264" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="249"/>
-      <c r="B14" s="251"/>
-      <c r="C14" s="251"/>
-      <c r="D14" s="251"/>
-      <c r="E14" s="253"/>
-      <c r="F14" s="251"/>
-      <c r="G14" s="255"/>
-      <c r="H14" s="253"/>
-      <c r="I14" s="253"/>
-      <c r="J14" s="253"/>
-      <c r="K14" s="299"/>
-      <c r="L14" s="264"/>
-      <c r="M14" s="266"/>
+      <c r="A14" s="280"/>
+      <c r="B14" s="282"/>
+      <c r="C14" s="282"/>
+      <c r="D14" s="282"/>
+      <c r="E14" s="257"/>
+      <c r="F14" s="282"/>
+      <c r="G14" s="284"/>
+      <c r="H14" s="257"/>
+      <c r="I14" s="257"/>
+      <c r="J14" s="257"/>
+      <c r="K14" s="267"/>
+      <c r="L14" s="293"/>
+      <c r="M14" s="255"/>
       <c r="N14" s="144" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="O14" s="274"/>
+      <c r="O14" s="265"/>
     </row>
     <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="129">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="J15" s="125">
         <f t="shared" ref="J15:J46" si="1">E$2*D15/100</f>
-        <v>41100.000000000007</v>
+        <v>61650.000000000007</v>
       </c>
       <c r="K15" s="125">
         <f>M$2*D15/100</f>
@@ -4466,11 +4466,11 @@
       <c r="M15" s="147"/>
       <c r="N15" s="86">
         <f>ROUND(SUM(G15:M15),0) + P15</f>
-        <v>267150.01</v>
+        <v>287700.01</v>
       </c>
       <c r="O15" s="139">
         <f t="shared" ref="O15:O35" si="2">ROUND(N15*3%,0) + N15</f>
-        <v>275165.01</v>
+        <v>296331.01</v>
       </c>
       <c r="P15" s="50">
         <v>0.01</v>
@@ -4500,12 +4500,12 @@
         <v>114714.3306</v>
       </c>
       <c r="I16" s="212">
-        <f t="shared" ref="I15:I46" si="4">J$2*D16/100</f>
+        <f t="shared" ref="I16:I46" si="4">J$2*D16/100</f>
         <v>124526.21691399999</v>
       </c>
       <c r="J16" s="212">
         <f t="shared" si="1"/>
-        <v>35400</v>
+        <v>53100</v>
       </c>
       <c r="K16" s="212">
         <f t="shared" ref="K16:K79" si="5">M$2*D16/100</f>
@@ -4515,11 +4515,11 @@
       <c r="M16" s="213"/>
       <c r="N16" s="214">
         <f>ROUND(SUM(G16:M16),0) + P16</f>
-        <v>4168625.02</v>
+        <v>4186325.02</v>
       </c>
       <c r="O16" s="215">
         <f t="shared" si="2"/>
-        <v>4293684.0199999996</v>
+        <v>4311915.0199999996</v>
       </c>
       <c r="P16" s="50">
         <f>P15+0.01</f>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="J17" s="125">
         <f t="shared" si="1"/>
-        <v>22200</v>
+        <v>33300</v>
       </c>
       <c r="K17" s="125">
         <f t="shared" si="5"/>
@@ -4571,11 +4571,11 @@
       <c r="M17" s="147"/>
       <c r="N17" s="86">
         <f t="shared" ref="N17:N80" si="6">ROUND(SUM(G17:M17),0) + P17</f>
-        <v>144300.03</v>
+        <v>155400.03</v>
       </c>
       <c r="O17" s="139">
         <f t="shared" si="2"/>
-        <v>148629.03</v>
+        <v>160062.03</v>
       </c>
       <c r="P17" s="50">
         <f t="shared" ref="P17:P32" si="7">P16+0.01</f>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="J18" s="126">
         <f t="shared" si="1"/>
-        <v>44100</v>
+        <v>66150</v>
       </c>
       <c r="K18" s="125">
         <f t="shared" si="5"/>
@@ -4624,11 +4624,11 @@
       <c r="M18" s="148"/>
       <c r="N18" s="86">
         <f t="shared" si="6"/>
-        <v>286650.03999999998</v>
+        <v>308700.03999999998</v>
       </c>
       <c r="O18" s="140">
         <f t="shared" si="2"/>
-        <v>295250.03999999998</v>
+        <v>317961.03999999998</v>
       </c>
       <c r="P18" s="50">
         <f t="shared" si="7"/>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="J19" s="125">
         <f t="shared" si="1"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K19" s="125">
         <f t="shared" si="5"/>
@@ -4676,11 +4676,11 @@
       <c r="M19" s="147"/>
       <c r="N19" s="86">
         <f t="shared" si="6"/>
-        <v>212518.05</v>
+        <v>229318.05</v>
       </c>
       <c r="O19" s="139">
         <f t="shared" si="2"/>
-        <v>218894.05</v>
+        <v>236198.05</v>
       </c>
       <c r="P19" s="50">
         <f t="shared" si="7"/>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="J20" s="125">
         <f t="shared" si="1"/>
-        <v>40500.000000000007</v>
+        <v>60750</v>
       </c>
       <c r="K20" s="125">
         <f t="shared" si="5"/>
@@ -4728,11 +4728,11 @@
       <c r="M20" s="147"/>
       <c r="N20" s="86">
         <f t="shared" si="6"/>
-        <v>262832.06</v>
+        <v>283082.06</v>
       </c>
       <c r="O20" s="139">
         <f t="shared" si="2"/>
-        <v>270717.06</v>
+        <v>291574.06</v>
       </c>
       <c r="P20" s="50">
         <f t="shared" si="7"/>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="J21" s="125">
         <f t="shared" si="1"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K21" s="125">
         <f t="shared" si="5"/>
@@ -4781,11 +4781,11 @@
       <c r="M21" s="147"/>
       <c r="N21" s="86">
         <f t="shared" si="6"/>
-        <v>218400.07</v>
+        <v>235200.07</v>
       </c>
       <c r="O21" s="139">
         <f t="shared" si="2"/>
-        <v>224952.07</v>
+        <v>242256.07</v>
       </c>
       <c r="P21" s="50">
         <f t="shared" si="7"/>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="J22" s="125">
         <f t="shared" si="1"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K22" s="125">
         <f t="shared" si="5"/>
@@ -4834,11 +4834,11 @@
       <c r="M22" s="147"/>
       <c r="N22" s="86">
         <f t="shared" si="6"/>
-        <v>159900.07999999999</v>
+        <v>172200.08</v>
       </c>
       <c r="O22" s="139">
         <f t="shared" si="2"/>
-        <v>164697.07999999999</v>
+        <v>177366.08</v>
       </c>
       <c r="P22" s="50">
         <f t="shared" si="7"/>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="J23" s="125">
         <f t="shared" si="1"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K23" s="125">
         <f t="shared" si="5"/>
@@ -4886,11 +4886,11 @@
       <c r="M23" s="147"/>
       <c r="N23" s="86">
         <f t="shared" si="6"/>
-        <v>155590.09</v>
+        <v>167890.09</v>
       </c>
       <c r="O23" s="139">
         <f t="shared" si="2"/>
-        <v>160258.09</v>
+        <v>172927.09</v>
       </c>
       <c r="P23" s="50">
         <f t="shared" si="7"/>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="J24" s="125">
         <f t="shared" si="1"/>
-        <v>40200.000000000007</v>
+        <v>60300</v>
       </c>
       <c r="K24" s="125">
         <f t="shared" si="5"/>
@@ -4938,11 +4938,11 @@
       <c r="M24" s="147"/>
       <c r="N24" s="86">
         <f t="shared" si="6"/>
-        <v>268753.09999999998</v>
+        <v>288853.09999999998</v>
       </c>
       <c r="O24" s="139">
         <f t="shared" si="2"/>
-        <v>276816.09999999998</v>
+        <v>297519.09999999998</v>
       </c>
       <c r="P24" s="50">
         <f t="shared" si="7"/>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="J25" s="125">
         <f t="shared" si="1"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K25" s="125">
         <f t="shared" si="5"/>
@@ -4991,11 +4991,11 @@
       <c r="M25" s="147"/>
       <c r="N25" s="86">
         <f t="shared" si="6"/>
-        <v>218400.11</v>
+        <v>235200.11</v>
       </c>
       <c r="O25" s="139">
         <f t="shared" si="2"/>
-        <v>224952.11</v>
+        <v>242256.11</v>
       </c>
       <c r="P25" s="50">
         <f t="shared" si="7"/>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="J26" s="212">
         <f t="shared" si="1"/>
-        <v>35100</v>
+        <v>52650</v>
       </c>
       <c r="K26" s="212">
         <f t="shared" si="5"/>
@@ -5043,11 +5043,11 @@
       <c r="M26" s="213"/>
       <c r="N26" s="214">
         <f t="shared" si="6"/>
-        <v>5191814.12</v>
+        <v>5209364.12</v>
       </c>
       <c r="O26" s="215">
         <f t="shared" si="2"/>
-        <v>5347568.12</v>
+        <v>5365645.12</v>
       </c>
       <c r="P26" s="50">
         <f t="shared" si="7"/>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="J27" s="125">
         <f t="shared" si="1"/>
-        <v>40500.000000000007</v>
+        <v>60750</v>
       </c>
       <c r="K27" s="125">
         <f t="shared" si="5"/>
@@ -5096,11 +5096,11 @@
       <c r="M27" s="147"/>
       <c r="N27" s="86">
         <f t="shared" si="6"/>
-        <v>263250.13</v>
+        <v>283500.13</v>
       </c>
       <c r="O27" s="139">
         <f t="shared" si="2"/>
-        <v>271148.13</v>
+        <v>292005.13</v>
       </c>
       <c r="P27" s="50">
         <f t="shared" si="7"/>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="J28" s="125">
         <f t="shared" si="1"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K28" s="125">
         <f t="shared" si="5"/>
@@ -5146,11 +5146,11 @@
       <c r="M28" s="147"/>
       <c r="N28" s="86">
         <f t="shared" si="6"/>
-        <v>827419.14</v>
+        <v>844219.14</v>
       </c>
       <c r="O28" s="139">
         <f t="shared" si="2"/>
-        <v>852242.14</v>
+        <v>869546.14</v>
       </c>
       <c r="P28" s="50">
         <f t="shared" si="7"/>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="J29" s="125">
         <f t="shared" si="1"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K29" s="125">
         <f t="shared" si="5"/>
@@ -5199,11 +5199,11 @@
       <c r="M29" s="147"/>
       <c r="N29" s="86">
         <f t="shared" si="6"/>
-        <v>159900.15</v>
+        <v>172200.15</v>
       </c>
       <c r="O29" s="139">
         <f t="shared" si="2"/>
-        <v>164697.15</v>
+        <v>177366.15</v>
       </c>
       <c r="P29" s="50">
         <f t="shared" si="7"/>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="J30" s="125">
         <f t="shared" si="1"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K30" s="125">
         <f t="shared" si="5"/>
@@ -5252,11 +5252,11 @@
       <c r="M30" s="147"/>
       <c r="N30" s="86">
         <f t="shared" si="6"/>
-        <v>159900.16</v>
+        <v>172200.16</v>
       </c>
       <c r="O30" s="139">
         <f t="shared" si="2"/>
-        <v>164697.16</v>
+        <v>177366.16</v>
       </c>
       <c r="P30" s="50">
         <f t="shared" si="7"/>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="J31" s="125">
         <f t="shared" si="1"/>
-        <v>40200.000000000007</v>
+        <v>60300</v>
       </c>
       <c r="K31" s="125">
         <f t="shared" si="5"/>
@@ -5305,11 +5305,11 @@
       <c r="M31" s="147"/>
       <c r="N31" s="86">
         <f t="shared" si="6"/>
-        <v>261300.17</v>
+        <v>281400.17</v>
       </c>
       <c r="O31" s="139">
         <f t="shared" si="2"/>
-        <v>269139.17000000004</v>
+        <v>289842.17</v>
       </c>
       <c r="P31" s="50">
         <f t="shared" si="7"/>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="J32" s="126">
         <f t="shared" si="1"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K32" s="125">
         <f t="shared" si="5"/>
@@ -5358,11 +5358,11 @@
       <c r="M32" s="148"/>
       <c r="N32" s="86">
         <f t="shared" si="6"/>
-        <v>218400.18</v>
+        <v>235200.18</v>
       </c>
       <c r="O32" s="140">
         <f t="shared" si="2"/>
-        <v>224952.18</v>
+        <v>242256.18</v>
       </c>
       <c r="P32" s="50">
         <f t="shared" si="7"/>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="J33" s="125">
         <f t="shared" si="1"/>
-        <v>35100</v>
+        <v>52650</v>
       </c>
       <c r="K33" s="125">
         <f t="shared" si="5"/>
@@ -5410,11 +5410,11 @@
       <c r="M33" s="147"/>
       <c r="N33" s="86">
         <f t="shared" si="6"/>
-        <v>194370.19</v>
+        <v>211920.19</v>
       </c>
       <c r="O33" s="139">
         <f t="shared" si="2"/>
-        <v>200201.19</v>
+        <v>218278.19</v>
       </c>
       <c r="P33" s="50">
         <f>P32+0.01</f>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="J34" s="128">
         <f t="shared" si="1"/>
-        <v>40500.000000000007</v>
+        <v>60750</v>
       </c>
       <c r="K34" s="128">
         <f t="shared" si="5"/>
@@ -5464,11 +5464,11 @@
       </c>
       <c r="N34" s="124">
         <f t="shared" si="6"/>
-        <v>1179388.2</v>
+        <v>1199638.2</v>
       </c>
       <c r="O34" s="141">
         <f t="shared" si="2"/>
-        <v>1214770.2</v>
+        <v>1235627.2</v>
       </c>
       <c r="P34" s="50">
         <f t="shared" ref="P34:P97" si="8">P33+0.01</f>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="J35" s="126">
         <f t="shared" si="1"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K35" s="125">
         <f t="shared" si="5"/>
@@ -5520,11 +5520,11 @@
       <c r="M35" s="148"/>
       <c r="N35" s="86">
         <f t="shared" si="6"/>
-        <v>218400.21</v>
+        <v>235200.21</v>
       </c>
       <c r="O35" s="140">
         <f t="shared" si="2"/>
-        <v>224952.21</v>
+        <v>242256.21</v>
       </c>
       <c r="P35" s="50">
         <f t="shared" si="8"/>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="J36" s="125">
         <f t="shared" si="1"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K36" s="125">
         <f t="shared" si="5"/>
@@ -5574,11 +5574,11 @@
       <c r="M36" s="147"/>
       <c r="N36" s="86">
         <f t="shared" si="6"/>
-        <v>159900.22</v>
+        <v>172200.22</v>
       </c>
       <c r="O36" s="139">
         <f t="shared" ref="O36:O99" si="9">ROUND(N36*3%,0) + N36</f>
-        <v>164697.22</v>
+        <v>177366.22</v>
       </c>
       <c r="P36" s="50">
         <f t="shared" si="8"/>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="J37" s="125">
         <f t="shared" si="1"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K37" s="125">
         <f t="shared" si="5"/>
@@ -5628,11 +5628,11 @@
       <c r="M37" s="147"/>
       <c r="N37" s="86">
         <f t="shared" si="6"/>
-        <v>159900.23000000001</v>
+        <v>172200.23</v>
       </c>
       <c r="O37" s="139">
         <f t="shared" si="9"/>
-        <v>164697.23000000001</v>
+        <v>177366.23</v>
       </c>
       <c r="P37" s="50">
         <f t="shared" si="8"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="J38" s="125">
         <f t="shared" si="1"/>
-        <v>40200.000000000007</v>
+        <v>60300</v>
       </c>
       <c r="K38" s="125">
         <f t="shared" si="5"/>
@@ -5681,11 +5681,11 @@
       <c r="M38" s="147"/>
       <c r="N38" s="86">
         <f t="shared" si="6"/>
-        <v>509736.24</v>
+        <v>529836.24</v>
       </c>
       <c r="O38" s="139">
         <f t="shared" si="9"/>
-        <v>525028.24</v>
+        <v>545731.24</v>
       </c>
       <c r="P38" s="50">
         <f t="shared" si="8"/>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="J39" s="125">
         <f t="shared" si="1"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K39" s="125">
         <f t="shared" si="5"/>
@@ -5734,11 +5734,11 @@
       <c r="M39" s="147"/>
       <c r="N39" s="86">
         <f t="shared" si="6"/>
-        <v>426048.25</v>
+        <v>442848.25</v>
       </c>
       <c r="O39" s="139">
         <f t="shared" si="9"/>
-        <v>438829.25</v>
+        <v>456133.25</v>
       </c>
       <c r="P39" s="50">
         <f t="shared" si="8"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="J40" s="125">
         <f t="shared" si="1"/>
-        <v>35100</v>
+        <v>52650</v>
       </c>
       <c r="K40" s="125">
         <f t="shared" si="5"/>
@@ -5787,11 +5787,11 @@
       <c r="M40" s="147"/>
       <c r="N40" s="86">
         <f t="shared" si="6"/>
-        <v>445068.26</v>
+        <v>462618.26</v>
       </c>
       <c r="O40" s="139">
         <f t="shared" si="9"/>
-        <v>458420.26</v>
+        <v>476497.26</v>
       </c>
       <c r="P40" s="50">
         <f t="shared" si="8"/>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="J41" s="125">
         <f t="shared" si="1"/>
-        <v>40500.000000000007</v>
+        <v>60750</v>
       </c>
       <c r="K41" s="125">
         <f t="shared" si="5"/>
@@ -5841,11 +5841,11 @@
       <c r="M41" s="147"/>
       <c r="N41" s="86">
         <f t="shared" si="6"/>
-        <v>263250.27</v>
+        <v>283500.27</v>
       </c>
       <c r="O41" s="139">
         <f t="shared" si="9"/>
-        <v>271148.27</v>
+        <v>292005.27</v>
       </c>
       <c r="P41" s="50">
         <f t="shared" si="8"/>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="J42" s="125">
         <f t="shared" si="1"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K42" s="125">
         <f t="shared" si="5"/>
@@ -5892,11 +5892,11 @@
       <c r="M42" s="147"/>
       <c r="N42" s="86">
         <f t="shared" si="6"/>
-        <v>1019522.28</v>
+        <v>1036322.28</v>
       </c>
       <c r="O42" s="139">
         <f t="shared" si="9"/>
-        <v>1050108.28</v>
+        <v>1067412.28</v>
       </c>
       <c r="P42" s="50">
         <f t="shared" si="8"/>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="J43" s="126">
         <f t="shared" si="1"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K43" s="125">
         <f t="shared" si="5"/>
@@ -5945,11 +5945,11 @@
       <c r="M43" s="148"/>
       <c r="N43" s="86">
         <f t="shared" si="6"/>
-        <v>155597.29</v>
+        <v>167897.29</v>
       </c>
       <c r="O43" s="140">
         <f t="shared" si="9"/>
-        <v>160265.29</v>
+        <v>172934.29</v>
       </c>
       <c r="P43" s="50">
         <f t="shared" si="8"/>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="J44" s="126">
         <f t="shared" si="1"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K44" s="125">
         <f t="shared" si="5"/>
@@ -6002,11 +6002,11 @@
       <c r="M44" s="148"/>
       <c r="N44" s="112">
         <f t="shared" si="6"/>
-        <v>159900.29999999999</v>
+        <v>172200.3</v>
       </c>
       <c r="O44" s="140">
         <f t="shared" si="9"/>
-        <v>164697.29999999999</v>
+        <v>177366.3</v>
       </c>
       <c r="P44" s="50">
         <f t="shared" si="8"/>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="J45" s="125">
         <f t="shared" si="1"/>
-        <v>40200.000000000007</v>
+        <v>60300</v>
       </c>
       <c r="K45" s="125">
         <f t="shared" si="5"/>
@@ -6056,11 +6056,11 @@
       <c r="M45" s="147"/>
       <c r="N45" s="86">
         <f t="shared" si="6"/>
-        <v>261300.31</v>
+        <v>281400.31</v>
       </c>
       <c r="O45" s="139">
         <f t="shared" si="9"/>
-        <v>269139.31</v>
+        <v>289842.31</v>
       </c>
       <c r="P45" s="50">
         <f t="shared" si="8"/>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="J46" s="125">
         <f t="shared" si="1"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K46" s="125">
         <f t="shared" si="5"/>
@@ -6110,11 +6110,11 @@
       <c r="M46" s="147"/>
       <c r="N46" s="86">
         <f t="shared" si="6"/>
-        <v>344530.32</v>
+        <v>361330.32</v>
       </c>
       <c r="O46" s="139">
         <f t="shared" si="9"/>
-        <v>354866.32</v>
+        <v>372170.32</v>
       </c>
       <c r="P46" s="50">
         <f t="shared" si="8"/>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="J47" s="128">
         <f t="shared" ref="J47:J78" si="13">E$2*D47/100</f>
-        <v>35100</v>
+        <v>52650</v>
       </c>
       <c r="K47" s="128">
         <f t="shared" si="5"/>
@@ -6163,11 +6163,11 @@
       </c>
       <c r="N47" s="124">
         <f t="shared" si="6"/>
-        <v>398150.33</v>
+        <v>415700.33</v>
       </c>
       <c r="O47" s="141">
         <f t="shared" si="9"/>
-        <v>410095.33</v>
+        <v>428171.33</v>
       </c>
       <c r="P47" s="50">
         <f t="shared" si="8"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="J48" s="125">
         <f t="shared" si="13"/>
-        <v>40500.000000000007</v>
+        <v>60750</v>
       </c>
       <c r="K48" s="125">
         <f t="shared" si="5"/>
@@ -6220,11 +6220,11 @@
       <c r="M48" s="147"/>
       <c r="N48" s="86">
         <f t="shared" si="6"/>
-        <v>263250.34000000003</v>
+        <v>283500.34000000003</v>
       </c>
       <c r="O48" s="139">
         <f t="shared" si="9"/>
-        <v>271148.34000000003</v>
+        <v>292005.34000000003</v>
       </c>
       <c r="P48" s="50">
         <f t="shared" si="8"/>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="J49" s="197">
         <f t="shared" si="13"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K49" s="125">
         <f t="shared" si="5"/>
@@ -6274,11 +6274,11 @@
       <c r="M49" s="198"/>
       <c r="N49" s="112">
         <f t="shared" si="6"/>
-        <v>218400.35</v>
+        <v>235200.35</v>
       </c>
       <c r="O49" s="140">
         <f t="shared" si="9"/>
-        <v>224952.35</v>
+        <v>242256.35</v>
       </c>
       <c r="P49" s="50">
         <f t="shared" si="8"/>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="J50" s="125">
         <f t="shared" si="13"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K50" s="125">
         <f t="shared" si="5"/>
@@ -6331,11 +6331,11 @@
       <c r="M50" s="147"/>
       <c r="N50" s="86">
         <f t="shared" si="6"/>
-        <v>159900.35999999999</v>
+        <v>172200.36</v>
       </c>
       <c r="O50" s="139">
         <f t="shared" si="9"/>
-        <v>164697.35999999999</v>
+        <v>177366.36</v>
       </c>
       <c r="P50" s="50">
         <f t="shared" si="8"/>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="J51" s="125">
         <f t="shared" si="13"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K51" s="125">
         <f t="shared" si="5"/>
@@ -6388,11 +6388,11 @@
       <c r="M51" s="147"/>
       <c r="N51" s="86">
         <f t="shared" si="6"/>
-        <v>158900.37</v>
+        <v>171200.37</v>
       </c>
       <c r="O51" s="139">
         <f t="shared" si="9"/>
-        <v>163667.37</v>
+        <v>176336.37</v>
       </c>
       <c r="P51" s="50">
         <f t="shared" si="8"/>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="J52" s="125">
         <f t="shared" si="13"/>
-        <v>40200.000000000007</v>
+        <v>60300</v>
       </c>
       <c r="K52" s="125">
         <f t="shared" si="5"/>
@@ -6442,11 +6442,11 @@
       <c r="M52" s="147"/>
       <c r="N52" s="86">
         <f t="shared" si="6"/>
-        <v>1032948.38</v>
+        <v>1053048.3799999999</v>
       </c>
       <c r="O52" s="139">
         <f t="shared" si="9"/>
-        <v>1063936.3799999999</v>
+        <v>1084639.3799999999</v>
       </c>
       <c r="P52" s="50">
         <f t="shared" si="8"/>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="J53" s="125">
         <f t="shared" si="13"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K53" s="125">
         <f t="shared" si="5"/>
@@ -6499,11 +6499,11 @@
       <c r="M53" s="147"/>
       <c r="N53" s="86">
         <f t="shared" si="6"/>
-        <v>218400.39</v>
+        <v>235200.39</v>
       </c>
       <c r="O53" s="139">
         <f t="shared" si="9"/>
-        <v>224952.39</v>
+        <v>242256.39</v>
       </c>
       <c r="P53" s="50">
         <f t="shared" si="8"/>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="J54" s="125">
         <f t="shared" si="13"/>
-        <v>35100</v>
+        <v>52650</v>
       </c>
       <c r="K54" s="125">
         <f t="shared" si="5"/>
@@ -6553,11 +6553,11 @@
       <c r="M54" s="147"/>
       <c r="N54" s="86">
         <f t="shared" si="6"/>
-        <v>228150.39999999999</v>
+        <v>245700.4</v>
       </c>
       <c r="O54" s="139">
         <f t="shared" si="9"/>
-        <v>234995.4</v>
+        <v>253071.4</v>
       </c>
       <c r="P54" s="50">
         <f t="shared" si="8"/>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="J55" s="125">
         <f t="shared" si="13"/>
-        <v>40500.000000000007</v>
+        <v>60750</v>
       </c>
       <c r="K55" s="125">
         <f t="shared" si="5"/>
@@ -6606,11 +6606,11 @@
       <c r="M55" s="147"/>
       <c r="N55" s="86">
         <f t="shared" si="6"/>
-        <v>255877.41</v>
+        <v>276127.40999999997</v>
       </c>
       <c r="O55" s="139">
         <f t="shared" si="9"/>
-        <v>263553.41000000003</v>
+        <v>284411.40999999997</v>
       </c>
       <c r="P55" s="50">
         <f t="shared" si="8"/>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="J56" s="128">
         <f t="shared" si="13"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K56" s="128">
         <f t="shared" si="5"/>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="N56" s="124">
         <f t="shared" si="6"/>
-        <v>258438.42</v>
+        <v>275238.42</v>
       </c>
       <c r="O56" s="141">
         <f t="shared" si="9"/>
-        <v>266191.42000000004</v>
+        <v>283495.42</v>
       </c>
       <c r="P56" s="50">
         <f t="shared" si="8"/>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="J57" s="128">
         <f t="shared" si="13"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K57" s="128">
         <f t="shared" si="5"/>
@@ -6716,11 +6716,11 @@
       </c>
       <c r="N57" s="124">
         <f>ROUND(SUM(G57:M57),0) + P57</f>
-        <v>778170.43</v>
+        <v>790470.43</v>
       </c>
       <c r="O57" s="141">
         <f t="shared" si="9"/>
-        <v>801515.43</v>
+        <v>814184.43</v>
       </c>
       <c r="P57" s="50">
         <f t="shared" si="8"/>
@@ -6763,7 +6763,7 @@
       </c>
       <c r="J58" s="125">
         <f t="shared" si="13"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K58" s="125">
         <f t="shared" si="5"/>
@@ -6773,11 +6773,11 @@
       <c r="M58" s="147"/>
       <c r="N58" s="86">
         <f t="shared" si="6"/>
-        <v>116813.44</v>
+        <v>129113.44</v>
       </c>
       <c r="O58" s="139">
         <f t="shared" si="9"/>
-        <v>120317.44</v>
+        <v>132986.44</v>
       </c>
       <c r="P58" s="50">
         <f t="shared" si="8"/>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="J59" s="125">
         <f t="shared" si="13"/>
-        <v>40200.000000000007</v>
+        <v>60300</v>
       </c>
       <c r="K59" s="125">
         <f t="shared" si="5"/>
@@ -6830,11 +6830,11 @@
       <c r="M59" s="147"/>
       <c r="N59" s="86">
         <f t="shared" si="6"/>
-        <v>261300.45</v>
+        <v>281400.45</v>
       </c>
       <c r="O59" s="139">
         <f t="shared" si="9"/>
-        <v>269139.45</v>
+        <v>289842.45</v>
       </c>
       <c r="P59" s="50">
         <f t="shared" si="8"/>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="J60" s="125">
         <f t="shared" si="13"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K60" s="125">
         <f t="shared" si="5"/>
@@ -6883,11 +6883,11 @@
       <c r="M60" s="147"/>
       <c r="N60" s="86">
         <f t="shared" si="6"/>
-        <v>226590.46</v>
+        <v>243390.46</v>
       </c>
       <c r="O60" s="139">
         <f t="shared" si="9"/>
-        <v>233388.46</v>
+        <v>250692.46</v>
       </c>
       <c r="P60" s="50">
         <f t="shared" si="8"/>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="J61" s="128">
         <f t="shared" si="13"/>
-        <v>35100</v>
+        <v>52650</v>
       </c>
       <c r="K61" s="128">
         <f t="shared" si="5"/>
@@ -6938,11 +6938,11 @@
       </c>
       <c r="N61" s="124">
         <f t="shared" si="6"/>
-        <v>1098245.47</v>
+        <v>1115795.47</v>
       </c>
       <c r="O61" s="141">
         <f t="shared" si="9"/>
-        <v>1131192.47</v>
+        <v>1149269.47</v>
       </c>
       <c r="P61" s="50">
         <f t="shared" si="8"/>
@@ -6953,53 +6953,53 @@
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A62" s="284">
+      <c r="A62" s="221">
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
-      <c r="B62" s="285" t="s">
+      <c r="B62" s="222" t="s">
         <v>47</v>
       </c>
-      <c r="C62" s="286"/>
-      <c r="D62" s="287">
+      <c r="C62" s="223"/>
+      <c r="D62" s="224">
         <v>1.35</v>
       </c>
-      <c r="E62" s="288">
+      <c r="E62" s="225">
         <v>250290.48</v>
       </c>
-      <c r="F62" s="288">
+      <c r="F62" s="225">
         <f t="shared" ref="F62:F67" si="14">E62</f>
         <v>250290.48</v>
       </c>
-      <c r="G62" s="289">
+      <c r="G62" s="226">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H62" s="289">
+      <c r="H62" s="226">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I62" s="290">
+      <c r="I62" s="227">
         <f t="shared" si="12"/>
         <v>142466.43460500002</v>
       </c>
-      <c r="J62" s="290">
+      <c r="J62" s="227">
         <f t="shared" si="13"/>
-        <v>40500.000000000007</v>
-      </c>
-      <c r="K62" s="290">
+        <v>60750</v>
+      </c>
+      <c r="K62" s="227">
         <f t="shared" si="5"/>
         <v>80283.565394999998</v>
       </c>
-      <c r="L62" s="290"/>
-      <c r="M62" s="291"/>
-      <c r="N62" s="292">
+      <c r="L62" s="227"/>
+      <c r="M62" s="228"/>
+      <c r="N62" s="229">
         <f t="shared" si="6"/>
-        <v>263250.48</v>
-      </c>
-      <c r="O62" s="293">
+        <v>283500.48</v>
+      </c>
+      <c r="O62" s="230">
         <f t="shared" si="9"/>
-        <v>271148.48</v>
+        <v>292005.48</v>
       </c>
       <c r="P62" s="50">
         <f t="shared" si="8"/>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="J63" s="125">
         <f t="shared" si="13"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K63" s="125">
         <f t="shared" si="5"/>
@@ -7052,11 +7052,11 @@
       <c r="M63" s="147"/>
       <c r="N63" s="86">
         <f t="shared" si="6"/>
-        <v>218400.49</v>
+        <v>235200.49</v>
       </c>
       <c r="O63" s="139">
         <f t="shared" si="9"/>
-        <v>224952.49</v>
+        <v>242256.49</v>
       </c>
       <c r="P63" s="50">
         <f t="shared" si="8"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="J64" s="125">
         <f t="shared" si="13"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K64" s="125">
         <f t="shared" si="5"/>
@@ -7105,11 +7105,11 @@
       <c r="M64" s="147"/>
       <c r="N64" s="86">
         <f t="shared" si="6"/>
-        <v>311929.5</v>
+        <v>324229.5</v>
       </c>
       <c r="O64" s="139">
         <f t="shared" si="9"/>
-        <v>321287.5</v>
+        <v>333956.5</v>
       </c>
       <c r="P64" s="50">
         <f t="shared" si="8"/>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="J65" s="125">
         <f t="shared" si="13"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K65" s="125">
         <f t="shared" si="5"/>
@@ -7159,11 +7159,11 @@
       <c r="M65" s="147"/>
       <c r="N65" s="86">
         <f t="shared" si="6"/>
-        <v>159900.51</v>
+        <v>172200.51</v>
       </c>
       <c r="O65" s="139">
         <f t="shared" si="9"/>
-        <v>164697.51</v>
+        <v>177366.51</v>
       </c>
       <c r="P65" s="50">
         <f t="shared" si="8"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="J66" s="125">
         <f t="shared" si="13"/>
-        <v>40200.000000000007</v>
+        <v>60300</v>
       </c>
       <c r="K66" s="125">
         <f t="shared" si="5"/>
@@ -7213,11 +7213,11 @@
       <c r="M66" s="147"/>
       <c r="N66" s="86">
         <f t="shared" si="6"/>
-        <v>261300.52</v>
+        <v>281400.52</v>
       </c>
       <c r="O66" s="139">
         <f t="shared" si="9"/>
-        <v>269139.52</v>
+        <v>289842.52</v>
       </c>
       <c r="P66" s="50">
         <f t="shared" si="8"/>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="J67" s="125">
         <f t="shared" si="13"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K67" s="125">
         <f t="shared" si="5"/>
@@ -7267,11 +7267,11 @@
       <c r="M67" s="147"/>
       <c r="N67" s="86">
         <f t="shared" si="6"/>
-        <v>218400.53</v>
+        <v>235200.53</v>
       </c>
       <c r="O67" s="139">
         <f t="shared" si="9"/>
-        <v>224952.53</v>
+        <v>242256.53</v>
       </c>
       <c r="P67" s="50">
         <f t="shared" si="8"/>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="J68" s="125">
         <f t="shared" si="13"/>
-        <v>35100</v>
+        <v>52650</v>
       </c>
       <c r="K68" s="125">
         <f t="shared" si="5"/>
@@ -7320,11 +7320,11 @@
       <c r="M68" s="147"/>
       <c r="N68" s="86">
         <f t="shared" si="6"/>
-        <v>222011.54</v>
+        <v>239561.54</v>
       </c>
       <c r="O68" s="139">
         <f t="shared" si="9"/>
-        <v>228671.54</v>
+        <v>246748.54</v>
       </c>
       <c r="P68" s="50">
         <f t="shared" si="8"/>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="J69" s="125">
         <f t="shared" si="13"/>
-        <v>40500.000000000007</v>
+        <v>60750</v>
       </c>
       <c r="K69" s="125">
         <f t="shared" si="5"/>
@@ -7374,11 +7374,11 @@
       <c r="M69" s="147"/>
       <c r="N69" s="86">
         <f t="shared" si="6"/>
-        <v>263250.55</v>
+        <v>283500.55</v>
       </c>
       <c r="O69" s="139">
         <f t="shared" si="9"/>
-        <v>271148.55</v>
+        <v>292005.55</v>
       </c>
       <c r="P69" s="50">
         <f t="shared" si="8"/>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="J70" s="125">
         <f t="shared" si="13"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K70" s="125">
         <f t="shared" si="5"/>
@@ -7427,11 +7427,11 @@
       <c r="M70" s="147"/>
       <c r="N70" s="86">
         <f t="shared" si="6"/>
-        <v>753529.56</v>
+        <v>770329.56</v>
       </c>
       <c r="O70" s="139">
         <f t="shared" si="9"/>
-        <v>776135.56</v>
+        <v>793439.56</v>
       </c>
       <c r="P70" s="50">
         <f t="shared" si="8"/>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="J71" s="125">
         <f t="shared" si="13"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K71" s="125">
         <f t="shared" si="5"/>
@@ -7481,11 +7481,11 @@
       <c r="M71" s="147"/>
       <c r="N71" s="86">
         <f t="shared" si="6"/>
-        <v>159900.57</v>
+        <v>172200.57</v>
       </c>
       <c r="O71" s="139">
         <f t="shared" si="9"/>
-        <v>164697.57</v>
+        <v>177366.57</v>
       </c>
       <c r="P71" s="50">
         <f t="shared" si="8"/>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="J72" s="125">
         <f t="shared" si="13"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K72" s="125">
         <f t="shared" si="5"/>
@@ -7538,11 +7538,11 @@
       <c r="M72" s="147"/>
       <c r="N72" s="86">
         <f t="shared" si="6"/>
-        <v>159900.57999999999</v>
+        <v>172200.58</v>
       </c>
       <c r="O72" s="139">
         <f t="shared" si="9"/>
-        <v>164697.57999999999</v>
+        <v>177366.58</v>
       </c>
       <c r="P72" s="50">
         <f t="shared" si="8"/>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="J73" s="126">
         <f t="shared" si="13"/>
-        <v>40200.000000000007</v>
+        <v>60300</v>
       </c>
       <c r="K73" s="125">
         <f t="shared" si="5"/>
@@ -7594,11 +7594,11 @@
       <c r="M73" s="148"/>
       <c r="N73" s="86">
         <f t="shared" si="6"/>
-        <v>254269.59</v>
+        <v>274369.59000000003</v>
       </c>
       <c r="O73" s="140">
         <f t="shared" si="9"/>
-        <v>261897.59</v>
+        <v>282600.59000000003</v>
       </c>
       <c r="P73" s="50">
         <f t="shared" si="8"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="J74" s="125">
         <f t="shared" si="13"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K74" s="125">
         <f t="shared" si="5"/>
@@ -7647,11 +7647,11 @@
       <c r="M74" s="147"/>
       <c r="N74" s="86">
         <f t="shared" si="6"/>
-        <v>212518.6</v>
+        <v>229318.6</v>
       </c>
       <c r="O74" s="139">
         <f t="shared" si="9"/>
-        <v>218894.6</v>
+        <v>236198.6</v>
       </c>
       <c r="P74" s="50">
         <f t="shared" si="8"/>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="J75" s="125">
         <f t="shared" si="13"/>
-        <v>35100</v>
+        <v>52650</v>
       </c>
       <c r="K75" s="125">
         <f t="shared" si="5"/>
@@ -7701,11 +7701,11 @@
       <c r="M75" s="147"/>
       <c r="N75" s="86">
         <f t="shared" si="6"/>
-        <v>228150.61</v>
+        <v>245700.61</v>
       </c>
       <c r="O75" s="139">
         <f t="shared" si="9"/>
-        <v>234995.61</v>
+        <v>253071.61</v>
       </c>
       <c r="P75" s="50">
         <f t="shared" si="8"/>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="J76" s="125">
         <f t="shared" si="13"/>
-        <v>40500.000000000007</v>
+        <v>60750</v>
       </c>
       <c r="K76" s="125">
         <f t="shared" si="5"/>
@@ -7755,11 +7755,11 @@
       <c r="M76" s="147"/>
       <c r="N76" s="86">
         <f t="shared" si="6"/>
-        <v>263250.62</v>
+        <v>283500.62</v>
       </c>
       <c r="O76" s="139">
         <f t="shared" si="9"/>
-        <v>271148.62</v>
+        <v>292005.62</v>
       </c>
       <c r="P76" s="50">
         <f t="shared" si="8"/>
@@ -7799,7 +7799,7 @@
       </c>
       <c r="J77" s="125">
         <f t="shared" si="13"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K77" s="125">
         <f t="shared" si="5"/>
@@ -7809,11 +7809,11 @@
       <c r="M77" s="147"/>
       <c r="N77" s="86">
         <f t="shared" si="6"/>
-        <v>218400.63</v>
+        <v>235200.63</v>
       </c>
       <c r="O77" s="139">
         <f t="shared" si="9"/>
-        <v>224952.63</v>
+        <v>242256.63</v>
       </c>
       <c r="P77" s="50">
         <f t="shared" si="8"/>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="J78" s="125">
         <f t="shared" si="13"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K78" s="125">
         <f t="shared" si="5"/>
@@ -7865,11 +7865,11 @@
       <c r="M78" s="147"/>
       <c r="N78" s="86">
         <f t="shared" si="6"/>
-        <v>155596.64000000001</v>
+        <v>167896.64</v>
       </c>
       <c r="O78" s="139">
         <f t="shared" si="9"/>
-        <v>160264.64000000001</v>
+        <v>172933.64</v>
       </c>
       <c r="P78" s="50">
         <f t="shared" si="8"/>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="J79" s="126">
         <f t="shared" ref="J79:J110" si="18">E$2*D79/100</f>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K79" s="125">
         <f t="shared" si="5"/>
@@ -7918,11 +7918,11 @@
       <c r="M79" s="148"/>
       <c r="N79" s="86">
         <f t="shared" si="6"/>
-        <v>723230.65</v>
+        <v>735530.65</v>
       </c>
       <c r="O79" s="140">
         <f t="shared" si="9"/>
-        <v>744927.65</v>
+        <v>757596.65</v>
       </c>
       <c r="P79" s="50">
         <f t="shared" si="8"/>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="J80" s="126">
         <f t="shared" si="18"/>
-        <v>40200.000000000007</v>
+        <v>60300</v>
       </c>
       <c r="K80" s="125">
         <f t="shared" ref="K80:K117" si="20">M$2*D80/100</f>
@@ -7974,11 +7974,11 @@
       <c r="M80" s="148"/>
       <c r="N80" s="112">
         <f t="shared" si="6"/>
-        <v>867449.66</v>
+        <v>887549.66</v>
       </c>
       <c r="O80" s="140">
         <f t="shared" si="9"/>
-        <v>893472.66</v>
+        <v>914175.66</v>
       </c>
       <c r="P80" s="50">
         <f t="shared" si="8"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="J81" s="125">
         <f t="shared" si="18"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K81" s="125">
         <f t="shared" si="20"/>
@@ -8027,11 +8027,11 @@
       <c r="M81" s="147"/>
       <c r="N81" s="86">
         <f t="shared" ref="N81:N117" si="21">ROUND(SUM(G81:M81),0) + P81</f>
-        <v>420173.67</v>
+        <v>436973.67</v>
       </c>
       <c r="O81" s="139">
         <f t="shared" si="9"/>
-        <v>432778.67</v>
+        <v>450082.67</v>
       </c>
       <c r="P81" s="50">
         <f t="shared" si="8"/>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="J82" s="212">
         <f t="shared" si="18"/>
-        <v>35100</v>
+        <v>52650</v>
       </c>
       <c r="K82" s="212">
         <f t="shared" si="20"/>
@@ -8082,11 +8082,11 @@
       <c r="M82" s="213"/>
       <c r="N82" s="214">
         <f t="shared" si="21"/>
-        <v>7881486.6799999997</v>
+        <v>7899036.6799999997</v>
       </c>
       <c r="O82" s="215">
         <f t="shared" si="9"/>
-        <v>8117931.6799999997</v>
+        <v>8136007.6799999997</v>
       </c>
       <c r="P82" s="50">
         <f t="shared" si="8"/>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="J83" s="125">
         <f t="shared" si="18"/>
-        <v>40500.000000000007</v>
+        <v>60750</v>
       </c>
       <c r="K83" s="125">
         <f t="shared" si="20"/>
@@ -8137,11 +8137,11 @@
       <c r="M83" s="147"/>
       <c r="N83" s="86">
         <f t="shared" si="21"/>
-        <v>263170.69</v>
+        <v>283420.69</v>
       </c>
       <c r="O83" s="139">
         <f t="shared" si="9"/>
-        <v>271065.69</v>
+        <v>291923.69</v>
       </c>
       <c r="P83" s="50">
         <f t="shared" si="8"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="J84" s="126">
         <f t="shared" si="18"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K84" s="125">
         <f t="shared" si="20"/>
@@ -8190,11 +8190,11 @@
       <c r="M84" s="148"/>
       <c r="N84" s="86">
         <f t="shared" si="21"/>
-        <v>426049.7</v>
+        <v>442849.7</v>
       </c>
       <c r="O84" s="140">
         <f t="shared" si="9"/>
-        <v>438830.7</v>
+        <v>456134.7</v>
       </c>
       <c r="P84" s="50">
         <f t="shared" si="8"/>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="J85" s="125">
         <f t="shared" si="18"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K85" s="125">
         <f t="shared" si="20"/>
@@ -8247,11 +8247,11 @@
       <c r="M85" s="147"/>
       <c r="N85" s="86">
         <f t="shared" si="21"/>
-        <v>159900.71</v>
+        <v>172200.71</v>
       </c>
       <c r="O85" s="139">
         <f t="shared" si="9"/>
-        <v>164697.71</v>
+        <v>177366.71</v>
       </c>
       <c r="P85" s="50">
         <f t="shared" si="8"/>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="J86" s="125">
         <f t="shared" si="18"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K86" s="125">
         <f t="shared" si="20"/>
@@ -8301,11 +8301,11 @@
       <c r="M86" s="147"/>
       <c r="N86" s="86">
         <f t="shared" si="21"/>
-        <v>159900.72</v>
+        <v>172200.72</v>
       </c>
       <c r="O86" s="139">
         <f t="shared" si="9"/>
-        <v>164697.72</v>
+        <v>177366.72</v>
       </c>
       <c r="P86" s="50">
         <f t="shared" si="8"/>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="J87" s="125">
         <f t="shared" si="18"/>
-        <v>40200.000000000007</v>
+        <v>60300</v>
       </c>
       <c r="K87" s="125">
         <f t="shared" si="20"/>
@@ -8355,11 +8355,11 @@
       <c r="M87" s="147"/>
       <c r="N87" s="86">
         <f t="shared" si="21"/>
-        <v>261300.73</v>
+        <v>281400.73</v>
       </c>
       <c r="O87" s="139">
         <f t="shared" si="9"/>
-        <v>269139.73</v>
+        <v>289842.73</v>
       </c>
       <c r="P87" s="50">
         <f t="shared" si="8"/>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="J88" s="125">
         <f t="shared" si="18"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K88" s="125">
         <f t="shared" si="20"/>
@@ -8408,11 +8408,11 @@
       <c r="M88" s="147"/>
       <c r="N88" s="86">
         <f t="shared" si="21"/>
-        <v>1381713.74</v>
+        <v>1398513.74</v>
       </c>
       <c r="O88" s="139">
         <f t="shared" si="9"/>
-        <v>1423164.74</v>
+        <v>1440468.74</v>
       </c>
       <c r="P88" s="50">
         <f t="shared" si="8"/>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="J89" s="125">
         <f t="shared" si="18"/>
-        <v>35100</v>
+        <v>52650</v>
       </c>
       <c r="K89" s="125">
         <f t="shared" si="20"/>
@@ -8461,11 +8461,11 @@
       <c r="M89" s="147"/>
       <c r="N89" s="86">
         <f t="shared" si="21"/>
-        <v>221832.75</v>
+        <v>239382.75</v>
       </c>
       <c r="O89" s="139">
         <f t="shared" si="9"/>
-        <v>228487.75</v>
+        <v>246563.75</v>
       </c>
       <c r="P89" s="50">
         <f t="shared" si="8"/>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="J90" s="203">
         <f t="shared" si="18"/>
-        <v>40500.000000000007</v>
+        <v>60750</v>
       </c>
       <c r="K90" s="203">
         <f t="shared" si="20"/>
@@ -8514,11 +8514,11 @@
       <c r="M90" s="204"/>
       <c r="N90" s="205">
         <f t="shared" si="21"/>
-        <v>270759.76</v>
+        <v>291009.76</v>
       </c>
       <c r="O90" s="206">
         <f t="shared" si="9"/>
-        <v>278882.76</v>
+        <v>299739.76</v>
       </c>
       <c r="P90" s="50">
         <f t="shared" si="8"/>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="J91" s="125">
         <f t="shared" si="18"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K91" s="125">
         <f t="shared" si="20"/>
@@ -8568,11 +8568,11 @@
       <c r="M91" s="147"/>
       <c r="N91" s="86">
         <f t="shared" si="21"/>
-        <v>218400.77</v>
+        <v>235200.77</v>
       </c>
       <c r="O91" s="139">
         <f t="shared" si="9"/>
-        <v>224952.77</v>
+        <v>242256.77</v>
       </c>
       <c r="P91" s="50">
         <f t="shared" si="8"/>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="J92" s="128">
         <f t="shared" si="18"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K92" s="128">
         <f t="shared" si="20"/>
@@ -8621,11 +8621,11 @@
       </c>
       <c r="N92" s="124">
         <f t="shared" si="21"/>
-        <v>324900.78000000003</v>
+        <v>337200.78</v>
       </c>
       <c r="O92" s="141">
         <f t="shared" si="9"/>
-        <v>334647.78000000003</v>
+        <v>347316.78</v>
       </c>
       <c r="P92" s="50">
         <f t="shared" si="8"/>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="J93" s="125">
         <f t="shared" si="18"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K93" s="125">
         <f t="shared" si="20"/>
@@ -8678,11 +8678,11 @@
       <c r="M93" s="147"/>
       <c r="N93" s="86">
         <f t="shared" si="21"/>
-        <v>159900.79</v>
+        <v>172200.79</v>
       </c>
       <c r="O93" s="139">
         <f t="shared" si="9"/>
-        <v>164697.79</v>
+        <v>177366.79</v>
       </c>
       <c r="P93" s="50">
         <f t="shared" si="8"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="J94" s="125">
         <f t="shared" si="18"/>
-        <v>40200.000000000007</v>
+        <v>60300</v>
       </c>
       <c r="K94" s="125">
         <f t="shared" si="20"/>
@@ -8734,11 +8734,11 @@
       <c r="M94" s="147"/>
       <c r="N94" s="86">
         <f t="shared" si="21"/>
-        <v>254062.8</v>
+        <v>274162.8</v>
       </c>
       <c r="O94" s="139">
         <f t="shared" si="9"/>
-        <v>261684.8</v>
+        <v>282387.8</v>
       </c>
       <c r="P94" s="50">
         <f t="shared" si="8"/>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="J95" s="126">
         <f t="shared" si="18"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K95" s="125">
         <f t="shared" si="20"/>
@@ -8788,11 +8788,11 @@
       <c r="M95" s="148"/>
       <c r="N95" s="112">
         <f t="shared" si="21"/>
-        <v>218400.81</v>
+        <v>235200.81</v>
       </c>
       <c r="O95" s="140">
         <f t="shared" si="9"/>
-        <v>224952.81</v>
+        <v>242256.81</v>
       </c>
       <c r="P95" s="50">
         <f t="shared" si="8"/>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="J96" s="125">
         <f t="shared" si="18"/>
-        <v>35100</v>
+        <v>52650</v>
       </c>
       <c r="K96" s="125">
         <f t="shared" si="20"/>
@@ -8845,11 +8845,11 @@
       <c r="M96" s="147"/>
       <c r="N96" s="86">
         <f t="shared" si="21"/>
-        <v>228150.82</v>
+        <v>245700.82</v>
       </c>
       <c r="O96" s="139">
         <f t="shared" si="9"/>
-        <v>234995.82</v>
+        <v>253071.82</v>
       </c>
       <c r="P96" s="50">
         <f t="shared" si="8"/>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="J97" s="125">
         <f t="shared" si="18"/>
-        <v>40500.000000000007</v>
+        <v>60750</v>
       </c>
       <c r="K97" s="125">
         <f t="shared" si="20"/>
@@ -8899,11 +8899,11 @@
       <c r="M97" s="147"/>
       <c r="N97" s="86">
         <f t="shared" si="21"/>
-        <v>263250.83</v>
+        <v>283500.83</v>
       </c>
       <c r="O97" s="139">
         <f t="shared" si="9"/>
-        <v>271148.83</v>
+        <v>292005.83</v>
       </c>
       <c r="P97" s="50">
         <f t="shared" si="8"/>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="J98" s="125">
         <f t="shared" si="18"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K98" s="125">
         <f t="shared" si="20"/>
@@ -8950,11 +8950,11 @@
       <c r="M98" s="147"/>
       <c r="N98" s="86">
         <f t="shared" si="21"/>
-        <v>156465.84</v>
+        <v>173265.84</v>
       </c>
       <c r="O98" s="139">
         <f t="shared" si="9"/>
-        <v>161159.84</v>
+        <v>178463.84</v>
       </c>
       <c r="P98" s="50">
         <f t="shared" ref="P98:P117" si="22">P97+0.01</f>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="J99" s="125">
         <f t="shared" si="18"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K99" s="125">
         <f t="shared" si="20"/>
@@ -9004,11 +9004,11 @@
       <c r="M99" s="147"/>
       <c r="N99" s="86">
         <f t="shared" si="21"/>
-        <v>159900.85</v>
+        <v>172200.85</v>
       </c>
       <c r="O99" s="139">
         <f t="shared" si="9"/>
-        <v>164697.85</v>
+        <v>177366.85</v>
       </c>
       <c r="P99" s="50">
         <f t="shared" si="22"/>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="J100" s="126">
         <f t="shared" si="18"/>
-        <v>24600</v>
+        <v>36900</v>
       </c>
       <c r="K100" s="125">
         <f t="shared" si="20"/>
@@ -9057,11 +9057,11 @@
       <c r="M100" s="148"/>
       <c r="N100" s="112">
         <f t="shared" si="21"/>
-        <v>155472.85999999999</v>
+        <v>167772.86</v>
       </c>
       <c r="O100" s="140">
         <f t="shared" ref="O100:O117" si="23">ROUND(N100*3%,0) + N100</f>
-        <v>160136.85999999999</v>
+        <v>172805.86</v>
       </c>
       <c r="P100" s="50">
         <f t="shared" si="22"/>
@@ -9084,7 +9084,7 @@
         <v>241200.87</v>
       </c>
       <c r="F101" s="84">
-        <f t="shared" ref="F99:F104" si="25">E101</f>
+        <f t="shared" ref="F101:F104" si="25">E101</f>
         <v>241200.87</v>
       </c>
       <c r="G101" s="85">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="J101" s="125">
         <f t="shared" si="18"/>
-        <v>40200.000000000007</v>
+        <v>60300</v>
       </c>
       <c r="K101" s="125">
         <f t="shared" si="20"/>
@@ -9111,11 +9111,11 @@
       <c r="M101" s="147"/>
       <c r="N101" s="86">
         <f t="shared" si="21"/>
-        <v>261300.87</v>
+        <v>281400.87</v>
       </c>
       <c r="O101" s="139">
         <f t="shared" si="23"/>
-        <v>269139.87</v>
+        <v>289842.87</v>
       </c>
       <c r="P101" s="50">
         <f t="shared" si="22"/>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="J102" s="125">
         <f t="shared" si="18"/>
-        <v>33600.000000000007</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="K102" s="125">
         <f t="shared" si="20"/>
@@ -9165,11 +9165,11 @@
       <c r="M102" s="147"/>
       <c r="N102" s="86">
         <f t="shared" si="21"/>
-        <v>218400.88</v>
+        <v>235200.88</v>
       </c>
       <c r="O102" s="139">
         <f t="shared" si="23"/>
-        <v>224952.88</v>
+        <v>242256.88</v>
       </c>
       <c r="P102" s="50">
         <f t="shared" si="22"/>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="J103" s="125">
         <f t="shared" si="18"/>
-        <v>35100</v>
+        <v>52650</v>
       </c>
       <c r="K103" s="125">
         <f t="shared" si="20"/>
@@ -9219,11 +9219,11 @@
       <c r="M103" s="147"/>
       <c r="N103" s="86">
         <f t="shared" si="21"/>
-        <v>228150.89</v>
+        <v>245700.89</v>
       </c>
       <c r="O103" s="139">
         <f t="shared" si="23"/>
-        <v>234995.89</v>
+        <v>253071.89</v>
       </c>
       <c r="P103" s="50">
         <f t="shared" si="22"/>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="J104" s="125">
         <f t="shared" si="18"/>
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="K104" s="125">
         <f t="shared" si="20"/>
@@ -9273,11 +9273,11 @@
       <c r="M104" s="147"/>
       <c r="N104" s="86">
         <f t="shared" si="21"/>
-        <v>19500.900000000001</v>
+        <v>21000.9</v>
       </c>
       <c r="O104" s="139">
         <f t="shared" si="23"/>
-        <v>20085.900000000001</v>
+        <v>21630.9</v>
       </c>
       <c r="P104" s="50">
         <f t="shared" si="22"/>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="J105" s="125">
         <f t="shared" si="18"/>
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="K105" s="125">
         <f t="shared" si="20"/>
@@ -9326,11 +9326,11 @@
       <c r="M105" s="147"/>
       <c r="N105" s="86">
         <f t="shared" si="21"/>
-        <v>20010.91</v>
+        <v>21510.91</v>
       </c>
       <c r="O105" s="139">
         <f t="shared" si="23"/>
-        <v>20610.91</v>
+        <v>22155.91</v>
       </c>
       <c r="P105" s="50">
         <f t="shared" si="22"/>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="J106" s="125">
         <f t="shared" si="18"/>
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="K106" s="125">
         <f t="shared" si="20"/>
@@ -9379,11 +9379,11 @@
       <c r="M106" s="147"/>
       <c r="N106" s="86">
         <f t="shared" si="21"/>
-        <v>18975.919999999998</v>
+        <v>20475.919999999998</v>
       </c>
       <c r="O106" s="139">
         <f t="shared" si="23"/>
-        <v>19544.919999999998</v>
+        <v>21089.919999999998</v>
       </c>
       <c r="P106" s="50">
         <f t="shared" si="22"/>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="J107" s="126">
         <f t="shared" si="18"/>
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="K107" s="125">
         <f t="shared" si="20"/>
@@ -9432,11 +9432,11 @@
       <c r="M107" s="148"/>
       <c r="N107" s="86">
         <f t="shared" si="21"/>
-        <v>18975.93</v>
+        <v>20475.93</v>
       </c>
       <c r="O107" s="140">
         <f t="shared" si="23"/>
-        <v>19544.93</v>
+        <v>21089.93</v>
       </c>
       <c r="P107" s="50">
         <f t="shared" si="22"/>
@@ -9459,7 +9459,7 @@
         <v>18000.939999999999</v>
       </c>
       <c r="F108" s="84">
-        <f>E108</f>
+        <f t="shared" ref="F108:F113" si="26">E108</f>
         <v>18000.939999999999</v>
       </c>
       <c r="G108" s="111">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="J108" s="126">
         <f t="shared" si="18"/>
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="K108" s="125">
         <f t="shared" si="20"/>
@@ -9486,11 +9486,11 @@
       <c r="M108" s="148"/>
       <c r="N108" s="86">
         <f t="shared" si="21"/>
-        <v>19500.939999999999</v>
+        <v>21000.94</v>
       </c>
       <c r="O108" s="140">
         <f t="shared" si="23"/>
-        <v>20085.939999999999</v>
+        <v>21630.94</v>
       </c>
       <c r="P108" s="50">
         <f t="shared" si="22"/>
@@ -9513,7 +9513,7 @@
         <v>18000.95</v>
       </c>
       <c r="F109" s="84">
-        <f>E109</f>
+        <f t="shared" si="26"/>
         <v>18000.95</v>
       </c>
       <c r="G109" s="111">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="J109" s="126">
         <f t="shared" si="18"/>
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="K109" s="125">
         <f t="shared" si="20"/>
@@ -9540,11 +9540,11 @@
       <c r="M109" s="148"/>
       <c r="N109" s="86">
         <f t="shared" si="21"/>
-        <v>19500.95</v>
+        <v>21000.95</v>
       </c>
       <c r="O109" s="140">
         <f t="shared" si="23"/>
-        <v>20085.95</v>
+        <v>21630.95</v>
       </c>
       <c r="P109" s="50">
         <f t="shared" si="22"/>
@@ -9567,7 +9567,7 @@
         <v>17491.96</v>
       </c>
       <c r="F110" s="84">
-        <f>E110</f>
+        <f t="shared" si="26"/>
         <v>17491.96</v>
       </c>
       <c r="G110" s="111">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="J110" s="126">
         <f t="shared" si="18"/>
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="K110" s="125">
         <f t="shared" si="20"/>
@@ -9594,11 +9594,11 @@
       <c r="M110" s="148"/>
       <c r="N110" s="86">
         <f t="shared" si="21"/>
-        <v>19500.96</v>
+        <v>21000.959999999999</v>
       </c>
       <c r="O110" s="140">
         <f t="shared" si="23"/>
-        <v>20085.96</v>
+        <v>21630.959999999999</v>
       </c>
       <c r="P110" s="50">
         <f t="shared" si="22"/>
@@ -9624,7 +9624,7 @@
         <v>18000.97</v>
       </c>
       <c r="F111" s="84">
-        <f>E111</f>
+        <f t="shared" si="26"/>
         <v>18000.97</v>
       </c>
       <c r="G111" s="111">
@@ -9636,12 +9636,12 @@
         <v>0</v>
       </c>
       <c r="I111" s="126">
-        <f t="shared" ref="I111:I117" si="26">J$2*D111/100</f>
+        <f t="shared" ref="I111:I117" si="27">J$2*D111/100</f>
         <v>10553.069230000001</v>
       </c>
       <c r="J111" s="126">
-        <f t="shared" ref="J111:J117" si="27">E$2*D111/100</f>
-        <v>3000</v>
+        <f t="shared" ref="J111:J117" si="28">E$2*D111/100</f>
+        <v>4500</v>
       </c>
       <c r="K111" s="125">
         <f t="shared" si="20"/>
@@ -9651,11 +9651,11 @@
       <c r="M111" s="148"/>
       <c r="N111" s="86">
         <f t="shared" si="21"/>
-        <v>19500.97</v>
+        <v>21000.97</v>
       </c>
       <c r="O111" s="140">
         <f t="shared" si="23"/>
-        <v>20085.97</v>
+        <v>21630.97</v>
       </c>
       <c r="P111" s="50">
         <f t="shared" si="22"/>
@@ -9678,7 +9678,7 @@
         <v>18000.98</v>
       </c>
       <c r="F112" s="84">
-        <f>E112</f>
+        <f t="shared" si="26"/>
         <v>18000.98</v>
       </c>
       <c r="G112" s="111">
@@ -9690,12 +9690,12 @@
         <v>0</v>
       </c>
       <c r="I112" s="126">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10553.069230000001</v>
       </c>
       <c r="J112" s="126">
-        <f t="shared" si="27"/>
-        <v>3000</v>
+        <f t="shared" si="28"/>
+        <v>4500</v>
       </c>
       <c r="K112" s="125">
         <f t="shared" si="20"/>
@@ -9705,11 +9705,11 @@
       <c r="M112" s="148"/>
       <c r="N112" s="86">
         <f t="shared" si="21"/>
-        <v>19500.98</v>
+        <v>21000.98</v>
       </c>
       <c r="O112" s="140">
         <f t="shared" si="23"/>
-        <v>20085.98</v>
+        <v>21630.98</v>
       </c>
       <c r="P112" s="50">
         <f t="shared" si="22"/>
@@ -9732,7 +9732,7 @@
         <v>18000.990000000002</v>
       </c>
       <c r="F113" s="84">
-        <f>E113</f>
+        <f t="shared" si="26"/>
         <v>18000.990000000002</v>
       </c>
       <c r="G113" s="111">
@@ -9744,12 +9744,12 @@
         <v>0</v>
       </c>
       <c r="I113" s="126">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10553.069230000001</v>
       </c>
       <c r="J113" s="126">
-        <f t="shared" si="27"/>
-        <v>3000</v>
+        <f t="shared" si="28"/>
+        <v>4500</v>
       </c>
       <c r="K113" s="125">
         <f t="shared" si="20"/>
@@ -9759,11 +9759,11 @@
       <c r="M113" s="148"/>
       <c r="N113" s="86">
         <f t="shared" si="21"/>
-        <v>19500.990000000002</v>
+        <v>21000.99</v>
       </c>
       <c r="O113" s="140">
         <f t="shared" si="23"/>
-        <v>20085.990000000002</v>
+        <v>21630.99</v>
       </c>
       <c r="P113" s="50">
         <f t="shared" si="22"/>
@@ -9795,12 +9795,12 @@
         <v>1583.85</v>
       </c>
       <c r="I114" s="126">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10553.069230000001</v>
       </c>
       <c r="J114" s="126">
-        <f t="shared" si="27"/>
-        <v>3000</v>
+        <f t="shared" si="28"/>
+        <v>4500</v>
       </c>
       <c r="K114" s="125">
         <f t="shared" si="20"/>
@@ -9810,11 +9810,11 @@
       <c r="M114" s="148"/>
       <c r="N114" s="86">
         <f t="shared" si="21"/>
-        <v>73880</v>
+        <v>75380</v>
       </c>
       <c r="O114" s="140">
         <f t="shared" si="23"/>
-        <v>76096</v>
+        <v>77641</v>
       </c>
       <c r="P114" s="50">
         <f t="shared" si="22"/>
@@ -9848,12 +9848,12 @@
         <v>0</v>
       </c>
       <c r="I115" s="126">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10553.069230000001</v>
       </c>
       <c r="J115" s="126">
-        <f t="shared" si="27"/>
-        <v>3000</v>
+        <f t="shared" si="28"/>
+        <v>4500</v>
       </c>
       <c r="K115" s="125">
         <f t="shared" si="20"/>
@@ -9863,11 +9863,11 @@
       <c r="M115" s="148"/>
       <c r="N115" s="86">
         <f t="shared" si="21"/>
-        <v>18976.009999999998</v>
+        <v>20476.009999999998</v>
       </c>
       <c r="O115" s="140">
         <f t="shared" si="23"/>
-        <v>19545.009999999998</v>
+        <v>21090.01</v>
       </c>
       <c r="P115" s="50">
         <f t="shared" si="22"/>
@@ -9902,12 +9902,12 @@
         <v>0</v>
       </c>
       <c r="I116" s="126">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10553.069230000001</v>
       </c>
       <c r="J116" s="126">
-        <f t="shared" si="27"/>
-        <v>3000</v>
+        <f t="shared" si="28"/>
+        <v>4500</v>
       </c>
       <c r="K116" s="125">
         <f t="shared" si="20"/>
@@ -9917,11 +9917,11 @@
       <c r="M116" s="148"/>
       <c r="N116" s="86">
         <f t="shared" si="21"/>
-        <v>19501.02</v>
+        <v>21001.02</v>
       </c>
       <c r="O116" s="140">
         <f t="shared" si="23"/>
-        <v>20086.02</v>
+        <v>21631.02</v>
       </c>
       <c r="P116" s="50">
         <f t="shared" si="22"/>
@@ -9956,12 +9956,12 @@
         <v>0</v>
       </c>
       <c r="I117" s="126">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10553.069230000001</v>
       </c>
       <c r="J117" s="126">
-        <f t="shared" si="27"/>
-        <v>3000</v>
+        <f t="shared" si="28"/>
+        <v>4500</v>
       </c>
       <c r="K117" s="125">
         <f t="shared" si="20"/>
@@ -9971,11 +9971,11 @@
       <c r="M117" s="148"/>
       <c r="N117" s="86">
         <f t="shared" si="21"/>
-        <v>19501.03</v>
+        <v>21001.03</v>
       </c>
       <c r="O117" s="140">
         <f t="shared" si="23"/>
-        <v>20086.03</v>
+        <v>21631.03</v>
       </c>
       <c r="P117" s="50">
         <f t="shared" si="22"/>
@@ -10005,11 +10005,11 @@
       <c r="B119" s="133"/>
       <c r="C119" s="133"/>
       <c r="D119" s="134">
-        <f t="shared" ref="D119:O119" si="28">SUM(D15:D118)</f>
+        <f t="shared" ref="D119:O119" si="29">SUM(D15:D118)</f>
         <v>100.15999999999993</v>
       </c>
       <c r="E119" s="135">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>39778263.560000002</v>
       </c>
       <c r="F119" s="136">
@@ -10017,31 +10017,31 @@
         <v>15858930.739999998</v>
       </c>
       <c r="G119" s="136">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>23919332.82</v>
       </c>
       <c r="H119" s="136">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>677683.33949999989</v>
       </c>
       <c r="I119" s="137">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>10569954.140767993</v>
       </c>
       <c r="J119" s="136">
-        <f t="shared" si="28"/>
-        <v>3004800</v>
+        <f t="shared" si="29"/>
+        <v>4507200</v>
       </c>
       <c r="K119" s="138"/>
       <c r="L119" s="138"/>
       <c r="M119" s="150"/>
       <c r="N119" s="145">
-        <f t="shared" si="28"/>
-        <v>45149570.56000001</v>
+        <f t="shared" si="29"/>
+        <v>46651970.56000001</v>
       </c>
       <c r="O119" s="142">
-        <f t="shared" si="28"/>
-        <v>46504061.560000002</v>
+        <f t="shared" si="29"/>
+        <v>48051527.560000002</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10050,96 +10050,96 @@
     </row>
     <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="237" t="s">
+      <c r="B122" s="268" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="237"/>
-      <c r="D122" s="237"/>
-      <c r="E122" s="237"/>
-      <c r="F122" s="237"/>
-      <c r="G122" s="237"/>
-      <c r="H122" s="237"/>
-      <c r="I122" s="237"/>
-      <c r="J122" s="237"/>
-      <c r="K122" s="237"/>
-      <c r="L122" s="237"/>
-      <c r="M122" s="237"/>
-      <c r="N122" s="237"/>
+      <c r="C122" s="268"/>
+      <c r="D122" s="268"/>
+      <c r="E122" s="268"/>
+      <c r="F122" s="268"/>
+      <c r="G122" s="268"/>
+      <c r="H122" s="268"/>
+      <c r="I122" s="268"/>
+      <c r="J122" s="268"/>
+      <c r="K122" s="268"/>
+      <c r="L122" s="268"/>
+      <c r="M122" s="268"/>
+      <c r="N122" s="268"/>
     </row>
     <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="237"/>
-      <c r="C123" s="237"/>
-      <c r="D123" s="237"/>
-      <c r="E123" s="237"/>
-      <c r="F123" s="237"/>
-      <c r="G123" s="237"/>
-      <c r="H123" s="237"/>
-      <c r="I123" s="237"/>
-      <c r="J123" s="237"/>
-      <c r="K123" s="237"/>
-      <c r="L123" s="237"/>
-      <c r="M123" s="237"/>
-      <c r="N123" s="237"/>
+      <c r="B123" s="268"/>
+      <c r="C123" s="268"/>
+      <c r="D123" s="268"/>
+      <c r="E123" s="268"/>
+      <c r="F123" s="268"/>
+      <c r="G123" s="268"/>
+      <c r="H123" s="268"/>
+      <c r="I123" s="268"/>
+      <c r="J123" s="268"/>
+      <c r="K123" s="268"/>
+      <c r="L123" s="268"/>
+      <c r="M123" s="268"/>
+      <c r="N123" s="268"/>
     </row>
     <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="237"/>
-      <c r="C124" s="237"/>
-      <c r="D124" s="237"/>
-      <c r="E124" s="237"/>
-      <c r="F124" s="237"/>
-      <c r="G124" s="237"/>
-      <c r="H124" s="237"/>
-      <c r="I124" s="237"/>
-      <c r="J124" s="237"/>
-      <c r="K124" s="237"/>
-      <c r="L124" s="237"/>
-      <c r="M124" s="237"/>
-      <c r="N124" s="237"/>
+      <c r="B124" s="268"/>
+      <c r="C124" s="268"/>
+      <c r="D124" s="268"/>
+      <c r="E124" s="268"/>
+      <c r="F124" s="268"/>
+      <c r="G124" s="268"/>
+      <c r="H124" s="268"/>
+      <c r="I124" s="268"/>
+      <c r="J124" s="268"/>
+      <c r="K124" s="268"/>
+      <c r="L124" s="268"/>
+      <c r="M124" s="268"/>
+      <c r="N124" s="268"/>
     </row>
     <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="237"/>
-      <c r="C125" s="237"/>
-      <c r="D125" s="237"/>
-      <c r="E125" s="237"/>
-      <c r="F125" s="237"/>
-      <c r="G125" s="237"/>
-      <c r="H125" s="237"/>
-      <c r="I125" s="237"/>
-      <c r="J125" s="237"/>
-      <c r="K125" s="237"/>
-      <c r="L125" s="237"/>
-      <c r="M125" s="237"/>
-      <c r="N125" s="237"/>
+      <c r="B125" s="268"/>
+      <c r="C125" s="268"/>
+      <c r="D125" s="268"/>
+      <c r="E125" s="268"/>
+      <c r="F125" s="268"/>
+      <c r="G125" s="268"/>
+      <c r="H125" s="268"/>
+      <c r="I125" s="268"/>
+      <c r="J125" s="268"/>
+      <c r="K125" s="268"/>
+      <c r="L125" s="268"/>
+      <c r="M125" s="268"/>
+      <c r="N125" s="268"/>
     </row>
     <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="237"/>
-      <c r="C126" s="237"/>
-      <c r="D126" s="237"/>
-      <c r="E126" s="237"/>
-      <c r="F126" s="237"/>
-      <c r="G126" s="237"/>
-      <c r="H126" s="237"/>
-      <c r="I126" s="237"/>
-      <c r="J126" s="237"/>
-      <c r="K126" s="237"/>
-      <c r="L126" s="237"/>
-      <c r="M126" s="237"/>
-      <c r="N126" s="237"/>
+      <c r="B126" s="268"/>
+      <c r="C126" s="268"/>
+      <c r="D126" s="268"/>
+      <c r="E126" s="268"/>
+      <c r="F126" s="268"/>
+      <c r="G126" s="268"/>
+      <c r="H126" s="268"/>
+      <c r="I126" s="268"/>
+      <c r="J126" s="268"/>
+      <c r="K126" s="268"/>
+      <c r="L126" s="268"/>
+      <c r="M126" s="268"/>
+      <c r="N126" s="268"/>
     </row>
     <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="237"/>
-      <c r="C127" s="237"/>
-      <c r="D127" s="237"/>
-      <c r="E127" s="237"/>
-      <c r="F127" s="237"/>
-      <c r="G127" s="237"/>
-      <c r="H127" s="237"/>
-      <c r="I127" s="237"/>
-      <c r="J127" s="237"/>
-      <c r="K127" s="237"/>
-      <c r="L127" s="237"/>
-      <c r="M127" s="237"/>
-      <c r="N127" s="237"/>
+      <c r="B127" s="268"/>
+      <c r="C127" s="268"/>
+      <c r="D127" s="268"/>
+      <c r="E127" s="268"/>
+      <c r="F127" s="268"/>
+      <c r="G127" s="268"/>
+      <c r="H127" s="268"/>
+      <c r="I127" s="268"/>
+      <c r="J127" s="268"/>
+      <c r="K127" s="268"/>
+      <c r="L127" s="268"/>
+      <c r="M127" s="268"/>
+      <c r="N127" s="268"/>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B130">
@@ -10150,7 +10150,7 @@
       <c r="A134" t="s">
         <v>261</v>
       </c>
-      <c r="B134" s="281">
+      <c r="B134" s="218">
         <v>-3942</v>
       </c>
     </row>
@@ -10164,12 +10164,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="K13:K14"/>
     <mergeCell ref="B122:N127"/>
     <mergeCell ref="D1:N1"/>
     <mergeCell ref="A4:O8"/>
@@ -10186,6 +10180,12 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="K13:K14"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
@@ -10270,30 +10270,30 @@
       <c r="N7" s="19"/>
     </row>
     <row r="8" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C8" s="275" t="s">
+      <c r="C8" s="294" t="s">
         <v>220</v>
       </c>
-      <c r="D8" s="276"/>
-      <c r="E8" s="276"/>
-      <c r="F8" s="276"/>
-      <c r="G8" s="276"/>
-      <c r="H8" s="276"/>
-      <c r="I8" s="276"/>
-      <c r="J8" s="277"/>
+      <c r="D8" s="295"/>
+      <c r="E8" s="295"/>
+      <c r="F8" s="295"/>
+      <c r="G8" s="295"/>
+      <c r="H8" s="295"/>
+      <c r="I8" s="295"/>
+      <c r="J8" s="296"/>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
     </row>
     <row r="9" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="278"/>
-      <c r="D9" s="279"/>
-      <c r="E9" s="279"/>
-      <c r="F9" s="279"/>
-      <c r="G9" s="279"/>
-      <c r="H9" s="279"/>
-      <c r="I9" s="279"/>
-      <c r="J9" s="280"/>
+      <c r="C9" s="297"/>
+      <c r="D9" s="298"/>
+      <c r="E9" s="298"/>
+      <c r="F9" s="298"/>
+      <c r="G9" s="298"/>
+      <c r="H9" s="298"/>
+      <c r="I9" s="298"/>
+      <c r="J9" s="299"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>

--- a/2026/ITALIA/Julio/Julio ITALIA.xlsx
+++ b/2026/ITALIA/Julio/Julio ITALIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE53F25F-640C-4BA8-AD0A-3592E9976EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54616E8F-50FE-4340-B274-71DB34F1CE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -22,6 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$144</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2118,204 +2123,6 @@
     <xf numFmtId="0" fontId="16" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2336,6 +2143,204 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -2422,9 +2427,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2462,9 +2467,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2497,9 +2502,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2532,9 +2554,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2709,31 +2748,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M145"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="261" t="s">
+      <c r="B1" s="270" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="261"/>
-      <c r="D1" s="261"/>
-      <c r="E1" s="262"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1" s="270"/>
+      <c r="D1" s="270"/>
+      <c r="E1" s="271"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="9" t="s">
         <v>148</v>
@@ -2742,16 +2781,16 @@
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="265" t="s">
+      <c r="B3" s="276" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="265"/>
-      <c r="D3" s="265"/>
-      <c r="E3" s="266"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="276"/>
+      <c r="D3" s="276"/>
+      <c r="E3" s="277"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>100</v>
       </c>
@@ -2762,7 +2801,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>147</v>
       </c>
@@ -2775,7 +2814,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="90" t="s">
         <v>137</v>
       </c>
@@ -2786,95 +2825,95 @@
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="48"/>
-      <c r="B8" s="267" t="s">
+      <c r="B8" s="278" t="s">
         <v>220</v>
       </c>
-      <c r="C8" s="267"/>
+      <c r="C8" s="278"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="48"/>
-      <c r="B9" s="267"/>
-      <c r="C9" s="267"/>
+      <c r="B9" s="278"/>
+      <c r="C9" s="278"/>
       <c r="D9" s="48"/>
       <c r="E9" s="48"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="48"/>
-      <c r="B10" s="267"/>
-      <c r="C10" s="267"/>
+      <c r="B10" s="278"/>
+      <c r="C10" s="278"/>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="48"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
       <c r="E11" s="48"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="48"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
       <c r="D12" s="48"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="268" t="s">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="279" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="268"/>
-      <c r="C13" s="268"/>
-      <c r="D13" s="268"/>
-      <c r="E13" s="268"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="268"/>
-      <c r="B14" s="268"/>
-      <c r="C14" s="268"/>
-      <c r="D14" s="268"/>
-      <c r="E14" s="268"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="268"/>
-      <c r="B15" s="268"/>
-      <c r="C15" s="268"/>
-      <c r="D15" s="268"/>
-      <c r="E15" s="268"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="268"/>
-      <c r="B16" s="268"/>
-      <c r="C16" s="268"/>
-      <c r="D16" s="268"/>
-      <c r="E16" s="268"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="279"/>
+      <c r="C13" s="279"/>
+      <c r="D13" s="279"/>
+      <c r="E13" s="279"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="279"/>
+      <c r="B14" s="279"/>
+      <c r="C14" s="279"/>
+      <c r="D14" s="279"/>
+      <c r="E14" s="279"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="279"/>
+      <c r="B15" s="279"/>
+      <c r="C15" s="279"/>
+      <c r="D15" s="279"/>
+      <c r="E15" s="279"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="279"/>
+      <c r="B16" s="279"/>
+      <c r="C16" s="279"/>
+      <c r="D16" s="279"/>
+      <c r="E16" s="279"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
       <c r="E17" s="48"/>
     </row>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="177"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="178" t="s">
         <v>104</v>
       </c>
@@ -2883,7 +2922,7 @@
       <c r="D20" s="58"/>
       <c r="E20" s="59"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
         <v>138</v>
       </c>
@@ -2892,11 +2931,11 @@
       <c r="D21" s="117"/>
       <c r="E21" s="151"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="263" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="272" t="s">
         <v>161</v>
       </c>
-      <c r="B22" s="264"/>
+      <c r="B22" s="273"/>
       <c r="C22" s="181"/>
       <c r="D22" s="182">
         <v>2337709.7000000002</v>
@@ -2904,11 +2943,11 @@
       <c r="E22" s="152"/>
       <c r="H22" s="19"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="263" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="272" t="s">
         <v>162</v>
       </c>
-      <c r="B23" s="264"/>
+      <c r="B23" s="273"/>
       <c r="C23" s="181"/>
       <c r="D23" s="182">
         <v>-508451.7</v>
@@ -2916,11 +2955,11 @@
       <c r="E23" s="20"/>
       <c r="H23" s="19"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="263" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="272" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="264"/>
+      <c r="B24" s="273"/>
       <c r="C24" s="181"/>
       <c r="D24" s="183">
         <v>0</v>
@@ -2933,7 +2972,7 @@
       </c>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="184" t="s">
         <v>105</v>
       </c>
@@ -2945,7 +2984,7 @@
         <v>1829258.0000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="184" t="s">
         <v>176</v>
       </c>
@@ -2954,35 +2993,35 @@
       <c r="D26" s="22"/>
       <c r="E26" s="154"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="181"/>
       <c r="B27" s="181"/>
       <c r="C27" s="181"/>
       <c r="D27" s="35"/>
       <c r="E27" s="167"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="181"/>
       <c r="B28" s="181"/>
       <c r="C28" s="181"/>
       <c r="D28" s="35"/>
       <c r="E28" s="167"/>
     </row>
-    <row r="29" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="181"/>
       <c r="B29" s="181"/>
       <c r="C29" s="181"/>
       <c r="D29" s="35"/>
       <c r="E29" s="167"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="181"/>
       <c r="B30" s="181"/>
       <c r="C30" s="181"/>
       <c r="D30" s="35"/>
       <c r="E30" s="155"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="181" t="s">
         <v>241</v>
       </c>
@@ -2997,7 +3036,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="181" t="s">
         <v>244</v>
       </c>
@@ -3010,7 +3049,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="184" t="s">
         <v>105</v>
       </c>
@@ -3022,7 +3061,7 @@
         <v>130087</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
         <v>139</v>
       </c>
@@ -3031,7 +3070,7 @@
       <c r="D34" s="22"/>
       <c r="E34" s="154"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="181" t="s">
         <v>252</v>
       </c>
@@ -3046,7 +3085,7 @@
       </c>
       <c r="G35" s="66"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="181" t="s">
         <v>253</v>
       </c>
@@ -3058,7 +3097,7 @@
       <c r="E36" s="155"/>
       <c r="G36" s="66"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="181" t="s">
         <v>141</v>
       </c>
@@ -3072,7 +3111,7 @@
       </c>
       <c r="G37" s="66"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="181" t="s">
         <v>143</v>
       </c>
@@ -3087,7 +3126,7 @@
       </c>
       <c r="G38" s="50"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>142</v>
       </c>
@@ -3101,7 +3140,7 @@
         <v>Debito 13/07</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="181" t="s">
         <v>149</v>
       </c>
@@ -3110,7 +3149,7 @@
       <c r="D40" s="35"/>
       <c r="E40" s="155"/>
     </row>
-    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="184" t="s">
         <v>140</v>
       </c>
@@ -3122,7 +3161,7 @@
         <v>473894.69</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>106</v>
       </c>
@@ -3131,11 +3170,11 @@
       <c r="D42" s="23"/>
       <c r="E42" s="156"/>
     </row>
-    <row r="43" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="256" t="s">
+    <row r="43" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="280" t="s">
         <v>183</v>
       </c>
-      <c r="B43" s="257"/>
+      <c r="B43" s="281"/>
       <c r="C43" s="26"/>
       <c r="D43" s="229">
         <v>7805</v>
@@ -3144,11 +3183,11 @@
         <v>184</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="256" t="s">
+    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="280" t="s">
         <v>185</v>
       </c>
-      <c r="B44" s="257"/>
+      <c r="B44" s="281"/>
       <c r="C44" s="26"/>
       <c r="D44" s="229">
         <v>213891</v>
@@ -3157,7 +3196,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
         <v>107</v>
       </c>
@@ -3169,7 +3208,7 @@
         <v>221696</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>108</v>
       </c>
@@ -3178,7 +3217,7 @@
       <c r="D46" s="28"/>
       <c r="E46" s="157"/>
     </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
         <v>109</v>
       </c>
@@ -3193,7 +3232,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
         <v>109</v>
       </c>
@@ -3208,7 +3247,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="29" t="s">
         <v>177</v>
       </c>
@@ -3221,7 +3260,7 @@
       </c>
       <c r="E49" s="20"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
         <v>178</v>
       </c>
@@ -3232,11 +3271,11 @@
       </c>
       <c r="E50" s="20"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="256" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="280" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="257"/>
+      <c r="B51" s="281"/>
       <c r="C51" s="29"/>
       <c r="D51" s="30">
         <v>5946930.7699999996</v>
@@ -3249,7 +3288,7 @@
         <v>283942</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="32" t="s">
         <v>111</v>
       </c>
@@ -3258,7 +3297,7 @@
       <c r="D52" s="30"/>
       <c r="E52" s="20"/>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="21" t="s">
         <v>112</v>
       </c>
@@ -3270,18 +3309,18 @@
         <v>7374026.3499999996</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="22"/>
       <c r="E54" s="159"/>
     </row>
-    <row r="55" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="258" t="s">
+    <row r="55" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="274" t="s">
         <v>164</v>
       </c>
-      <c r="B55" s="259"/>
+      <c r="B55" s="275"/>
       <c r="C55" s="29"/>
       <c r="D55" s="30">
         <v>285000</v>
@@ -3290,11 +3329,11 @@
         <v>228</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="258" t="s">
+    <row r="56" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="274" t="s">
         <v>249</v>
       </c>
-      <c r="B56" s="259"/>
+      <c r="B56" s="275"/>
       <c r="C56" s="29"/>
       <c r="D56" s="30">
         <v>280000</v>
@@ -3303,11 +3342,11 @@
         <v>248</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="186.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="258" t="s">
+    <row r="57" spans="1:6" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="274" t="s">
         <v>236</v>
       </c>
-      <c r="B57" s="259"/>
+      <c r="B57" s="275"/>
       <c r="C57" s="29"/>
       <c r="D57" s="30">
         <v>1400000</v>
@@ -3315,7 +3354,7 @@
       <c r="E57" s="166"/>
       <c r="F57" s="50"/>
     </row>
-    <row r="58" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="92" t="s">
         <v>225</v>
       </c>
@@ -3332,11 +3371,11 @@
         <v>148946.88</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="258" t="s">
+    <row r="59" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="274" t="s">
         <v>239</v>
       </c>
-      <c r="B59" s="259"/>
+      <c r="B59" s="275"/>
       <c r="C59" s="29"/>
       <c r="D59" s="30">
         <v>687000</v>
@@ -3346,7 +3385,7 @@
       </c>
       <c r="F59" s="50"/>
     </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
         <v>217</v>
       </c>
@@ -3358,7 +3397,7 @@
       <c r="E60" s="34"/>
       <c r="F60" s="218"/>
     </row>
-    <row r="61" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="92" t="s">
         <v>210</v>
       </c>
@@ -3372,7 +3411,7 @@
       </c>
       <c r="F61" s="50"/>
     </row>
-    <row r="62" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="92" t="s">
         <v>229</v>
       </c>
@@ -3386,7 +3425,7 @@
       </c>
       <c r="F62" s="50"/>
     </row>
-    <row r="63" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="92" t="s">
         <v>209</v>
       </c>
@@ -3400,7 +3439,7 @@
       </c>
       <c r="F63" s="50"/>
     </row>
-    <row r="64" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="92" t="s">
         <v>211</v>
       </c>
@@ -3414,7 +3453,7 @@
       </c>
       <c r="F64" s="50"/>
     </row>
-    <row r="65" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="92" t="s">
         <v>209</v>
       </c>
@@ -3428,11 +3467,11 @@
       </c>
       <c r="F65" s="50"/>
     </row>
-    <row r="66" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="258" t="s">
+    <row r="66" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="274" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="259"/>
+      <c r="B66" s="275"/>
       <c r="C66" s="29"/>
       <c r="D66" s="30">
         <v>138600</v>
@@ -3442,7 +3481,7 @@
       </c>
       <c r="F66" s="50"/>
     </row>
-    <row r="67" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="92" t="s">
         <v>227</v>
       </c>
@@ -3456,7 +3495,7 @@
       </c>
       <c r="F67" s="50"/>
     </row>
-    <row r="68" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="92" t="s">
         <v>235</v>
       </c>
@@ -3470,7 +3509,7 @@
       </c>
       <c r="F68" s="50"/>
     </row>
-    <row r="69" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="92" t="s">
         <v>238</v>
       </c>
@@ -3484,11 +3523,11 @@
       </c>
       <c r="F69" s="50"/>
     </row>
-    <row r="70" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="258" t="s">
+    <row r="70" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="274" t="s">
         <v>264</v>
       </c>
-      <c r="B70" s="259"/>
+      <c r="B70" s="275"/>
       <c r="C70" s="29"/>
       <c r="D70" s="30">
         <v>85000</v>
@@ -3496,7 +3535,7 @@
       <c r="E70" s="166"/>
       <c r="F70" s="50"/>
     </row>
-    <row r="71" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="92" t="s">
         <v>200</v>
       </c>
@@ -3510,11 +3549,11 @@
       </c>
       <c r="F71" s="50"/>
     </row>
-    <row r="72" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="258" t="s">
+    <row r="72" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="274" t="s">
         <v>208</v>
       </c>
-      <c r="B72" s="259"/>
+      <c r="B72" s="275"/>
       <c r="C72" s="29"/>
       <c r="D72" s="30">
         <v>124611.12</v>
@@ -3524,11 +3563,11 @@
       </c>
       <c r="F72" s="50"/>
     </row>
-    <row r="73" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="258" t="s">
+    <row r="73" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="274" t="s">
         <v>222</v>
       </c>
-      <c r="B73" s="259"/>
+      <c r="B73" s="275"/>
       <c r="C73" s="29"/>
       <c r="D73" s="30">
         <v>124611.12</v>
@@ -3538,7 +3577,7 @@
       </c>
       <c r="F73" s="50"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="21" t="s">
         <v>0</v>
       </c>
@@ -3550,7 +3589,7 @@
         <v>4840462.24</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
         <v>113</v>
       </c>
@@ -3559,11 +3598,11 @@
       <c r="D75" s="15"/>
       <c r="E75" s="151"/>
     </row>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="258" t="s">
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="274" t="s">
         <v>223</v>
       </c>
-      <c r="B76" s="259"/>
+      <c r="B76" s="275"/>
       <c r="C76" s="18"/>
       <c r="D76" s="230">
         <v>650000</v>
@@ -3575,11 +3614,11 @@
         <v>237</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="258" t="s">
+    <row r="77" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="274" t="s">
         <v>234</v>
       </c>
-      <c r="B77" s="259"/>
+      <c r="B77" s="275"/>
       <c r="C77" s="18"/>
       <c r="D77" s="231">
         <v>50000</v>
@@ -3588,7 +3627,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
         <v>163</v>
       </c>
@@ -3601,7 +3640,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="92" t="s">
         <v>247</v>
       </c>
@@ -3614,7 +3653,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="92" t="s">
         <v>224</v>
       </c>
@@ -3627,7 +3666,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="21" t="s">
         <v>105</v>
       </c>
@@ -3639,7 +3678,7 @@
         <v>1484217.8</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="14" t="s">
         <v>114</v>
       </c>
@@ -3648,7 +3687,7 @@
       <c r="D82" s="38"/>
       <c r="E82" s="41"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="29" t="s">
         <v>251</v>
       </c>
@@ -3660,18 +3699,18 @@
       </c>
       <c r="E83" s="160"/>
     </row>
-    <row r="84" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="256" t="s">
+    <row r="84" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="280" t="s">
         <v>250</v>
       </c>
-      <c r="B84" s="257"/>
+      <c r="B84" s="281"/>
       <c r="C84" s="91"/>
       <c r="D84" s="232">
         <v>225591.15</v>
       </c>
       <c r="E84" s="160"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="39" t="s">
         <v>105</v>
       </c>
@@ -3683,14 +3722,14 @@
         <v>322988.87</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="29"/>
       <c r="B86" s="29"/>
       <c r="C86" s="29"/>
       <c r="D86" s="42"/>
       <c r="E86" s="43"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="44" t="s">
         <v>115</v>
       </c>
@@ -3701,13 +3740,13 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="47"/>
       <c r="D88" s="48"/>
       <c r="E88" s="49"/>
       <c r="F88" s="50"/>
     </row>
-    <row r="89" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="51" t="s">
         <v>116</v>
       </c>
@@ -3721,16 +3760,16 @@
       <c r="F89" s="56"/>
       <c r="G89" s="50"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D90" s="48"/>
       <c r="E90" s="48"/>
     </row>
-    <row r="91" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D91" s="48"/>
       <c r="E91" s="48"/>
       <c r="H91" s="57"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
         <v>117</v>
       </c>
@@ -3739,34 +3778,34 @@
       <c r="D92" s="58"/>
       <c r="E92" s="59"/>
     </row>
-    <row r="93" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="260"/>
-      <c r="B93" s="260"/>
+    <row r="93" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="286"/>
+      <c r="B93" s="286"/>
       <c r="C93" s="31"/>
-      <c r="D93" s="252"/>
-      <c r="E93" s="254"/>
-    </row>
-    <row r="94" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="260"/>
-      <c r="B94" s="260"/>
+      <c r="D93" s="282"/>
+      <c r="E93" s="284"/>
+    </row>
+    <row r="94" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="286"/>
+      <c r="B94" s="286"/>
       <c r="C94" s="31"/>
-      <c r="D94" s="253"/>
-      <c r="E94" s="255"/>
-    </row>
-    <row r="95" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D94" s="283"/>
+      <c r="E94" s="285"/>
+    </row>
+    <row r="95" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="29"/>
       <c r="B95" s="29"/>
       <c r="D95" s="42"/>
       <c r="E95" s="42"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="24"/>
       <c r="B96" s="61"/>
       <c r="C96" s="29"/>
       <c r="D96" s="35"/>
       <c r="E96" s="60"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="62" t="s">
         <v>145</v>
       </c>
@@ -3778,15 +3817,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D98" s="48"/>
       <c r="E98" s="48"/>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="D99" s="48"/>
       <c r="E99" s="48"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="44" t="s">
         <v>118</v>
       </c>
@@ -3797,11 +3836,11 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D101" s="48"/>
       <c r="E101" s="48"/>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="51" t="s">
         <v>119</v>
       </c>
@@ -3813,11 +3852,11 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D103" s="48"/>
       <c r="E103" s="48"/>
     </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="64" t="s">
         <v>120</v>
       </c>
@@ -3828,7 +3867,7 @@
       <c r="D104" s="48"/>
       <c r="E104" s="48"/>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="64" t="s">
         <v>121</v>
       </c>
@@ -3839,7 +3878,7 @@
       <c r="D105" s="48"/>
       <c r="E105" s="48"/>
     </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="64" t="s">
         <v>122</v>
       </c>
@@ -3850,7 +3889,7 @@
       <c r="D106" s="48"/>
       <c r="E106" s="48"/>
     </row>
-    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="64" t="s">
         <v>123</v>
       </c>
@@ -3861,143 +3900,143 @@
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D108" s="48"/>
       <c r="E108" s="48"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D109" s="48"/>
       <c r="E109" s="48"/>
     </row>
-    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="270" t="s">
+    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="269" t="s">
         <v>172</v>
       </c>
-      <c r="B110" s="270"/>
+      <c r="B110" s="269"/>
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
     </row>
-    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="270"/>
-      <c r="B111" s="270"/>
+    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="269"/>
+      <c r="B111" s="269"/>
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
     </row>
-    <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="270"/>
-      <c r="B112" s="270"/>
+    <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="269"/>
+      <c r="B112" s="269"/>
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
     </row>
-    <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="270" t="s">
+    <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="269" t="s">
         <v>199</v>
       </c>
-      <c r="B114" s="270"/>
+      <c r="B114" s="269"/>
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
-    <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="270"/>
-      <c r="B115" s="270"/>
+    <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="269"/>
+      <c r="B115" s="269"/>
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
-    <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="270"/>
-      <c r="B116" s="270"/>
+    <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="269"/>
+      <c r="B116" s="269"/>
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
     </row>
-    <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
       <c r="F117" s="217"/>
     </row>
-    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="270" t="s">
+    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="269" t="s">
         <v>179</v>
       </c>
-      <c r="B118" s="270"/>
+      <c r="B118" s="269"/>
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
     </row>
-    <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="270"/>
-      <c r="B119" s="270"/>
+    <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="269"/>
+      <c r="B119" s="269"/>
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
-    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="270"/>
-      <c r="B120" s="270"/>
+    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="269"/>
+      <c r="B120" s="269"/>
       <c r="D120" s="48"/>
       <c r="E120" s="48"/>
     </row>
-    <row r="121" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
     </row>
-    <row r="122" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="270" t="s">
+    <row r="122" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="269" t="s">
         <v>182</v>
       </c>
-      <c r="B122" s="270"/>
+      <c r="B122" s="269"/>
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
     </row>
-    <row r="123" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="270"/>
-      <c r="B123" s="270"/>
+    <row r="123" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="269"/>
+      <c r="B123" s="269"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
     </row>
-    <row r="124" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="270"/>
-      <c r="B124" s="270"/>
+    <row r="124" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="269"/>
+      <c r="B124" s="269"/>
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
     </row>
-    <row r="125" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
     </row>
-    <row r="126" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="270" t="s">
+    <row r="126" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="269" t="s">
         <v>181</v>
       </c>
-      <c r="B126" s="270"/>
+      <c r="B126" s="269"/>
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
     </row>
-    <row r="127" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="270"/>
-      <c r="B127" s="270"/>
+    <row r="127" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="269"/>
+      <c r="B127" s="269"/>
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="270"/>
-      <c r="B128" s="270"/>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="269"/>
+      <c r="B128" s="269"/>
       <c r="D128" s="48"/>
       <c r="E128" s="48"/>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D129" s="48"/>
       <c r="E129" s="48"/>
     </row>
-    <row r="130" spans="1:6" s="68" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" s="68" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
       <c r="B130" s="66"/>
       <c r="C130" s="67"/>
       <c r="D130" s="162"/>
       <c r="E130" s="162"/>
     </row>
-    <row r="131" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="168" t="s">
         <v>189</v>
       </c>
@@ -4008,7 +4047,7 @@
       <c r="D131" s="163"/>
       <c r="E131" s="163"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="26" t="s">
         <v>144</v>
       </c>
@@ -4019,7 +4058,7 @@
       <c r="D132" s="48"/>
       <c r="E132" s="48"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="26" t="s">
         <v>124</v>
       </c>
@@ -4031,19 +4070,19 @@
       <c r="E133" s="48"/>
       <c r="F133" s="66"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="26" t="s">
         <v>2</v>
       </c>
       <c r="B134" s="71">
         <f>PRORRATEO!F119</f>
-        <v>15926490.739999998</v>
+        <v>16391721.119999999</v>
       </c>
       <c r="D134" s="48"/>
       <c r="E134" s="48"/>
       <c r="F134" s="66"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="26" t="s">
         <v>260</v>
       </c>
@@ -4054,7 +4093,7 @@
       <c r="E135" s="48"/>
       <c r="F135" s="66"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="26" t="s">
         <v>259</v>
       </c>
@@ -4065,32 +4104,32 @@
       <c r="E136" s="48"/>
       <c r="F136" s="66"/>
     </row>
-    <row r="137" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="72" t="s">
         <v>160</v>
       </c>
       <c r="B137" s="73">
         <f>SUM(B131:C136)</f>
-        <v>1224859.7399999946</v>
+        <v>1690090.1199999955</v>
       </c>
       <c r="D137" s="66"/>
       <c r="E137" s="50"/>
       <c r="F137" s="50"/>
     </row>
-    <row r="138" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="269" t="s">
+    <row r="138" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="268" t="s">
         <v>125</v>
       </c>
-      <c r="B139" s="269"/>
-      <c r="C139" s="269"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="269"/>
-      <c r="B140" s="269"/>
-      <c r="C140" s="269"/>
-    </row>
-    <row r="141" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B139" s="268"/>
+      <c r="C139" s="268"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="268"/>
+      <c r="B140" s="268"/>
+      <c r="C140" s="268"/>
+    </row>
+    <row r="141" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="74" t="s">
         <v>254</v>
       </c>
@@ -4100,7 +4139,7 @@
       <c r="C141" s="75"/>
       <c r="D141" s="56"/>
     </row>
-    <row r="142" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="74" t="s">
         <v>257</v>
       </c>
@@ -4110,7 +4149,7 @@
       <c r="C142" s="75"/>
       <c r="D142" s="56"/>
     </row>
-    <row r="143" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="74" t="s">
         <v>258</v>
       </c>
@@ -4120,7 +4159,7 @@
       <c r="C143" s="75"/>
       <c r="D143" s="56"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="76" t="s">
         <v>0</v>
       </c>
@@ -4130,17 +4169,19 @@
       </c>
       <c r="C144" s="78"/>
     </row>
-    <row r="145" spans="13:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M145" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A139:C140"/>
-    <mergeCell ref="A114:B116"/>
-    <mergeCell ref="A126:B128"/>
-    <mergeCell ref="A122:B124"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="A118:B120"/>
+    <mergeCell ref="D93:D94"/>
+    <mergeCell ref="E93:E94"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A93:B94"/>
+    <mergeCell ref="A70:B70"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A76:B76"/>
@@ -4157,14 +4198,12 @@
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="A72:B72"/>
-    <mergeCell ref="D93:D94"/>
-    <mergeCell ref="E93:E94"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A93:B94"/>
-    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A139:C140"/>
+    <mergeCell ref="A114:B116"/>
+    <mergeCell ref="A126:B128"/>
+    <mergeCell ref="A122:B124"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="A118:B120"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4175,55 +4214,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:Q135"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="11" width="16.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" customWidth="1"/>
-    <col min="13" max="13" width="16.109375" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="11" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="93"/>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
-      <c r="D1" s="272"/>
-      <c r="E1" s="272"/>
-      <c r="F1" s="272"/>
-      <c r="G1" s="272"/>
-      <c r="H1" s="272"/>
-      <c r="I1" s="272"/>
-      <c r="J1" s="272"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="272"/>
-      <c r="M1" s="272"/>
-      <c r="N1" s="272"/>
+      <c r="D1" s="302"/>
+      <c r="E1" s="302"/>
+      <c r="F1" s="302"/>
+      <c r="G1" s="302"/>
+      <c r="H1" s="302"/>
+      <c r="I1" s="302"/>
+      <c r="J1" s="302"/>
+      <c r="K1" s="302"/>
+      <c r="L1" s="302"/>
+      <c r="M1" s="302"/>
+      <c r="N1" s="302"/>
       <c r="O1" s="95"/>
     </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="96"/>
       <c r="B2" s="97"/>
       <c r="C2" s="98"/>
       <c r="D2" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="296">
+      <c r="E2" s="324">
         <v>4500000</v>
       </c>
-      <c r="F2" s="296"/>
+      <c r="F2" s="324"/>
       <c r="G2" s="98"/>
       <c r="H2" s="98"/>
       <c r="I2" s="98" t="s">
@@ -4247,7 +4286,7 @@
         <v>13312274.1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="102"/>
       <c r="B3" s="103"/>
       <c r="C3" s="103"/>
@@ -4265,241 +4304,241 @@
       <c r="O3" s="106"/>
       <c r="P3" s="80"/>
     </row>
-    <row r="4" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="273" t="s">
+    <row r="4" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="303" t="s">
         <v>159</v>
       </c>
-      <c r="B4" s="274"/>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="274"/>
-      <c r="I4" s="274"/>
-      <c r="J4" s="274"/>
-      <c r="K4" s="274"/>
-      <c r="L4" s="274"/>
-      <c r="M4" s="274"/>
-      <c r="N4" s="274"/>
-      <c r="O4" s="275"/>
+      <c r="B4" s="304"/>
+      <c r="C4" s="304"/>
+      <c r="D4" s="304"/>
+      <c r="E4" s="304"/>
+      <c r="F4" s="304"/>
+      <c r="G4" s="304"/>
+      <c r="H4" s="304"/>
+      <c r="I4" s="304"/>
+      <c r="J4" s="304"/>
+      <c r="K4" s="304"/>
+      <c r="L4" s="304"/>
+      <c r="M4" s="304"/>
+      <c r="N4" s="304"/>
+      <c r="O4" s="305"/>
       <c r="P4" s="80"/>
     </row>
-    <row r="5" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="276"/>
-      <c r="B5" s="277"/>
-      <c r="C5" s="277"/>
-      <c r="D5" s="277"/>
-      <c r="E5" s="277"/>
-      <c r="F5" s="277"/>
-      <c r="G5" s="277"/>
-      <c r="H5" s="277"/>
-      <c r="I5" s="277"/>
-      <c r="J5" s="277"/>
-      <c r="K5" s="277"/>
-      <c r="L5" s="277"/>
-      <c r="M5" s="277"/>
-      <c r="N5" s="277"/>
-      <c r="O5" s="278"/>
+    <row r="5" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="306"/>
+      <c r="B5" s="307"/>
+      <c r="C5" s="307"/>
+      <c r="D5" s="307"/>
+      <c r="E5" s="307"/>
+      <c r="F5" s="307"/>
+      <c r="G5" s="307"/>
+      <c r="H5" s="307"/>
+      <c r="I5" s="307"/>
+      <c r="J5" s="307"/>
+      <c r="K5" s="307"/>
+      <c r="L5" s="307"/>
+      <c r="M5" s="307"/>
+      <c r="N5" s="307"/>
+      <c r="O5" s="308"/>
       <c r="P5" s="80"/>
     </row>
-    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="276"/>
-      <c r="B6" s="277"/>
-      <c r="C6" s="277"/>
-      <c r="D6" s="277"/>
-      <c r="E6" s="277"/>
-      <c r="F6" s="277"/>
-      <c r="G6" s="277"/>
-      <c r="H6" s="277"/>
-      <c r="I6" s="277"/>
-      <c r="J6" s="277"/>
-      <c r="K6" s="277"/>
-      <c r="L6" s="277"/>
-      <c r="M6" s="277"/>
-      <c r="N6" s="277"/>
-      <c r="O6" s="278"/>
+    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="306"/>
+      <c r="B6" s="307"/>
+      <c r="C6" s="307"/>
+      <c r="D6" s="307"/>
+      <c r="E6" s="307"/>
+      <c r="F6" s="307"/>
+      <c r="G6" s="307"/>
+      <c r="H6" s="307"/>
+      <c r="I6" s="307"/>
+      <c r="J6" s="307"/>
+      <c r="K6" s="307"/>
+      <c r="L6" s="307"/>
+      <c r="M6" s="307"/>
+      <c r="N6" s="307"/>
+      <c r="O6" s="308"/>
       <c r="P6" s="80"/>
     </row>
-    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="276"/>
-      <c r="B7" s="277"/>
-      <c r="C7" s="277"/>
-      <c r="D7" s="277"/>
-      <c r="E7" s="277"/>
-      <c r="F7" s="277"/>
-      <c r="G7" s="277"/>
-      <c r="H7" s="277"/>
-      <c r="I7" s="277"/>
-      <c r="J7" s="277"/>
-      <c r="K7" s="277"/>
-      <c r="L7" s="277"/>
-      <c r="M7" s="277"/>
-      <c r="N7" s="277"/>
-      <c r="O7" s="278"/>
+    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="306"/>
+      <c r="B7" s="307"/>
+      <c r="C7" s="307"/>
+      <c r="D7" s="307"/>
+      <c r="E7" s="307"/>
+      <c r="F7" s="307"/>
+      <c r="G7" s="307"/>
+      <c r="H7" s="307"/>
+      <c r="I7" s="307"/>
+      <c r="J7" s="307"/>
+      <c r="K7" s="307"/>
+      <c r="L7" s="307"/>
+      <c r="M7" s="307"/>
+      <c r="N7" s="307"/>
+      <c r="O7" s="308"/>
       <c r="P7" s="80"/>
     </row>
-    <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="279"/>
-      <c r="B8" s="280"/>
-      <c r="C8" s="280"/>
-      <c r="D8" s="280"/>
-      <c r="E8" s="280"/>
-      <c r="F8" s="280"/>
-      <c r="G8" s="280"/>
-      <c r="H8" s="280"/>
-      <c r="I8" s="280"/>
-      <c r="J8" s="280"/>
-      <c r="K8" s="280"/>
-      <c r="L8" s="280"/>
-      <c r="M8" s="280"/>
-      <c r="N8" s="280"/>
-      <c r="O8" s="281"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="290" t="s">
+    <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="309"/>
+      <c r="B8" s="310"/>
+      <c r="C8" s="310"/>
+      <c r="D8" s="310"/>
+      <c r="E8" s="310"/>
+      <c r="F8" s="310"/>
+      <c r="G8" s="310"/>
+      <c r="H8" s="310"/>
+      <c r="I8" s="310"/>
+      <c r="J8" s="310"/>
+      <c r="K8" s="310"/>
+      <c r="L8" s="310"/>
+      <c r="M8" s="310"/>
+      <c r="N8" s="310"/>
+      <c r="O8" s="311"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="318" t="s">
         <v>157</v>
       </c>
-      <c r="B9" s="291"/>
-      <c r="C9" s="291"/>
-      <c r="D9" s="291"/>
-      <c r="E9" s="291"/>
-      <c r="F9" s="291"/>
-      <c r="G9" s="291"/>
-      <c r="H9" s="291"/>
-      <c r="I9" s="291"/>
-      <c r="J9" s="291"/>
-      <c r="K9" s="291"/>
-      <c r="L9" s="291"/>
-      <c r="M9" s="291"/>
-      <c r="N9" s="291"/>
-      <c r="O9" s="292"/>
-    </row>
-    <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="301" t="s">
+      <c r="B9" s="319"/>
+      <c r="C9" s="319"/>
+      <c r="D9" s="319"/>
+      <c r="E9" s="319"/>
+      <c r="F9" s="319"/>
+      <c r="G9" s="319"/>
+      <c r="H9" s="319"/>
+      <c r="I9" s="319"/>
+      <c r="J9" s="319"/>
+      <c r="K9" s="319"/>
+      <c r="L9" s="319"/>
+      <c r="M9" s="319"/>
+      <c r="N9" s="319"/>
+      <c r="O9" s="320"/>
+    </row>
+    <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="291" t="s">
         <v>218</v>
       </c>
-      <c r="B10" s="302"/>
-      <c r="C10" s="302"/>
-      <c r="D10" s="302"/>
-      <c r="E10" s="302"/>
-      <c r="F10" s="302"/>
-      <c r="G10" s="302"/>
-      <c r="H10" s="302"/>
-      <c r="I10" s="302"/>
-      <c r="J10" s="302"/>
-      <c r="K10" s="302"/>
-      <c r="L10" s="302"/>
-      <c r="M10" s="302"/>
-      <c r="N10" s="302"/>
-      <c r="O10" s="303"/>
-    </row>
-    <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="304" t="s">
+      <c r="B10" s="292"/>
+      <c r="C10" s="292"/>
+      <c r="D10" s="292"/>
+      <c r="E10" s="292"/>
+      <c r="F10" s="292"/>
+      <c r="G10" s="292"/>
+      <c r="H10" s="292"/>
+      <c r="I10" s="292"/>
+      <c r="J10" s="292"/>
+      <c r="K10" s="292"/>
+      <c r="L10" s="292"/>
+      <c r="M10" s="292"/>
+      <c r="N10" s="292"/>
+      <c r="O10" s="293"/>
+    </row>
+    <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="294" t="s">
         <v>219</v>
       </c>
-      <c r="B11" s="305"/>
-      <c r="C11" s="305"/>
-      <c r="D11" s="305"/>
-      <c r="E11" s="305"/>
-      <c r="F11" s="305"/>
-      <c r="G11" s="305"/>
-      <c r="H11" s="305"/>
-      <c r="I11" s="305"/>
-      <c r="J11" s="305"/>
-      <c r="K11" s="305"/>
-      <c r="L11" s="305"/>
-      <c r="M11" s="305"/>
-      <c r="N11" s="305"/>
-      <c r="O11" s="306"/>
-    </row>
-    <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="293" t="s">
+      <c r="B11" s="295"/>
+      <c r="C11" s="295"/>
+      <c r="D11" s="295"/>
+      <c r="E11" s="295"/>
+      <c r="F11" s="295"/>
+      <c r="G11" s="295"/>
+      <c r="H11" s="295"/>
+      <c r="I11" s="295"/>
+      <c r="J11" s="295"/>
+      <c r="K11" s="295"/>
+      <c r="L11" s="295"/>
+      <c r="M11" s="295"/>
+      <c r="N11" s="295"/>
+      <c r="O11" s="296"/>
+    </row>
+    <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="321" t="s">
         <v>158</v>
       </c>
-      <c r="B12" s="294"/>
-      <c r="C12" s="294"/>
-      <c r="D12" s="294"/>
-      <c r="E12" s="294"/>
-      <c r="F12" s="294"/>
-      <c r="G12" s="294"/>
-      <c r="H12" s="294"/>
-      <c r="I12" s="294"/>
-      <c r="J12" s="294"/>
-      <c r="K12" s="294"/>
-      <c r="L12" s="294"/>
-      <c r="M12" s="294"/>
-      <c r="N12" s="294"/>
-      <c r="O12" s="295"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="282" t="s">
+      <c r="B12" s="322"/>
+      <c r="C12" s="322"/>
+      <c r="D12" s="322"/>
+      <c r="E12" s="322"/>
+      <c r="F12" s="322"/>
+      <c r="G12" s="322"/>
+      <c r="H12" s="322"/>
+      <c r="I12" s="322"/>
+      <c r="J12" s="322"/>
+      <c r="K12" s="322"/>
+      <c r="L12" s="322"/>
+      <c r="M12" s="322"/>
+      <c r="N12" s="322"/>
+      <c r="O12" s="323"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="312" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="284" t="s">
+      <c r="B13" s="314" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="284" t="s">
+      <c r="C13" s="314" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="284" t="s">
+      <c r="D13" s="314" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="286" t="s">
+      <c r="E13" s="289" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="284" t="s">
+      <c r="F13" s="314" t="s">
         <v>133</v>
       </c>
-      <c r="G13" s="288" t="s">
+      <c r="G13" s="316" t="s">
         <v>134</v>
       </c>
-      <c r="H13" s="286" t="s">
+      <c r="H13" s="289" t="s">
         <v>135</v>
       </c>
-      <c r="I13" s="286" t="s">
+      <c r="I13" s="289" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="286" t="s">
+      <c r="J13" s="289" t="s">
         <v>126</v>
       </c>
-      <c r="K13" s="309" t="s">
+      <c r="K13" s="299" t="s">
         <v>265</v>
       </c>
-      <c r="L13" s="297" t="s">
+      <c r="L13" s="325" t="s">
         <v>174</v>
       </c>
-      <c r="M13" s="299" t="s">
+      <c r="M13" s="287" t="s">
         <v>180</v>
       </c>
       <c r="N13" s="143" t="s">
         <v>213</v>
       </c>
-      <c r="O13" s="307" t="s">
+      <c r="O13" s="297" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="283"/>
-      <c r="B14" s="285"/>
-      <c r="C14" s="285"/>
-      <c r="D14" s="285"/>
-      <c r="E14" s="287"/>
-      <c r="F14" s="285"/>
-      <c r="G14" s="289"/>
-      <c r="H14" s="287"/>
-      <c r="I14" s="287"/>
-      <c r="J14" s="287"/>
-      <c r="K14" s="310"/>
-      <c r="L14" s="298"/>
-      <c r="M14" s="300"/>
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="313"/>
+      <c r="B14" s="315"/>
+      <c r="C14" s="315"/>
+      <c r="D14" s="315"/>
+      <c r="E14" s="290"/>
+      <c r="F14" s="315"/>
+      <c r="G14" s="317"/>
+      <c r="H14" s="290"/>
+      <c r="I14" s="290"/>
+      <c r="J14" s="290"/>
+      <c r="K14" s="300"/>
+      <c r="L14" s="326"/>
+      <c r="M14" s="288"/>
       <c r="N14" s="144" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="O14" s="308"/>
-    </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O14" s="298"/>
+    </row>
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="129">
         <v>1</v>
       </c>
@@ -4551,7 +4590,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="187">
         <v>2</v>
       </c>
@@ -4604,7 +4643,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="129">
         <v>3</v>
       </c>
@@ -4657,7 +4696,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="130">
         <v>4</v>
       </c>
@@ -4710,7 +4749,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="129">
         <v>5</v>
       </c>
@@ -4762,7 +4801,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="129">
         <v>6</v>
       </c>
@@ -4814,7 +4853,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="129">
         <v>7</v>
       </c>
@@ -4867,7 +4906,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="129">
         <v>8</v>
       </c>
@@ -4920,7 +4959,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="129">
         <v>9</v>
       </c>
@@ -4972,7 +5011,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="129">
         <v>10</v>
       </c>
@@ -5024,7 +5063,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="129">
         <v>11</v>
       </c>
@@ -5077,7 +5116,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="187">
         <v>12</v>
       </c>
@@ -5129,7 +5168,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="129">
         <v>13</v>
       </c>
@@ -5182,7 +5221,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="129">
         <v>14</v>
       </c>
@@ -5232,7 +5271,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="130">
         <v>15</v>
       </c>
@@ -5285,7 +5324,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="129">
         <v>16</v>
       </c>
@@ -5338,7 +5377,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="129">
         <v>17</v>
       </c>
@@ -5391,7 +5430,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="130">
         <v>18</v>
       </c>
@@ -5444,7 +5483,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="239">
         <v>19</v>
       </c>
@@ -5499,7 +5538,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="131">
         <v>20</v>
       </c>
@@ -5553,7 +5592,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="130">
         <v>21</v>
       </c>
@@ -5606,7 +5645,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="130">
         <f>A35+1</f>
         <v>22</v>
@@ -5660,7 +5699,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="129">
         <f t="shared" ref="A37:A100" si="10">A36+1</f>
         <v>23</v>
@@ -5714,7 +5753,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="129">
         <f t="shared" si="10"/>
         <v>24</v>
@@ -5767,7 +5806,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="129">
         <f t="shared" si="10"/>
         <v>25</v>
@@ -5820,7 +5859,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="129">
         <f t="shared" si="10"/>
         <v>26</v>
@@ -5873,7 +5912,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="129">
         <f t="shared" si="10"/>
         <v>27</v>
@@ -5927,7 +5966,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="129">
         <f t="shared" si="10"/>
         <v>28</v>
@@ -5978,7 +6017,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="130">
         <f t="shared" si="10"/>
         <v>29</v>
@@ -6034,7 +6073,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="130">
         <f t="shared" si="10"/>
         <v>30</v>
@@ -6088,7 +6127,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="129">
         <f t="shared" si="10"/>
         <v>31</v>
@@ -6142,7 +6181,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="129">
         <f t="shared" si="10"/>
         <v>32</v>
@@ -6196,7 +6235,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="131">
         <f t="shared" si="10"/>
         <v>33</v>
@@ -6252,7 +6291,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="129">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -6306,7 +6345,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="192">
         <f t="shared" si="10"/>
         <v>35</v>
@@ -6363,7 +6402,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="129">
         <f t="shared" si="10"/>
         <v>36</v>
@@ -6420,7 +6459,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="129">
         <f t="shared" si="10"/>
         <v>37</v>
@@ -6435,17 +6474,14 @@
       <c r="E51" s="84">
         <v>282942.37</v>
       </c>
-      <c r="F51" s="84">
-        <f>132000+148000+3942</f>
-        <v>283942</v>
-      </c>
+      <c r="F51" s="84"/>
       <c r="G51" s="85">
         <f t="shared" si="0"/>
-        <v>-999.63000000000466</v>
+        <v>282942.37</v>
       </c>
       <c r="H51" s="85">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8488.2710999999999</v>
       </c>
       <c r="I51" s="125">
         <f t="shared" si="12"/>
@@ -6463,11 +6499,11 @@
       <c r="M51" s="147"/>
       <c r="N51" s="86">
         <f t="shared" si="6"/>
-        <v>171200.37</v>
+        <v>463631.37</v>
       </c>
       <c r="O51" s="139">
         <f t="shared" si="9"/>
-        <v>176336.37</v>
+        <v>477540.37</v>
       </c>
       <c r="P51" s="50">
         <f t="shared" si="8"/>
@@ -6477,7 +6513,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="129">
         <f t="shared" si="10"/>
         <v>38</v>
@@ -6492,14 +6528,17 @@
       <c r="E52" s="83">
         <v>749172.38</v>
       </c>
-      <c r="F52" s="84"/>
+      <c r="F52" s="84">
+        <f>E52</f>
+        <v>749172.38</v>
+      </c>
       <c r="G52" s="85">
         <f t="shared" si="0"/>
-        <v>749172.38</v>
+        <v>0</v>
       </c>
       <c r="H52" s="85">
         <f t="shared" si="3"/>
-        <v>22475.171399999999</v>
+        <v>0</v>
       </c>
       <c r="I52" s="125">
         <f t="shared" si="12"/>
@@ -6517,11 +6556,11 @@
       <c r="M52" s="147"/>
       <c r="N52" s="86">
         <f t="shared" si="6"/>
-        <v>1053048.3799999999</v>
+        <v>281400.38</v>
       </c>
       <c r="O52" s="139">
         <f t="shared" si="9"/>
-        <v>1084639.3799999999</v>
+        <v>289842.38</v>
       </c>
       <c r="P52" s="50">
         <f t="shared" si="8"/>
@@ -6531,7 +6570,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="129">
         <f t="shared" si="10"/>
         <v>39</v>
@@ -6585,7 +6624,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="129">
         <f t="shared" si="10"/>
         <v>40</v>
@@ -6639,7 +6678,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="129">
         <f t="shared" si="10"/>
         <v>41</v>
@@ -6692,7 +6731,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="131">
         <f t="shared" si="10"/>
         <v>42</v>
@@ -6747,7 +6786,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="131">
         <f t="shared" si="10"/>
         <v>43</v>
@@ -6805,7 +6844,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="130">
         <f t="shared" si="10"/>
         <v>44</v>
@@ -6862,7 +6901,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="130">
         <f t="shared" si="10"/>
         <v>45</v>
@@ -6916,12 +6955,12 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A60" s="328">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="262">
         <f t="shared" si="10"/>
         <v>46</v>
       </c>
-      <c r="B60" s="329" t="s">
+      <c r="B60" s="263" t="s">
         <v>45</v>
       </c>
       <c r="C60" s="113"/>
@@ -6972,7 +7011,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="131">
         <f t="shared" si="10"/>
         <v>47</v>
@@ -7027,7 +7066,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="219">
         <f t="shared" si="10"/>
         <v>48</v>
@@ -7084,7 +7123,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="130">
         <f t="shared" si="10"/>
         <v>49</v>
@@ -7138,7 +7177,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="130">
         <f t="shared" si="10"/>
         <v>50</v>
@@ -7191,7 +7230,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="130">
         <f t="shared" si="10"/>
         <v>51</v>
@@ -7245,7 +7284,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="130">
         <f t="shared" si="10"/>
         <v>52</v>
@@ -7299,7 +7338,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="130">
         <f t="shared" si="10"/>
         <v>53</v>
@@ -7353,7 +7392,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="130">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -7406,7 +7445,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="130">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -7460,7 +7499,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="130">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -7513,7 +7552,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="130">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7570,7 +7609,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="130">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7627,7 +7666,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="130">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7680,7 +7719,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="130">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -7733,7 +7772,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="130">
         <f t="shared" si="10"/>
         <v>61</v>
@@ -7787,7 +7826,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="130">
         <f t="shared" si="10"/>
         <v>62</v>
@@ -7841,7 +7880,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="130">
         <f t="shared" si="10"/>
         <v>63</v>
@@ -7898,7 +7937,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="130">
         <f t="shared" si="10"/>
         <v>64</v>
@@ -7951,12 +7990,12 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A79" s="322">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" s="256">
         <f t="shared" si="10"/>
         <v>65</v>
       </c>
-      <c r="B79" s="323" t="s">
+      <c r="B79" s="257" t="s">
         <v>64</v>
       </c>
       <c r="C79" s="113"/>
@@ -7966,9 +8005,7 @@
       <c r="E79" s="84">
         <v>546922.65</v>
       </c>
-      <c r="F79" s="176">
-        <v>0</v>
-      </c>
+      <c r="F79" s="176"/>
       <c r="G79" s="111">
         <f t="shared" ref="G79:G117" si="16">E79-F79</f>
         <v>546922.65</v>
@@ -8007,7 +8044,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="130">
         <f t="shared" si="10"/>
         <v>66</v>
@@ -8060,7 +8097,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="130">
         <f t="shared" si="10"/>
         <v>67</v>
@@ -8113,7 +8150,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="187">
         <f t="shared" si="10"/>
         <v>68</v>
@@ -8168,7 +8205,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="233">
         <f t="shared" si="10"/>
         <v>69</v>
@@ -8223,7 +8260,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="245">
         <f t="shared" si="10"/>
         <v>70</v>
@@ -8279,7 +8316,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="130">
         <f t="shared" si="10"/>
         <v>71</v>
@@ -8333,7 +8370,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="130">
         <f t="shared" si="10"/>
         <v>72</v>
@@ -8387,7 +8424,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="130">
         <f t="shared" si="10"/>
         <v>73</v>
@@ -8441,7 +8478,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="239">
         <f t="shared" si="10"/>
         <v>74</v>
@@ -8497,7 +8534,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="129">
         <f t="shared" si="10"/>
         <v>75</v>
@@ -8550,7 +8587,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="189">
         <f t="shared" si="10"/>
         <v>76</v>
@@ -8603,7 +8640,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="129">
         <f t="shared" si="10"/>
         <v>77</v>
@@ -8657,7 +8694,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="131">
         <f t="shared" si="10"/>
         <v>78</v>
@@ -8713,7 +8750,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="129">
         <f t="shared" si="10"/>
         <v>79</v>
@@ -8770,7 +8807,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="130">
         <f t="shared" si="10"/>
         <v>80</v>
@@ -8823,7 +8860,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="130">
         <f t="shared" si="10"/>
         <v>81</v>
@@ -8880,7 +8917,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="130">
         <f t="shared" si="10"/>
         <v>82</v>
@@ -8934,7 +8971,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="130">
         <f t="shared" si="10"/>
         <v>83</v>
@@ -8988,7 +9025,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="130">
         <f t="shared" si="10"/>
         <v>84</v>
@@ -9039,7 +9076,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="129">
         <f t="shared" si="10"/>
         <v>85</v>
@@ -9093,7 +9130,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="130">
         <f t="shared" si="10"/>
         <v>86</v>
@@ -9146,7 +9183,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="129">
         <f t="shared" ref="A101:A117" si="24">A100+1</f>
         <v>87</v>
@@ -9200,7 +9237,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="129">
         <f t="shared" si="24"/>
         <v>88</v>
@@ -9254,7 +9291,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="129">
         <f t="shared" si="24"/>
         <v>89</v>
@@ -9308,7 +9345,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="129">
         <f t="shared" si="24"/>
         <v>90</v>
@@ -9362,7 +9399,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="129">
         <f t="shared" si="24"/>
         <v>91</v>
@@ -9415,7 +9452,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="129">
         <f t="shared" si="24"/>
         <v>92</v>
@@ -9468,7 +9505,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="130">
         <f t="shared" si="24"/>
         <v>93</v>
@@ -9521,7 +9558,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="130">
         <f t="shared" si="24"/>
         <v>94</v>
@@ -9575,7 +9612,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="130">
         <f t="shared" si="24"/>
         <v>95</v>
@@ -9629,7 +9666,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="130">
         <f t="shared" si="24"/>
         <v>96</v>
@@ -9686,7 +9723,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="130">
         <f t="shared" si="24"/>
         <v>97</v>
@@ -9740,7 +9777,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="130">
         <f t="shared" si="24"/>
         <v>98</v>
@@ -9794,7 +9831,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="130">
         <f t="shared" si="24"/>
         <v>99</v>
@@ -9848,7 +9885,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="130">
         <f t="shared" si="24"/>
         <v>100</v>
@@ -9902,7 +9939,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="130">
         <f t="shared" si="24"/>
         <v>101</v>
@@ -9955,7 +9992,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="130">
         <f t="shared" si="24"/>
         <v>102</v>
@@ -10009,7 +10046,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="130">
         <f t="shared" si="24"/>
         <v>103</v>
@@ -10063,7 +10100,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="130"/>
       <c r="B118" s="108"/>
       <c r="C118" s="113"/>
@@ -10081,7 +10118,7 @@
       <c r="O118" s="140"/>
       <c r="P118" s="50"/>
     </row>
-    <row r="119" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="132"/>
       <c r="B119" s="133"/>
       <c r="C119" s="133"/>
@@ -10095,15 +10132,15 @@
       </c>
       <c r="F119" s="136">
         <f>SUM(F15:F118)</f>
-        <v>15926490.739999998</v>
+        <v>16391721.119999999</v>
       </c>
       <c r="G119" s="136">
         <f t="shared" si="29"/>
-        <v>23851772.82</v>
+        <v>23386542.439999998</v>
       </c>
       <c r="H119" s="136">
         <f t="shared" si="29"/>
-        <v>676099.48949999991</v>
+        <v>662112.58919999993</v>
       </c>
       <c r="I119" s="137">
         <f t="shared" si="29"/>
@@ -10118,116 +10155,116 @@
       <c r="M119" s="150"/>
       <c r="N119" s="145">
         <f t="shared" si="29"/>
-        <v>46712826.56000001</v>
+        <v>46233609.56000001</v>
       </c>
       <c r="O119" s="142">
         <f t="shared" si="29"/>
-        <v>48114209.560000002</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>47620616.560000002</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="89"/>
       <c r="C120" s="89"/>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="271" t="s">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="301" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="271"/>
-      <c r="D122" s="271"/>
-      <c r="E122" s="271"/>
-      <c r="F122" s="271"/>
-      <c r="G122" s="271"/>
-      <c r="H122" s="271"/>
-      <c r="I122" s="271"/>
-      <c r="J122" s="271"/>
-      <c r="K122" s="271"/>
-      <c r="L122" s="271"/>
-      <c r="M122" s="271"/>
-      <c r="N122" s="271"/>
-    </row>
-    <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="271"/>
-      <c r="C123" s="271"/>
-      <c r="D123" s="271"/>
-      <c r="E123" s="271"/>
-      <c r="F123" s="271"/>
-      <c r="G123" s="271"/>
-      <c r="H123" s="271"/>
-      <c r="I123" s="271"/>
-      <c r="J123" s="271"/>
-      <c r="K123" s="271"/>
-      <c r="L123" s="271"/>
-      <c r="M123" s="271"/>
-      <c r="N123" s="271"/>
-    </row>
-    <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="271"/>
-      <c r="C124" s="271"/>
-      <c r="D124" s="271"/>
-      <c r="E124" s="271"/>
-      <c r="F124" s="271"/>
-      <c r="G124" s="271"/>
-      <c r="H124" s="271"/>
-      <c r="I124" s="271"/>
-      <c r="J124" s="271"/>
-      <c r="K124" s="271"/>
-      <c r="L124" s="271"/>
-      <c r="M124" s="271"/>
-      <c r="N124" s="271"/>
-    </row>
-    <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="271"/>
-      <c r="C125" s="271"/>
-      <c r="D125" s="271"/>
-      <c r="E125" s="271"/>
-      <c r="F125" s="271"/>
-      <c r="G125" s="271"/>
-      <c r="H125" s="271"/>
-      <c r="I125" s="271"/>
-      <c r="J125" s="271"/>
-      <c r="K125" s="271"/>
-      <c r="L125" s="271"/>
-      <c r="M125" s="271"/>
-      <c r="N125" s="271"/>
-    </row>
-    <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="271"/>
-      <c r="C126" s="271"/>
-      <c r="D126" s="271"/>
-      <c r="E126" s="271"/>
-      <c r="F126" s="271"/>
-      <c r="G126" s="271"/>
-      <c r="H126" s="271"/>
-      <c r="I126" s="271"/>
-      <c r="J126" s="271"/>
-      <c r="K126" s="271"/>
-      <c r="L126" s="271"/>
-      <c r="M126" s="271"/>
-      <c r="N126" s="271"/>
-    </row>
-    <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="271"/>
-      <c r="C127" s="271"/>
-      <c r="D127" s="271"/>
-      <c r="E127" s="271"/>
-      <c r="F127" s="271"/>
-      <c r="G127" s="271"/>
-      <c r="H127" s="271"/>
-      <c r="I127" s="271"/>
-      <c r="J127" s="271"/>
-      <c r="K127" s="271"/>
-      <c r="L127" s="271"/>
-      <c r="M127" s="271"/>
-      <c r="N127" s="271"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C122" s="301"/>
+      <c r="D122" s="301"/>
+      <c r="E122" s="301"/>
+      <c r="F122" s="301"/>
+      <c r="G122" s="301"/>
+      <c r="H122" s="301"/>
+      <c r="I122" s="301"/>
+      <c r="J122" s="301"/>
+      <c r="K122" s="301"/>
+      <c r="L122" s="301"/>
+      <c r="M122" s="301"/>
+      <c r="N122" s="301"/>
+    </row>
+    <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="301"/>
+      <c r="C123" s="301"/>
+      <c r="D123" s="301"/>
+      <c r="E123" s="301"/>
+      <c r="F123" s="301"/>
+      <c r="G123" s="301"/>
+      <c r="H123" s="301"/>
+      <c r="I123" s="301"/>
+      <c r="J123" s="301"/>
+      <c r="K123" s="301"/>
+      <c r="L123" s="301"/>
+      <c r="M123" s="301"/>
+      <c r="N123" s="301"/>
+    </row>
+    <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="301"/>
+      <c r="C124" s="301"/>
+      <c r="D124" s="301"/>
+      <c r="E124" s="301"/>
+      <c r="F124" s="301"/>
+      <c r="G124" s="301"/>
+      <c r="H124" s="301"/>
+      <c r="I124" s="301"/>
+      <c r="J124" s="301"/>
+      <c r="K124" s="301"/>
+      <c r="L124" s="301"/>
+      <c r="M124" s="301"/>
+      <c r="N124" s="301"/>
+    </row>
+    <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="301"/>
+      <c r="C125" s="301"/>
+      <c r="D125" s="301"/>
+      <c r="E125" s="301"/>
+      <c r="F125" s="301"/>
+      <c r="G125" s="301"/>
+      <c r="H125" s="301"/>
+      <c r="I125" s="301"/>
+      <c r="J125" s="301"/>
+      <c r="K125" s="301"/>
+      <c r="L125" s="301"/>
+      <c r="M125" s="301"/>
+      <c r="N125" s="301"/>
+    </row>
+    <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="301"/>
+      <c r="C126" s="301"/>
+      <c r="D126" s="301"/>
+      <c r="E126" s="301"/>
+      <c r="F126" s="301"/>
+      <c r="G126" s="301"/>
+      <c r="H126" s="301"/>
+      <c r="I126" s="301"/>
+      <c r="J126" s="301"/>
+      <c r="K126" s="301"/>
+      <c r="L126" s="301"/>
+      <c r="M126" s="301"/>
+      <c r="N126" s="301"/>
+    </row>
+    <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="301"/>
+      <c r="C127" s="301"/>
+      <c r="D127" s="301"/>
+      <c r="E127" s="301"/>
+      <c r="F127" s="301"/>
+      <c r="G127" s="301"/>
+      <c r="H127" s="301"/>
+      <c r="I127" s="301"/>
+      <c r="J127" s="301"/>
+      <c r="K127" s="301"/>
+      <c r="L127" s="301"/>
+      <c r="M127" s="301"/>
+      <c r="N127" s="301"/>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B130">
         <v>1631378.049999997</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>260</v>
       </c>
@@ -10235,7 +10272,7 @@
         <v>-3942</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>259</v>
       </c>
@@ -10245,12 +10282,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="K13:K14"/>
     <mergeCell ref="B122:N127"/>
     <mergeCell ref="D1:N1"/>
     <mergeCell ref="A4:O8"/>
@@ -10267,6 +10298,12 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="K13:K14"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
@@ -10276,16 +10313,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
   <dimension ref="C3:N65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="19"/>
     </row>
-    <row r="4" spans="3:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:14" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="172" t="s">
         <v>190</v>
       </c>
@@ -10301,7 +10338,7 @@
       <c r="K4" s="19"/>
       <c r="L4" s="19"/>
     </row>
-    <row r="5" spans="3:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="174" t="s">
         <v>191</v>
       </c>
@@ -10318,7 +10355,7 @@
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C6" s="174" t="s">
         <v>194</v>
       </c>
@@ -10340,7 +10377,7 @@
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
     </row>
-    <row r="7" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="47" t="s">
         <v>197</v>
       </c>
@@ -10350,38 +10387,38 @@
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
     </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C8" s="311" t="s">
+    <row r="8" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C8" s="327" t="s">
         <v>268</v>
       </c>
-      <c r="D8" s="312"/>
-      <c r="E8" s="312"/>
-      <c r="F8" s="312"/>
-      <c r="G8" s="312"/>
-      <c r="H8" s="312"/>
-      <c r="I8" s="312"/>
-      <c r="J8" s="313"/>
+      <c r="D8" s="328"/>
+      <c r="E8" s="328"/>
+      <c r="F8" s="328"/>
+      <c r="G8" s="328"/>
+      <c r="H8" s="328"/>
+      <c r="I8" s="328"/>
+      <c r="J8" s="329"/>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
     </row>
-    <row r="9" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="314"/>
-      <c r="D9" s="315"/>
-      <c r="E9" s="315"/>
-      <c r="F9" s="315"/>
-      <c r="G9" s="315"/>
-      <c r="H9" s="315"/>
-      <c r="I9" s="315"/>
-      <c r="J9" s="316"/>
+    <row r="9" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="330"/>
+      <c r="D9" s="331"/>
+      <c r="E9" s="331"/>
+      <c r="F9" s="331"/>
+      <c r="G9" s="331"/>
+      <c r="H9" s="331"/>
+      <c r="I9" s="331"/>
+      <c r="J9" s="332"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
     </row>
-    <row r="11" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C12" s="236" t="s">
         <v>190</v>
       </c>
@@ -10395,7 +10432,7 @@
       <c r="I12" s="169"/>
       <c r="J12" s="170"/>
     </row>
-    <row r="13" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C13" s="238" t="s">
         <v>191</v>
       </c>
@@ -10409,7 +10446,7 @@
       <c r="J13" s="171"/>
       <c r="L13" s="235"/>
     </row>
-    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C14" s="238" t="s">
         <v>194</v>
       </c>
@@ -10424,36 +10461,36 @@
       </c>
       <c r="J14" s="171"/>
     </row>
-    <row r="15" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="47" t="s">
         <v>197</v>
       </c>
       <c r="J15" s="171"/>
     </row>
-    <row r="16" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C16" s="317" t="s">
+    <row r="16" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C16" s="333" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="312"/>
-      <c r="E16" s="312"/>
-      <c r="F16" s="312"/>
-      <c r="G16" s="312"/>
-      <c r="H16" s="312"/>
-      <c r="I16" s="312"/>
-      <c r="J16" s="313"/>
-    </row>
-    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="314"/>
-      <c r="D17" s="315"/>
-      <c r="E17" s="315"/>
-      <c r="F17" s="315"/>
-      <c r="G17" s="315"/>
-      <c r="H17" s="315"/>
-      <c r="I17" s="315"/>
-      <c r="J17" s="316"/>
-    </row>
-    <row r="19" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D16" s="328"/>
+      <c r="E16" s="328"/>
+      <c r="F16" s="328"/>
+      <c r="G16" s="328"/>
+      <c r="H16" s="328"/>
+      <c r="I16" s="328"/>
+      <c r="J16" s="329"/>
+    </row>
+    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="330"/>
+      <c r="D17" s="331"/>
+      <c r="E17" s="331"/>
+      <c r="F17" s="331"/>
+      <c r="G17" s="331"/>
+      <c r="H17" s="331"/>
+      <c r="I17" s="331"/>
+      <c r="J17" s="332"/>
+    </row>
+    <row r="19" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="241" t="s">
         <v>190</v>
       </c>
@@ -10467,7 +10504,7 @@
       <c r="I20" s="169"/>
       <c r="J20" s="170"/>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="243" t="s">
         <v>191</v>
       </c>
@@ -10480,7 +10517,7 @@
       </c>
       <c r="J21" s="171"/>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C22" s="243" t="s">
         <v>194</v>
       </c>
@@ -10498,37 +10535,37 @@
       </c>
       <c r="J22" s="171"/>
     </row>
-    <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="243" t="s">
         <v>197</v>
       </c>
       <c r="D23" s="244"/>
       <c r="J23" s="171"/>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="311" t="s">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C24" s="327" t="s">
         <v>275</v>
       </c>
-      <c r="D24" s="312"/>
-      <c r="E24" s="312"/>
-      <c r="F24" s="312"/>
-      <c r="G24" s="312"/>
-      <c r="H24" s="312"/>
-      <c r="I24" s="312"/>
-      <c r="J24" s="313"/>
-    </row>
-    <row r="25" spans="3:10" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="314"/>
-      <c r="D25" s="315"/>
-      <c r="E25" s="315"/>
-      <c r="F25" s="315"/>
-      <c r="G25" s="315"/>
-      <c r="H25" s="315"/>
-      <c r="I25" s="315"/>
-      <c r="J25" s="316"/>
-    </row>
-    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D24" s="328"/>
+      <c r="E24" s="328"/>
+      <c r="F24" s="328"/>
+      <c r="G24" s="328"/>
+      <c r="H24" s="328"/>
+      <c r="I24" s="328"/>
+      <c r="J24" s="329"/>
+    </row>
+    <row r="25" spans="3:10" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="330"/>
+      <c r="D25" s="331"/>
+      <c r="E25" s="331"/>
+      <c r="F25" s="331"/>
+      <c r="G25" s="331"/>
+      <c r="H25" s="331"/>
+      <c r="I25" s="331"/>
+      <c r="J25" s="332"/>
+    </row>
+    <row r="27" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C28" s="247" t="s">
         <v>190</v>
       </c>
@@ -10542,7 +10579,7 @@
       <c r="I28" s="169"/>
       <c r="J28" s="170"/>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C29" s="249" t="s">
         <v>191</v>
       </c>
@@ -10555,7 +10592,7 @@
       </c>
       <c r="J29" s="171"/>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C30" s="249" t="s">
         <v>194</v>
       </c>
@@ -10573,37 +10610,37 @@
       </c>
       <c r="J30" s="171"/>
     </row>
-    <row r="31" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="249" t="s">
         <v>197</v>
       </c>
       <c r="D31" s="250"/>
       <c r="J31" s="171"/>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="311" t="s">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C32" s="327" t="s">
         <v>272</v>
       </c>
-      <c r="D32" s="312"/>
-      <c r="E32" s="312"/>
-      <c r="F32" s="312"/>
-      <c r="G32" s="312"/>
-      <c r="H32" s="312"/>
-      <c r="I32" s="312"/>
-      <c r="J32" s="313"/>
-    </row>
-    <row r="33" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C33" s="314"/>
-      <c r="D33" s="315"/>
-      <c r="E33" s="315"/>
-      <c r="F33" s="315"/>
-      <c r="G33" s="315"/>
-      <c r="H33" s="315"/>
-      <c r="I33" s="315"/>
-      <c r="J33" s="316"/>
-    </row>
-    <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="D32" s="328"/>
+      <c r="E32" s="328"/>
+      <c r="F32" s="328"/>
+      <c r="G32" s="328"/>
+      <c r="H32" s="328"/>
+      <c r="I32" s="328"/>
+      <c r="J32" s="329"/>
+    </row>
+    <row r="33" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="330"/>
+      <c r="D33" s="331"/>
+      <c r="E33" s="331"/>
+      <c r="F33" s="331"/>
+      <c r="G33" s="331"/>
+      <c r="H33" s="331"/>
+      <c r="I33" s="331"/>
+      <c r="J33" s="332"/>
+    </row>
+    <row r="35" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C36" s="241" t="s">
         <v>190</v>
       </c>
@@ -10617,7 +10654,7 @@
       <c r="I36" s="169"/>
       <c r="J36" s="170"/>
     </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C37" s="243" t="s">
         <v>191</v>
       </c>
@@ -10630,7 +10667,7 @@
       </c>
       <c r="J37" s="171"/>
     </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C38" s="243" t="s">
         <v>194</v>
       </c>
@@ -10648,41 +10685,41 @@
       </c>
       <c r="J38" s="171"/>
     </row>
-    <row r="39" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C39" s="243" t="s">
         <v>197</v>
       </c>
       <c r="D39" s="244"/>
       <c r="J39" s="171"/>
     </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C40" s="311" t="s">
+    <row r="40" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C40" s="327" t="s">
         <v>274</v>
       </c>
-      <c r="D40" s="312"/>
-      <c r="E40" s="312"/>
-      <c r="F40" s="312"/>
-      <c r="G40" s="312"/>
-      <c r="H40" s="312"/>
-      <c r="I40" s="312"/>
-      <c r="J40" s="313"/>
-    </row>
-    <row r="41" spans="3:10" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="314"/>
-      <c r="D41" s="315"/>
-      <c r="E41" s="315"/>
-      <c r="F41" s="315"/>
-      <c r="G41" s="315"/>
-      <c r="H41" s="315"/>
-      <c r="I41" s="315"/>
-      <c r="J41" s="316"/>
-    </row>
-    <row r="43" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C44" s="318" t="s">
+      <c r="D40" s="328"/>
+      <c r="E40" s="328"/>
+      <c r="F40" s="328"/>
+      <c r="G40" s="328"/>
+      <c r="H40" s="328"/>
+      <c r="I40" s="328"/>
+      <c r="J40" s="329"/>
+    </row>
+    <row r="41" spans="3:10" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="330"/>
+      <c r="D41" s="331"/>
+      <c r="E41" s="331"/>
+      <c r="F41" s="331"/>
+      <c r="G41" s="331"/>
+      <c r="H41" s="331"/>
+      <c r="I41" s="331"/>
+      <c r="J41" s="332"/>
+    </row>
+    <row r="43" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C44" s="252" t="s">
         <v>190</v>
       </c>
-      <c r="D44" s="319">
+      <c r="D44" s="253">
         <v>1</v>
       </c>
       <c r="E44" s="169"/>
@@ -10692,11 +10729,11 @@
       <c r="I44" s="169"/>
       <c r="J44" s="170"/>
     </row>
-    <row r="45" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C45" s="320" t="s">
+    <row r="45" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C45" s="254" t="s">
         <v>191</v>
       </c>
-      <c r="D45" s="321"/>
+      <c r="D45" s="255"/>
       <c r="E45" t="s">
         <v>192</v>
       </c>
@@ -10705,11 +10742,11 @@
       </c>
       <c r="J45" s="171"/>
     </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C46" s="320" t="s">
+    <row r="46" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C46" s="254" t="s">
         <v>194</v>
       </c>
-      <c r="D46" s="321" t="s">
+      <c r="D46" s="255" t="s">
         <v>195</v>
       </c>
       <c r="E46" t="s">
@@ -10723,41 +10760,41 @@
       </c>
       <c r="J46" s="171"/>
     </row>
-    <row r="47" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C47" s="320" t="s">
+    <row r="47" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C47" s="254" t="s">
         <v>197</v>
       </c>
-      <c r="D47" s="321"/>
+      <c r="D47" s="255"/>
       <c r="J47" s="171"/>
     </row>
-    <row r="48" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C48" s="311" t="s">
+    <row r="48" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C48" s="327" t="s">
         <v>277</v>
       </c>
-      <c r="D48" s="312"/>
-      <c r="E48" s="312"/>
-      <c r="F48" s="312"/>
-      <c r="G48" s="312"/>
-      <c r="H48" s="312"/>
-      <c r="I48" s="312"/>
-      <c r="J48" s="313"/>
-    </row>
-    <row r="49" spans="3:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="314"/>
-      <c r="D49" s="315"/>
-      <c r="E49" s="315"/>
-      <c r="F49" s="315"/>
-      <c r="G49" s="315"/>
-      <c r="H49" s="315"/>
-      <c r="I49" s="315"/>
-      <c r="J49" s="316"/>
-    </row>
-    <row r="51" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C52" s="324" t="s">
+      <c r="D48" s="328"/>
+      <c r="E48" s="328"/>
+      <c r="F48" s="328"/>
+      <c r="G48" s="328"/>
+      <c r="H48" s="328"/>
+      <c r="I48" s="328"/>
+      <c r="J48" s="329"/>
+    </row>
+    <row r="49" spans="3:10" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="330"/>
+      <c r="D49" s="331"/>
+      <c r="E49" s="331"/>
+      <c r="F49" s="331"/>
+      <c r="G49" s="331"/>
+      <c r="H49" s="331"/>
+      <c r="I49" s="331"/>
+      <c r="J49" s="332"/>
+    </row>
+    <row r="51" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C52" s="258" t="s">
         <v>190</v>
       </c>
-      <c r="D52" s="325">
+      <c r="D52" s="259">
         <v>1</v>
       </c>
       <c r="E52" s="169"/>
@@ -10767,11 +10804,11 @@
       <c r="I52" s="169"/>
       <c r="J52" s="170"/>
     </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C53" s="326" t="s">
+    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C53" s="260" t="s">
         <v>191</v>
       </c>
-      <c r="D53" s="327"/>
+      <c r="D53" s="261"/>
       <c r="E53" t="s">
         <v>192</v>
       </c>
@@ -10780,11 +10817,11 @@
       </c>
       <c r="J53" s="171"/>
     </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C54" s="326" t="s">
+    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C54" s="260" t="s">
         <v>194</v>
       </c>
-      <c r="D54" s="327" t="s">
+      <c r="D54" s="261" t="s">
         <v>195</v>
       </c>
       <c r="E54" t="s">
@@ -10798,41 +10835,41 @@
       </c>
       <c r="J54" s="171"/>
     </row>
-    <row r="55" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C55" s="326" t="s">
+    <row r="55" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="260" t="s">
         <v>197</v>
       </c>
-      <c r="D55" s="327"/>
+      <c r="D55" s="261"/>
       <c r="J55" s="171"/>
     </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C56" s="311" t="s">
+    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C56" s="327" t="s">
         <v>279</v>
       </c>
-      <c r="D56" s="312"/>
-      <c r="E56" s="312"/>
-      <c r="F56" s="312"/>
-      <c r="G56" s="312"/>
-      <c r="H56" s="312"/>
-      <c r="I56" s="312"/>
-      <c r="J56" s="313"/>
-    </row>
-    <row r="57" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C57" s="314"/>
-      <c r="D57" s="315"/>
-      <c r="E57" s="315"/>
-      <c r="F57" s="315"/>
-      <c r="G57" s="315"/>
-      <c r="H57" s="315"/>
-      <c r="I57" s="315"/>
-      <c r="J57" s="316"/>
-    </row>
-    <row r="59" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C60" s="330" t="s">
+      <c r="D56" s="328"/>
+      <c r="E56" s="328"/>
+      <c r="F56" s="328"/>
+      <c r="G56" s="328"/>
+      <c r="H56" s="328"/>
+      <c r="I56" s="328"/>
+      <c r="J56" s="329"/>
+    </row>
+    <row r="57" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="330"/>
+      <c r="D57" s="331"/>
+      <c r="E57" s="331"/>
+      <c r="F57" s="331"/>
+      <c r="G57" s="331"/>
+      <c r="H57" s="331"/>
+      <c r="I57" s="331"/>
+      <c r="J57" s="332"/>
+    </row>
+    <row r="59" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C60" s="264" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="331">
+      <c r="D60" s="265">
         <v>1</v>
       </c>
       <c r="E60" s="169"/>
@@ -10842,11 +10879,11 @@
       <c r="I60" s="169"/>
       <c r="J60" s="170"/>
     </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C61" s="332" t="s">
+    <row r="61" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C61" s="266" t="s">
         <v>191</v>
       </c>
-      <c r="D61" s="333"/>
+      <c r="D61" s="267"/>
       <c r="E61" t="s">
         <v>192</v>
       </c>
@@ -10855,11 +10892,11 @@
       </c>
       <c r="J61" s="171"/>
     </row>
-    <row r="62" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C62" s="332" t="s">
+    <row r="62" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C62" s="266" t="s">
         <v>194</v>
       </c>
-      <c r="D62" s="333" t="s">
+      <c r="D62" s="267" t="s">
         <v>195</v>
       </c>
       <c r="E62" t="s">
@@ -10873,34 +10910,34 @@
       </c>
       <c r="J62" s="171"/>
     </row>
-    <row r="63" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C63" s="332" t="s">
+    <row r="63" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C63" s="266" t="s">
         <v>197</v>
       </c>
-      <c r="D63" s="333"/>
+      <c r="D63" s="267"/>
       <c r="J63" s="171"/>
     </row>
-    <row r="64" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C64" s="311" t="s">
+    <row r="64" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C64" s="327" t="s">
         <v>280</v>
       </c>
-      <c r="D64" s="312"/>
-      <c r="E64" s="312"/>
-      <c r="F64" s="312"/>
-      <c r="G64" s="312"/>
-      <c r="H64" s="312"/>
-      <c r="I64" s="312"/>
-      <c r="J64" s="313"/>
-    </row>
-    <row r="65" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C65" s="314"/>
-      <c r="D65" s="315"/>
-      <c r="E65" s="315"/>
-      <c r="F65" s="315"/>
-      <c r="G65" s="315"/>
-      <c r="H65" s="315"/>
-      <c r="I65" s="315"/>
-      <c r="J65" s="316"/>
+      <c r="D64" s="328"/>
+      <c r="E64" s="328"/>
+      <c r="F64" s="328"/>
+      <c r="G64" s="328"/>
+      <c r="H64" s="328"/>
+      <c r="I64" s="328"/>
+      <c r="J64" s="329"/>
+    </row>
+    <row r="65" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="330"/>
+      <c r="D65" s="331"/>
+      <c r="E65" s="331"/>
+      <c r="F65" s="331"/>
+      <c r="G65" s="331"/>
+      <c r="H65" s="331"/>
+      <c r="I65" s="331"/>
+      <c r="J65" s="332"/>
     </row>
   </sheetData>
   <mergeCells count="8">
